--- a/data/live/BallparkPal_Batters_2026-04-12.xlsx
+++ b/data/live/BallparkPal_Batters_2026-04-12.xlsx
@@ -23947,61 +23947,61 @@
         <v>5</v>
       </c>
       <c r="L218" t="n">
-        <v>4.419</v>
+        <v>4.405</v>
       </c>
       <c r="M218" t="n">
-        <v>3.852</v>
+        <v>3.823</v>
       </c>
       <c r="N218" t="n">
-        <v>0.964</v>
+        <v>0.944</v>
       </c>
       <c r="O218" t="n">
-        <v>1.815</v>
+        <v>1.737</v>
       </c>
       <c r="P218" t="n">
-        <v>1.021</v>
+        <v>1.015</v>
       </c>
       <c r="Q218" t="n">
-        <v>0.479</v>
+        <v>0.495</v>
       </c>
       <c r="R218" t="n">
-        <v>0.508</v>
+        <v>0.504</v>
       </c>
       <c r="S218" t="n">
-        <v>0.255</v>
+        <v>0.259</v>
       </c>
       <c r="T218" t="n">
-        <v>0.007</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="U218" t="n">
-        <v>0.194</v>
+        <v>0.172</v>
       </c>
       <c r="V218" t="n">
-        <v>0.617</v>
+        <v>0.591</v>
       </c>
       <c r="W218" t="n">
-        <v>0.639</v>
+        <v>0.599</v>
       </c>
       <c r="X218" t="n">
-        <v>0.031</v>
+        <v>0.041</v>
       </c>
       <c r="Y218" t="n">
-        <v>0.026</v>
+        <v>0.036</v>
       </c>
       <c r="Z218" t="n">
-        <v>8.391</v>
+        <v>8.146000000000001</v>
       </c>
       <c r="AA218" t="n">
-        <v>11.237</v>
+        <v>10.893</v>
       </c>
       <c r="AB218" t="n">
-        <v>0.178</v>
+        <v>0.16</v>
       </c>
       <c r="AC218" t="n">
-        <v>0.651</v>
+        <v>0.654</v>
       </c>
       <c r="AD218" t="n">
-        <v>0.026</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="219">
@@ -24055,61 +24055,61 @@
         <v>3</v>
       </c>
       <c r="L219" t="n">
-        <v>4.589</v>
+        <v>4.575</v>
       </c>
       <c r="M219" t="n">
-        <v>3.727</v>
+        <v>3.731</v>
       </c>
       <c r="N219" t="n">
-        <v>0.995</v>
+        <v>1.011</v>
       </c>
       <c r="O219" t="n">
-        <v>1.648</v>
+        <v>1.599</v>
       </c>
       <c r="P219" t="n">
-        <v>0.702</v>
+        <v>0.696</v>
       </c>
       <c r="Q219" t="n">
-        <v>0.755</v>
+        <v>0.741</v>
       </c>
       <c r="R219" t="n">
-        <v>0.643</v>
+        <v>0.681</v>
       </c>
       <c r="S219" t="n">
-        <v>0.196</v>
+        <v>0.195</v>
       </c>
       <c r="T219" t="n">
-        <v>0.008</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="U219" t="n">
-        <v>0.147</v>
+        <v>0.125</v>
       </c>
       <c r="V219" t="n">
-        <v>0.608</v>
+        <v>0.548</v>
       </c>
       <c r="W219" t="n">
-        <v>0.707</v>
+        <v>0.649</v>
       </c>
       <c r="X219" t="n">
         <v>0.048</v>
       </c>
       <c r="Y219" t="n">
-        <v>0.04</v>
+        <v>0.038</v>
       </c>
       <c r="Z219" t="n">
-        <v>8.785</v>
+        <v>8.41</v>
       </c>
       <c r="AA219" t="n">
-        <v>11.838</v>
+        <v>11.244</v>
       </c>
       <c r="AB219" t="n">
-        <v>0.137</v>
+        <v>0.116</v>
       </c>
       <c r="AC219" t="n">
-        <v>0.654</v>
+        <v>0.672</v>
       </c>
       <c r="AD219" t="n">
-        <v>0.039</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="220">
@@ -24160,64 +24160,64 @@
         </is>
       </c>
       <c r="K220" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L220" t="n">
-        <v>4.23</v>
+        <v>4.324</v>
       </c>
       <c r="M220" t="n">
-        <v>3.583</v>
+        <v>3.649</v>
       </c>
       <c r="N220" t="n">
-        <v>0.923</v>
+        <v>0.914</v>
       </c>
       <c r="O220" t="n">
-        <v>1.738</v>
+        <v>1.692</v>
       </c>
       <c r="P220" t="n">
-        <v>1.049</v>
+        <v>1.104</v>
       </c>
       <c r="Q220" t="n">
-        <v>0.554</v>
+        <v>0.599</v>
       </c>
       <c r="R220" t="n">
-        <v>0.507</v>
+        <v>0.51</v>
       </c>
       <c r="S220" t="n">
-        <v>0.213</v>
+        <v>0.214</v>
       </c>
       <c r="T220" t="n">
         <v>0.006</v>
       </c>
       <c r="U220" t="n">
-        <v>0.197</v>
+        <v>0.184</v>
       </c>
       <c r="V220" t="n">
-        <v>0.651</v>
+        <v>0.681</v>
       </c>
       <c r="W220" t="n">
-        <v>0.633</v>
+        <v>0.608</v>
       </c>
       <c r="X220" t="n">
-        <v>0.016</v>
+        <v>0.023</v>
       </c>
       <c r="Y220" t="n">
-        <v>0.013</v>
+        <v>0.018</v>
       </c>
       <c r="Z220" t="n">
-        <v>8.34</v>
+        <v>8.353</v>
       </c>
       <c r="AA220" t="n">
-        <v>11.255</v>
+        <v>11.308</v>
       </c>
       <c r="AB220" t="n">
-        <v>0.18</v>
+        <v>0.165</v>
       </c>
       <c r="AC220" t="n">
-        <v>0.631</v>
+        <v>0.626</v>
       </c>
       <c r="AD220" t="n">
-        <v>0.012</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="221">
@@ -24268,64 +24268,64 @@
         </is>
       </c>
       <c r="K221" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L221" t="n">
-        <v>4.017</v>
+        <v>4.151</v>
       </c>
       <c r="M221" t="n">
-        <v>3.361</v>
+        <v>3.485</v>
       </c>
       <c r="N221" t="n">
-        <v>0.803</v>
+        <v>0.836</v>
       </c>
       <c r="O221" t="n">
-        <v>1.518</v>
+        <v>1.558</v>
       </c>
       <c r="P221" t="n">
-        <v>1.24</v>
+        <v>1.274</v>
       </c>
       <c r="Q221" t="n">
-        <v>0.573</v>
+        <v>0.585</v>
       </c>
       <c r="R221" t="n">
-        <v>0.455</v>
+        <v>0.489</v>
       </c>
       <c r="S221" t="n">
-        <v>0.158</v>
+        <v>0.155</v>
       </c>
       <c r="T221" t="n">
-        <v>0.013</v>
+        <v>0.008</v>
       </c>
       <c r="U221" t="n">
-        <v>0.177</v>
+        <v>0.184</v>
       </c>
       <c r="V221" t="n">
-        <v>0.569</v>
+        <v>0.582</v>
       </c>
       <c r="W221" t="n">
-        <v>0.6</v>
+        <v>0.599</v>
       </c>
       <c r="X221" t="n">
-        <v>0.1</v>
+        <v>0.103</v>
       </c>
       <c r="Y221" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="Z221" t="n">
-        <v>7.945</v>
+        <v>8.096</v>
       </c>
       <c r="AA221" t="n">
-        <v>10.704</v>
+        <v>10.888</v>
       </c>
       <c r="AB221" t="n">
-        <v>0.166</v>
+        <v>0.17</v>
       </c>
       <c r="AC221" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="AD221" t="n">
-        <v>0.083</v>
+        <v>0.081</v>
       </c>
     </row>
     <row r="222">
@@ -24379,61 +24379,61 @@
         <v>4</v>
       </c>
       <c r="L222" t="n">
-        <v>4.568</v>
+        <v>4.534</v>
       </c>
       <c r="M222" t="n">
-        <v>4.068</v>
+        <v>4.051</v>
       </c>
       <c r="N222" t="n">
-        <v>1.179</v>
+        <v>1.173</v>
       </c>
       <c r="O222" t="n">
-        <v>2.197</v>
+        <v>2.084</v>
       </c>
       <c r="P222" t="n">
-        <v>0.749</v>
+        <v>0.745</v>
       </c>
       <c r="Q222" t="n">
-        <v>0.403</v>
+        <v>0.369</v>
       </c>
       <c r="R222" t="n">
-        <v>0.66</v>
+        <v>0.698</v>
       </c>
       <c r="S222" t="n">
-        <v>0.258</v>
+        <v>0.247</v>
       </c>
       <c r="T222" t="n">
-        <v>0.022</v>
+        <v>0.021</v>
       </c>
       <c r="U222" t="n">
-        <v>0.238</v>
+        <v>0.207</v>
       </c>
       <c r="V222" t="n">
-        <v>0.712</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="W222" t="n">
-        <v>0.714</v>
+        <v>0.679</v>
       </c>
       <c r="X222" t="n">
-        <v>0.036</v>
+        <v>0.033</v>
       </c>
       <c r="Y222" t="n">
-        <v>0.03</v>
+        <v>0.026</v>
       </c>
       <c r="Z222" t="n">
-        <v>9.640000000000001</v>
+        <v>9.167</v>
       </c>
       <c r="AA222" t="n">
-        <v>12.755</v>
+        <v>12.088</v>
       </c>
       <c r="AB222" t="n">
-        <v>0.212</v>
+        <v>0.192</v>
       </c>
       <c r="AC222" t="n">
-        <v>0.724</v>
+        <v>0.727</v>
       </c>
       <c r="AD222" t="n">
-        <v>0.029</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="223">
@@ -24487,61 +24487,61 @@
         <v>1</v>
       </c>
       <c r="L223" t="n">
-        <v>4.926</v>
+        <v>4.934</v>
       </c>
       <c r="M223" t="n">
-        <v>4.292</v>
+        <v>4.263</v>
       </c>
       <c r="N223" t="n">
-        <v>1.251</v>
+        <v>1.256</v>
       </c>
       <c r="O223" t="n">
-        <v>1.93</v>
+        <v>1.931</v>
       </c>
       <c r="P223" t="n">
-        <v>0.541</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="Q223" t="n">
-        <v>0.522</v>
+        <v>0.556</v>
       </c>
       <c r="R223" t="n">
-        <v>0.874</v>
+        <v>0.889</v>
       </c>
       <c r="S223" t="n">
-        <v>0.217</v>
+        <v>0.201</v>
       </c>
       <c r="T223" t="n">
-        <v>0.018</v>
+        <v>0.023</v>
       </c>
       <c r="U223" t="n">
-        <v>0.142</v>
+        <v>0.143</v>
       </c>
       <c r="V223" t="n">
-        <v>0.571</v>
+        <v>0.595</v>
       </c>
       <c r="W223" t="n">
-        <v>0.797</v>
+        <v>0.756</v>
       </c>
       <c r="X223" t="n">
-        <v>0.216</v>
+        <v>0.222</v>
       </c>
       <c r="Y223" t="n">
-        <v>0.183</v>
+        <v>0.19</v>
       </c>
       <c r="Z223" t="n">
-        <v>9.965999999999999</v>
+        <v>10.044</v>
       </c>
       <c r="AA223" t="n">
-        <v>13.002</v>
+        <v>13.098</v>
       </c>
       <c r="AB223" t="n">
-        <v>0.135</v>
+        <v>0.133</v>
       </c>
       <c r="AC223" t="n">
-        <v>0.747</v>
+        <v>0.752</v>
       </c>
       <c r="AD223" t="n">
-        <v>0.173</v>
+        <v>0.176</v>
       </c>
     </row>
     <row r="224">
@@ -24595,61 +24595,61 @@
         <v>4</v>
       </c>
       <c r="L224" t="n">
-        <v>4.475</v>
+        <v>4.451</v>
       </c>
       <c r="M224" t="n">
-        <v>3.666</v>
+        <v>3.664</v>
       </c>
       <c r="N224" t="n">
-        <v>0.864</v>
+        <v>0.884</v>
       </c>
       <c r="O224" t="n">
-        <v>1.663</v>
+        <v>1.617</v>
       </c>
       <c r="P224" t="n">
-        <v>1.387</v>
+        <v>1.377</v>
       </c>
       <c r="Q224" t="n">
-        <v>0.726</v>
+        <v>0.706</v>
       </c>
       <c r="R224" t="n">
-        <v>0.486</v>
+        <v>0.519</v>
       </c>
       <c r="S224" t="n">
-        <v>0.162</v>
+        <v>0.175</v>
       </c>
       <c r="T224" t="n">
-        <v>0.013</v>
+        <v>0.012</v>
       </c>
       <c r="U224" t="n">
-        <v>0.203</v>
+        <v>0.178</v>
       </c>
       <c r="V224" t="n">
-        <v>0.715</v>
+        <v>0.664</v>
       </c>
       <c r="W224" t="n">
-        <v>0.675</v>
+        <v>0.635</v>
       </c>
       <c r="X224" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="Y224" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="Z224" t="n">
+        <v>8.586</v>
+      </c>
+      <c r="AA224" t="n">
+        <v>11.646</v>
+      </c>
+      <c r="AB224" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="AC224" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="AD224" t="n">
         <v>0.052</v>
-      </c>
-      <c r="Y224" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="Z224" t="n">
-        <v>8.85</v>
-      </c>
-      <c r="AA224" t="n">
-        <v>12.084</v>
-      </c>
-      <c r="AB224" t="n">
-        <v>0.187</v>
-      </c>
-      <c r="AC224" t="n">
-        <v>0.602</v>
-      </c>
-      <c r="AD224" t="n">
-        <v>0.041</v>
       </c>
     </row>
     <row r="225">
@@ -24703,61 +24703,61 @@
         <v>2</v>
       </c>
       <c r="L225" t="n">
-        <v>4.726</v>
+        <v>4.761</v>
       </c>
       <c r="M225" t="n">
-        <v>4.244</v>
+        <v>4.263</v>
       </c>
       <c r="N225" t="n">
-        <v>1.155</v>
+        <v>1.135</v>
       </c>
       <c r="O225" t="n">
-        <v>2.211</v>
+        <v>2.15</v>
       </c>
       <c r="P225" t="n">
-        <v>1.047</v>
+        <v>1.068</v>
       </c>
       <c r="Q225" t="n">
         <v>0.386</v>
       </c>
       <c r="R225" t="n">
-        <v>0.627</v>
+        <v>0.632</v>
       </c>
       <c r="S225" t="n">
-        <v>0.257</v>
+        <v>0.239</v>
       </c>
       <c r="T225" t="n">
-        <v>0.014</v>
+        <v>0.017</v>
       </c>
       <c r="U225" t="n">
-        <v>0.257</v>
+        <v>0.247</v>
       </c>
       <c r="V225" t="n">
-        <v>0.679</v>
+        <v>0.657</v>
       </c>
       <c r="W225" t="n">
-        <v>0.746</v>
+        <v>0.727</v>
       </c>
       <c r="X225" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Y225" t="n">
         <v>0.042</v>
       </c>
-      <c r="Y225" t="n">
-        <v>0.035</v>
-      </c>
       <c r="Z225" t="n">
-        <v>9.643000000000001</v>
+        <v>9.446</v>
       </c>
       <c r="AA225" t="n">
-        <v>12.763</v>
+        <v>12.482</v>
       </c>
       <c r="AB225" t="n">
-        <v>0.224</v>
+        <v>0.222</v>
       </c>
       <c r="AC225" t="n">
-        <v>0.719</v>
+        <v>0.714</v>
       </c>
       <c r="AD225" t="n">
-        <v>0.034</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="226">
@@ -24811,61 +24811,61 @@
         <v>1</v>
       </c>
       <c r="L226" t="n">
-        <v>4.81</v>
+        <v>4.834</v>
       </c>
       <c r="M226" t="n">
-        <v>4.269</v>
+        <v>4.283</v>
       </c>
       <c r="N226" t="n">
-        <v>1.058</v>
+        <v>1.05</v>
       </c>
       <c r="O226" t="n">
-        <v>2.095</v>
+        <v>1.992</v>
       </c>
       <c r="P226" t="n">
-        <v>1.279</v>
+        <v>1.302</v>
       </c>
       <c r="Q226" t="n">
-        <v>0.437</v>
+        <v>0.447</v>
       </c>
       <c r="R226" t="n">
-        <v>0.544</v>
+        <v>0.58</v>
       </c>
       <c r="S226" t="n">
-        <v>0.24</v>
+        <v>0.223</v>
       </c>
       <c r="T226" t="n">
-        <v>0.026</v>
+        <v>0.022</v>
       </c>
       <c r="U226" t="n">
-        <v>0.248</v>
+        <v>0.225</v>
       </c>
       <c r="V226" t="n">
-        <v>0.609</v>
+        <v>0.547</v>
       </c>
       <c r="W226" t="n">
-        <v>0.751</v>
+        <v>0.744</v>
       </c>
       <c r="X226" t="n">
-        <v>0.298</v>
+        <v>0.294</v>
       </c>
       <c r="Y226" t="n">
-        <v>0.252</v>
+        <v>0.241</v>
       </c>
       <c r="Z226" t="n">
-        <v>10.38</v>
+        <v>9.962999999999999</v>
       </c>
       <c r="AA226" t="n">
-        <v>13.647</v>
+        <v>13.059</v>
       </c>
       <c r="AB226" t="n">
-        <v>0.223</v>
+        <v>0.205</v>
       </c>
       <c r="AC226" t="n">
         <v>0.6820000000000001</v>
       </c>
       <c r="AD226" t="n">
-        <v>0.225</v>
+        <v>0.217</v>
       </c>
     </row>
     <row r="227">
@@ -24919,61 +24919,61 @@
         <v>3</v>
       </c>
       <c r="L227" t="n">
-        <v>4.563</v>
+        <v>4.573</v>
       </c>
       <c r="M227" t="n">
         <v>4.03</v>
       </c>
       <c r="N227" t="n">
-        <v>1.03</v>
+        <v>1.072</v>
       </c>
       <c r="O227" t="n">
-        <v>1.903</v>
+        <v>1.881</v>
       </c>
       <c r="P227" t="n">
-        <v>1.023</v>
+        <v>0.974</v>
       </c>
       <c r="Q227" t="n">
-        <v>0.434</v>
+        <v>0.446</v>
       </c>
       <c r="R227" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.641</v>
       </c>
       <c r="S227" t="n">
-        <v>0.244</v>
+        <v>0.227</v>
       </c>
       <c r="T227" t="n">
-        <v>0.03</v>
+        <v>0.031</v>
       </c>
       <c r="U227" t="n">
-        <v>0.189</v>
+        <v>0.173</v>
       </c>
       <c r="V227" t="n">
-        <v>0.615</v>
+        <v>0.581</v>
       </c>
       <c r="W227" t="n">
-        <v>0.643</v>
+        <v>0.639</v>
       </c>
       <c r="X227" t="n">
-        <v>0.044</v>
+        <v>0.052</v>
       </c>
       <c r="Y227" t="n">
-        <v>0.036</v>
+        <v>0.043</v>
       </c>
       <c r="Z227" t="n">
-        <v>8.619999999999999</v>
+        <v>8.585000000000001</v>
       </c>
       <c r="AA227" t="n">
-        <v>11.438</v>
+        <v>11.317</v>
       </c>
       <c r="AB227" t="n">
-        <v>0.178</v>
+        <v>0.161</v>
       </c>
       <c r="AC227" t="n">
-        <v>0.675</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="AD227" t="n">
-        <v>0.036</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="228">
@@ -25027,61 +25027,61 @@
         <v>5</v>
       </c>
       <c r="L228" t="n">
-        <v>4.401</v>
+        <v>4.406</v>
       </c>
       <c r="M228" t="n">
-        <v>3.576</v>
+        <v>3.569</v>
       </c>
       <c r="N228" t="n">
-        <v>0.883</v>
+        <v>0.905</v>
       </c>
       <c r="O228" t="n">
-        <v>1.683</v>
+        <v>1.684</v>
       </c>
       <c r="P228" t="n">
-        <v>1.247</v>
+        <v>1.222</v>
       </c>
       <c r="Q228" t="n">
         <v>0.737</v>
       </c>
       <c r="R228" t="n">
-        <v>0.488</v>
+        <v>0.517</v>
       </c>
       <c r="S228" t="n">
         <v>0.18</v>
       </c>
       <c r="T228" t="n">
-        <v>0.027</v>
+        <v>0.024</v>
       </c>
       <c r="U228" t="n">
-        <v>0.189</v>
+        <v>0.184</v>
       </c>
       <c r="V228" t="n">
-        <v>0.717</v>
+        <v>0.702</v>
       </c>
       <c r="W228" t="n">
-        <v>0.673</v>
+        <v>0.677</v>
       </c>
       <c r="X228" t="n">
-        <v>0.076</v>
+        <v>0.081</v>
       </c>
       <c r="Y228" t="n">
-        <v>0.062</v>
+        <v>0.067</v>
       </c>
       <c r="Z228" t="n">
-        <v>9.029</v>
+        <v>9.045</v>
       </c>
       <c r="AA228" t="n">
-        <v>12.295</v>
+        <v>12.285</v>
       </c>
       <c r="AB228" t="n">
-        <v>0.175</v>
+        <v>0.171</v>
       </c>
       <c r="AC228" t="n">
-        <v>0.618</v>
+        <v>0.628</v>
       </c>
       <c r="AD228" t="n">
-        <v>0.061</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="229">
@@ -25135,61 +25135,61 @@
         <v>9</v>
       </c>
       <c r="L229" t="n">
-        <v>3.852</v>
+        <v>3.837</v>
       </c>
       <c r="M229" t="n">
-        <v>3.481</v>
+        <v>3.437</v>
       </c>
       <c r="N229" t="n">
-        <v>0.842</v>
+        <v>0.827</v>
       </c>
       <c r="O229" t="n">
-        <v>1.605</v>
+        <v>1.553</v>
       </c>
       <c r="P229" t="n">
-        <v>1.052</v>
+        <v>0.993</v>
       </c>
       <c r="Q229" t="n">
-        <v>0.295</v>
+        <v>0.318</v>
       </c>
       <c r="R229" t="n">
-        <v>0.433</v>
+        <v>0.441</v>
       </c>
       <c r="S229" t="n">
-        <v>0.232</v>
+        <v>0.216</v>
       </c>
       <c r="T229" t="n">
         <v>0</v>
       </c>
       <c r="U229" t="n">
-        <v>0.177</v>
+        <v>0.17</v>
       </c>
       <c r="V229" t="n">
-        <v>0.547</v>
+        <v>0.523</v>
       </c>
       <c r="W229" t="n">
-        <v>0.535</v>
+        <v>0.505</v>
       </c>
       <c r="X229" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="Y229" t="n">
         <v>0.034</v>
       </c>
-      <c r="Y229" t="n">
-        <v>0.03</v>
-      </c>
       <c r="Z229" t="n">
-        <v>7.133</v>
+        <v>6.965</v>
       </c>
       <c r="AA229" t="n">
-        <v>9.507</v>
+        <v>9.263</v>
       </c>
       <c r="AB229" t="n">
-        <v>0.166</v>
+        <v>0.154</v>
       </c>
       <c r="AC229" t="n">
-        <v>0.597</v>
+        <v>0.581</v>
       </c>
       <c r="AD229" t="n">
-        <v>0.029</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="230">
@@ -25207,16 +25207,16 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>683737</v>
+        <v>687462</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Michael Busch</t>
+          <t>Spencer Horwitz</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Busch</t>
+          <t>Horwitz</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
@@ -25226,78 +25226,78 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
           <t>CHC</t>
         </is>
       </c>
-      <c r="J230" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
       <c r="K230" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L230" t="n">
-        <v>4.659</v>
+        <v>4.32</v>
       </c>
       <c r="M230" t="n">
-        <v>3.854</v>
+        <v>3.757</v>
       </c>
       <c r="N230" t="n">
-        <v>1.119</v>
+        <v>1.064</v>
       </c>
       <c r="O230" t="n">
-        <v>2.187</v>
+        <v>1.916</v>
       </c>
       <c r="P230" t="n">
-        <v>1.1</v>
+        <v>0.66</v>
       </c>
       <c r="Q230" t="n">
-        <v>0.724</v>
+        <v>0.464</v>
       </c>
       <c r="R230" t="n">
-        <v>0.612</v>
+        <v>0.615</v>
       </c>
       <c r="S230" t="n">
-        <v>0.218</v>
+        <v>0.248</v>
       </c>
       <c r="T230" t="n">
-        <v>0.019</v>
+        <v>0</v>
       </c>
       <c r="U230" t="n">
-        <v>0.271</v>
+        <v>0.201</v>
       </c>
       <c r="V230" t="n">
-        <v>0.756</v>
+        <v>0.661</v>
       </c>
       <c r="W230" t="n">
-        <v>0.825</v>
+        <v>0.6</v>
       </c>
       <c r="X230" t="n">
-        <v>0.037</v>
+        <v>0.026</v>
       </c>
       <c r="Y230" t="n">
-        <v>0.03</v>
+        <v>0.021</v>
       </c>
       <c r="Z230" t="n">
-        <v>10.54</v>
+        <v>8.656000000000001</v>
       </c>
       <c r="AA230" t="n">
-        <v>14.196</v>
+        <v>11.505</v>
       </c>
       <c r="AB230" t="n">
-        <v>0.241</v>
+        <v>0.186</v>
       </c>
       <c r="AC230" t="n">
-        <v>0.709</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="AD230" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="231">
@@ -25315,16 +25315,16 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>687462</v>
+        <v>691718</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Spencer Horwitz</t>
+          <t>Pete Crow-Armstrong</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Horwitz</t>
+          <t>Crow-Armstrong</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -25334,78 +25334,78 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
           <t>PIT</t>
-        </is>
-      </c>
-      <c r="J231" t="inlineStr">
-        <is>
-          <t>CHC</t>
         </is>
       </c>
       <c r="K231" t="n">
         <v>7</v>
       </c>
       <c r="L231" t="n">
-        <v>4.33</v>
+        <v>4.183</v>
       </c>
       <c r="M231" t="n">
-        <v>3.776</v>
+        <v>3.786</v>
       </c>
       <c r="N231" t="n">
-        <v>1.063</v>
+        <v>0.948</v>
       </c>
       <c r="O231" t="n">
-        <v>1.889</v>
+        <v>1.706</v>
       </c>
       <c r="P231" t="n">
-        <v>0.662</v>
+        <v>1.194</v>
       </c>
       <c r="Q231" t="n">
-        <v>0.457</v>
+        <v>0.303</v>
       </c>
       <c r="R231" t="n">
-        <v>0.616</v>
+        <v>0.554</v>
       </c>
       <c r="S231" t="n">
-        <v>0.257</v>
+        <v>0.198</v>
       </c>
       <c r="T231" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="U231" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="V231" t="n">
-        <v>0.64</v>
+        <v>0.639</v>
       </c>
       <c r="W231" t="n">
-        <v>0.624</v>
+        <v>0.55</v>
       </c>
       <c r="X231" t="n">
-        <v>0.026</v>
+        <v>0.286</v>
       </c>
       <c r="Y231" t="n">
-        <v>0.021</v>
+        <v>0.232</v>
       </c>
       <c r="Z231" t="n">
-        <v>8.577</v>
+        <v>8.699</v>
       </c>
       <c r="AA231" t="n">
-        <v>11.4</v>
+        <v>11.416</v>
       </c>
       <c r="AB231" t="n">
-        <v>0.174</v>
+        <v>0.158</v>
       </c>
       <c r="AC231" t="n">
-        <v>0.677</v>
+        <v>0.642</v>
       </c>
       <c r="AD231" t="n">
-        <v>0.021</v>
+        <v>0.209</v>
       </c>
     </row>
     <row r="232">
@@ -25423,97 +25423,97 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>691718</v>
+        <v>693304</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Pete Crow-Armstrong</t>
+          <t>Nick Gonzales</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Crow-Armstrong</t>
+          <t>Gonzales</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
           <t>CHC</t>
-        </is>
-      </c>
-      <c r="J232" t="inlineStr">
-        <is>
-          <t>PIT</t>
         </is>
       </c>
       <c r="K232" t="n">
         <v>6</v>
       </c>
       <c r="L232" t="n">
-        <v>4.303</v>
+        <v>4.338</v>
       </c>
       <c r="M232" t="n">
-        <v>3.895</v>
+        <v>4.034</v>
       </c>
       <c r="N232" t="n">
-        <v>1.007</v>
+        <v>1.163</v>
       </c>
       <c r="O232" t="n">
-        <v>1.882</v>
+        <v>1.883</v>
       </c>
       <c r="P232" t="n">
-        <v>1.211</v>
+        <v>0.644</v>
       </c>
       <c r="Q232" t="n">
-        <v>0.324</v>
+        <v>0.196</v>
       </c>
       <c r="R232" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.744</v>
       </c>
       <c r="S232" t="n">
-        <v>0.217</v>
+        <v>0.257</v>
       </c>
       <c r="T232" t="n">
-        <v>0.029</v>
+        <v>0.025</v>
       </c>
       <c r="U232" t="n">
-        <v>0.2</v>
+        <v>0.138</v>
       </c>
       <c r="V232" t="n">
-        <v>0.753</v>
+        <v>0.58</v>
       </c>
       <c r="W232" t="n">
-        <v>0.624</v>
+        <v>0.577</v>
       </c>
       <c r="X232" t="n">
-        <v>0.309</v>
+        <v>0.041</v>
       </c>
       <c r="Y232" t="n">
-        <v>0.255</v>
+        <v>0.034</v>
       </c>
       <c r="Z232" t="n">
-        <v>9.677</v>
+        <v>7.966</v>
       </c>
       <c r="AA232" t="n">
-        <v>12.781</v>
+        <v>10.316</v>
       </c>
       <c r="AB232" t="n">
-        <v>0.182</v>
+        <v>0.13</v>
       </c>
       <c r="AC232" t="n">
-        <v>0.667</v>
+        <v>0.713</v>
       </c>
       <c r="AD232" t="n">
-        <v>0.228</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="233">
@@ -25531,97 +25531,97 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>693304</v>
+        <v>694208</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Nick Gonzales</t>
+          <t>Moises Ballesteros</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Gonzales</t>
+          <t>Ballesteros</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
           <t>PIT</t>
         </is>
       </c>
-      <c r="J233" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
       <c r="K233" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L233" t="n">
-        <v>4.337</v>
+        <v>4.596</v>
       </c>
       <c r="M233" t="n">
-        <v>4.023</v>
+        <v>3.936</v>
       </c>
       <c r="N233" t="n">
-        <v>1.168</v>
+        <v>0.964</v>
       </c>
       <c r="O233" t="n">
-        <v>1.888</v>
+        <v>1.657</v>
       </c>
       <c r="P233" t="n">
+        <v>1.264</v>
+      </c>
+      <c r="Q233" t="n">
+        <v>0.5639999999999999</v>
+      </c>
+      <c r="R233" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="S233" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="T233" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="U233" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="V233" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="W233" t="n">
         <v>0.637</v>
       </c>
-      <c r="Q233" t="n">
-        <v>0.206</v>
-      </c>
-      <c r="R233" t="n">
-        <v>0.738</v>
-      </c>
-      <c r="S233" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="T233" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="U233" t="n">
-        <v>0.134</v>
-      </c>
-      <c r="V233" t="n">
-        <v>0.584</v>
-      </c>
-      <c r="W233" t="n">
-        <v>0.587</v>
-      </c>
       <c r="X233" t="n">
-        <v>0.038</v>
+        <v>0.033</v>
       </c>
       <c r="Y233" t="n">
-        <v>0.031</v>
+        <v>0.027</v>
       </c>
       <c r="Z233" t="n">
-        <v>8.007</v>
+        <v>8.132999999999999</v>
       </c>
       <c r="AA233" t="n">
-        <v>10.388</v>
+        <v>10.862</v>
       </c>
       <c r="AB233" t="n">
-        <v>0.126</v>
+        <v>0.153</v>
       </c>
       <c r="AC233" t="n">
-        <v>0.714</v>
+        <v>0.637</v>
       </c>
       <c r="AD233" t="n">
-        <v>0.031</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="234">
@@ -25639,97 +25639,97 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>694208</v>
+        <v>804606</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Moises Ballesteros</t>
+          <t>Konnor Griffin</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Ballesteros</t>
+          <t>Griffin</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
           <t>CHC</t>
-        </is>
-      </c>
-      <c r="J234" t="inlineStr">
-        <is>
-          <t>PIT</t>
         </is>
       </c>
       <c r="K234" t="n">
         <v>8</v>
       </c>
       <c r="L234" t="n">
-        <v>4.018</v>
+        <v>4.088</v>
       </c>
       <c r="M234" t="n">
-        <v>3.465</v>
+        <v>3.755</v>
       </c>
       <c r="N234" t="n">
-        <v>0.84</v>
+        <v>0.854</v>
       </c>
       <c r="O234" t="n">
-        <v>1.491</v>
+        <v>1.464</v>
       </c>
       <c r="P234" t="n">
-        <v>1.111</v>
+        <v>0.991</v>
       </c>
       <c r="Q234" t="n">
-        <v>0.482</v>
+        <v>0.248</v>
       </c>
       <c r="R234" t="n">
-        <v>0.515</v>
+        <v>0.524</v>
       </c>
       <c r="S234" t="n">
-        <v>0.156</v>
+        <v>0.191</v>
       </c>
       <c r="T234" t="n">
-        <v>0.008999999999999999</v>
+        <v>0</v>
       </c>
       <c r="U234" t="n">
-        <v>0.159</v>
+        <v>0.14</v>
       </c>
       <c r="V234" t="n">
-        <v>0.549</v>
+        <v>0.503</v>
       </c>
       <c r="W234" t="n">
-        <v>0.582</v>
+        <v>0.473</v>
       </c>
       <c r="X234" t="n">
-        <v>0.022</v>
+        <v>0.134</v>
       </c>
       <c r="Y234" t="n">
-        <v>0.018</v>
+        <v>0.113</v>
       </c>
       <c r="Z234" t="n">
-        <v>7.305</v>
+        <v>6.932</v>
       </c>
       <c r="AA234" t="n">
-        <v>9.81</v>
+        <v>9.084</v>
       </c>
       <c r="AB234" t="n">
-        <v>0.147</v>
+        <v>0.132</v>
       </c>
       <c r="AC234" t="n">
-        <v>0.579</v>
+        <v>0.594</v>
       </c>
       <c r="AD234" t="n">
-        <v>0.017</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="235">
@@ -25747,16 +25747,16 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>804606</v>
+        <v>807713</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Konnor Griffin</t>
+          <t>Matt Shaw</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Griffin</t>
+          <t>Shaw</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -25766,78 +25766,78 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
           <t>PIT</t>
         </is>
       </c>
-      <c r="J235" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
       <c r="K235" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L235" t="n">
-        <v>4.131</v>
+        <v>3.766</v>
       </c>
       <c r="M235" t="n">
-        <v>3.789</v>
+        <v>3.172</v>
       </c>
       <c r="N235" t="n">
-        <v>0.906</v>
+        <v>0.779</v>
       </c>
       <c r="O235" t="n">
-        <v>1.607</v>
+        <v>1.269</v>
       </c>
       <c r="P235" t="n">
-        <v>0.995</v>
+        <v>0.959</v>
       </c>
       <c r="Q235" t="n">
-        <v>0.253</v>
+        <v>0.516</v>
       </c>
       <c r="R235" t="n">
-        <v>0.537</v>
+        <v>0.497</v>
       </c>
       <c r="S235" t="n">
-        <v>0.202</v>
+        <v>0.175</v>
       </c>
       <c r="T235" t="n">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="U235" t="n">
-        <v>0.166</v>
+        <v>0.099</v>
       </c>
       <c r="V235" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.441</v>
       </c>
       <c r="W235" t="n">
-        <v>0.529</v>
+        <v>0.521</v>
       </c>
       <c r="X235" t="n">
-        <v>0.142</v>
+        <v>0.146</v>
       </c>
       <c r="Y235" t="n">
-        <v>0.114</v>
+        <v>0.121</v>
       </c>
       <c r="Z235" t="n">
-        <v>7.54</v>
+        <v>6.986</v>
       </c>
       <c r="AA235" t="n">
-        <v>9.917</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="AB235" t="n">
-        <v>0.156</v>
+        <v>0.095</v>
       </c>
       <c r="AC235" t="n">
-        <v>0.617</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="AD235" t="n">
-        <v>0.11</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="236">

--- a/data/live/BallparkPal_Batters_2026-04-12.xlsx
+++ b/data/live/BallparkPal_Batters_2026-04-12.xlsx
@@ -616,64 +616,64 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>4.159</v>
+        <v>4.253</v>
       </c>
       <c r="M2" t="n">
-        <v>3.66</v>
+        <v>3.741</v>
       </c>
       <c r="N2" t="n">
-        <v>0.908</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>1.634</v>
+        <v>1.67</v>
       </c>
       <c r="P2" t="n">
-        <v>0.727</v>
+        <v>0.709</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.409</v>
+        <v>0.411</v>
       </c>
       <c r="R2" t="n">
-        <v>0.553</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>0.165</v>
+        <v>0.175</v>
       </c>
       <c r="T2" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.179</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.534</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="Y2" t="n">
         <v>0.011</v>
       </c>
-      <c r="U2" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.549</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.529</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.013</v>
-      </c>
       <c r="Z2" t="n">
-        <v>7.408</v>
+        <v>7.606</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.824</v>
+        <v>10.109</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.167</v>
+        <v>0.168</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.619</v>
+        <v>0.642</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.013</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="3">
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>621439</v>
+        <v>605170</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Byron Buxton</t>
+          <t>Victor Caratini</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buxton</t>
+          <t>Caratini</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>S</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -724,64 +724,64 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L3" t="n">
-        <v>4.652</v>
+        <v>4.212</v>
       </c>
       <c r="M3" t="n">
-        <v>4.137</v>
+        <v>3.792</v>
       </c>
       <c r="N3" t="n">
-        <v>1.028</v>
+        <v>0.948</v>
       </c>
       <c r="O3" t="n">
-        <v>2.07</v>
+        <v>1.597</v>
       </c>
       <c r="P3" t="n">
-        <v>1.192</v>
+        <v>0.655</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.42</v>
+        <v>0.321</v>
       </c>
       <c r="R3" t="n">
-        <v>0.517</v>
+        <v>0.595</v>
       </c>
       <c r="S3" t="n">
-        <v>0.225</v>
+        <v>0.204</v>
       </c>
       <c r="T3" t="n">
-        <v>0.041</v>
+        <v>0.003</v>
       </c>
       <c r="U3" t="n">
-        <v>0.245</v>
+        <v>0.147</v>
       </c>
       <c r="V3" t="n">
-        <v>0.539</v>
+        <v>0.495</v>
       </c>
       <c r="W3" t="n">
-        <v>0.698</v>
+        <v>0.472</v>
       </c>
       <c r="X3" t="n">
-        <v>0.221</v>
+        <v>0.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.179</v>
+        <v>0.018</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.664999999999999</v>
+        <v>6.956</v>
       </c>
       <c r="AA3" t="n">
-        <v>12.666</v>
+        <v>9.103</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.223</v>
+        <v>0.136</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.67</v>
+        <v>0.646</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.168</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="4">
@@ -799,23 +799,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>623168</v>
+        <v>650391</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tyler Heineman</t>
+          <t>Eloy Jimenez</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Heineman</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
+          <t>Jimenez</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>H</t>
@@ -832,64 +828,64 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L4" t="n">
-        <v>3.491</v>
+        <v>3.821</v>
       </c>
       <c r="M4" t="n">
-        <v>3.188</v>
+        <v>3.244</v>
       </c>
       <c r="N4" t="n">
-        <v>0.668</v>
+        <v>0.709</v>
       </c>
       <c r="O4" t="n">
-        <v>1.056</v>
+        <v>1.215</v>
       </c>
       <c r="P4" t="n">
-        <v>0.737</v>
+        <v>0.797</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.22</v>
+        <v>0.495</v>
       </c>
       <c r="R4" t="n">
-        <v>0.437</v>
+        <v>0.433</v>
       </c>
       <c r="S4" t="n">
-        <v>0.149</v>
+        <v>0.159</v>
       </c>
       <c r="T4" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="U4" t="n">
-        <v>0.077</v>
+        <v>0.114</v>
       </c>
       <c r="V4" t="n">
-        <v>0.36</v>
+        <v>0.396</v>
       </c>
       <c r="W4" t="n">
-        <v>0.324</v>
+        <v>0.399</v>
       </c>
       <c r="X4" t="n">
-        <v>0.019</v>
+        <v>0.015</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.017</v>
+        <v>0.014</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.753</v>
+        <v>5.904</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.226</v>
+        <v>7.876</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.073</v>
+        <v>0.109</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.509</v>
+        <v>0.532</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.016</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="5">
@@ -940,64 +936,64 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L5" t="n">
-        <v>3.86</v>
+        <v>4.095</v>
       </c>
       <c r="M5" t="n">
-        <v>3.533</v>
+        <v>3.734</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7</v>
+        <v>0.748</v>
       </c>
       <c r="O5" t="n">
-        <v>1.245</v>
+        <v>1.319</v>
       </c>
       <c r="P5" t="n">
-        <v>1.171</v>
+        <v>1.234</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.249</v>
+        <v>0.275</v>
       </c>
       <c r="R5" t="n">
-        <v>0.424</v>
+        <v>0.455</v>
       </c>
       <c r="S5" t="n">
-        <v>0.143</v>
+        <v>0.153</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.134</v>
+        <v>0.139</v>
       </c>
       <c r="V5" t="n">
-        <v>0.436</v>
+        <v>0.426</v>
       </c>
       <c r="W5" t="n">
-        <v>0.39</v>
+        <v>0.397</v>
       </c>
       <c r="X5" t="n">
-        <v>0.021</v>
+        <v>0.027</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.016</v>
+        <v>0.022</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.557</v>
+        <v>5.835</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.355</v>
+        <v>7.681</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.127</v>
+        <v>0.131</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.523</v>
+        <v>0.546</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.016</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="6">
@@ -1051,61 +1047,61 @@
         <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>4.256</v>
+        <v>4.171</v>
       </c>
       <c r="M6" t="n">
-        <v>3.745</v>
+        <v>3.676</v>
       </c>
       <c r="N6" t="n">
-        <v>0.909</v>
+        <v>0.853</v>
       </c>
       <c r="O6" t="n">
-        <v>1.542</v>
+        <v>1.408</v>
       </c>
       <c r="P6" t="n">
-        <v>0.968</v>
+        <v>0.989</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.416</v>
+        <v>0.406</v>
       </c>
       <c r="R6" t="n">
-        <v>0.585</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>0.159</v>
+        <v>0.156</v>
       </c>
       <c r="T6" t="n">
-        <v>0.021</v>
+        <v>0.018</v>
       </c>
       <c r="U6" t="n">
-        <v>0.144</v>
+        <v>0.121</v>
       </c>
       <c r="V6" t="n">
-        <v>0.538</v>
+        <v>0.482</v>
       </c>
       <c r="W6" t="n">
-        <v>0.471</v>
+        <v>0.427</v>
       </c>
       <c r="X6" t="n">
-        <v>0.067</v>
+        <v>0.068</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.054</v>
+        <v>0.058</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.28</v>
+        <v>6.726</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.59</v>
+        <v>8.84</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.135</v>
+        <v>0.114</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.632</v>
+        <v>0.601</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.054</v>
+        <v>0.057</v>
       </c>
     </row>
     <row r="7">
@@ -1159,61 +1155,61 @@
         <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>4.362</v>
+        <v>4.319</v>
       </c>
       <c r="M7" t="n">
-        <v>3.846</v>
+        <v>3.811</v>
       </c>
       <c r="N7" t="n">
-        <v>0.862</v>
+        <v>0.856</v>
       </c>
       <c r="O7" t="n">
-        <v>1.57</v>
+        <v>1.544</v>
       </c>
       <c r="P7" t="n">
-        <v>1.17</v>
+        <v>1.145</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.424</v>
+        <v>0.413</v>
       </c>
       <c r="R7" t="n">
         <v>0.512</v>
       </c>
       <c r="S7" t="n">
-        <v>0.159</v>
+        <v>0.158</v>
       </c>
       <c r="T7" t="n">
-        <v>0.025</v>
+        <v>0.027</v>
       </c>
       <c r="U7" t="n">
-        <v>0.166</v>
+        <v>0.158</v>
       </c>
       <c r="V7" t="n">
-        <v>0.464</v>
+        <v>0.416</v>
       </c>
       <c r="W7" t="n">
-        <v>0.533</v>
+        <v>0.507</v>
       </c>
       <c r="X7" t="n">
-        <v>0.095</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.074</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.407</v>
+        <v>7.148</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.757999999999999</v>
+        <v>9.365</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.155</v>
+        <v>0.148</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.611</v>
+        <v>0.601</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.068</v>
       </c>
     </row>
     <row r="8">
@@ -1267,61 +1263,61 @@
         <v>2</v>
       </c>
       <c r="L8" t="n">
-        <v>4.576</v>
+        <v>4.538</v>
       </c>
       <c r="M8" t="n">
-        <v>3.961</v>
+        <v>3.959</v>
       </c>
       <c r="N8" t="n">
-        <v>1.002</v>
+        <v>0.985</v>
       </c>
       <c r="O8" t="n">
-        <v>1.712</v>
+        <v>1.769</v>
       </c>
       <c r="P8" t="n">
-        <v>0.951</v>
+        <v>0.915</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.506</v>
+        <v>0.484</v>
       </c>
       <c r="R8" t="n">
-        <v>0.628</v>
+        <v>0.577</v>
       </c>
       <c r="S8" t="n">
-        <v>0.201</v>
+        <v>0.215</v>
       </c>
       <c r="T8" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.012</v>
       </c>
       <c r="U8" t="n">
-        <v>0.163</v>
+        <v>0.181</v>
       </c>
       <c r="V8" t="n">
-        <v>0.489</v>
+        <v>0.494</v>
       </c>
       <c r="W8" t="n">
-        <v>0.591</v>
+        <v>0.592</v>
       </c>
       <c r="X8" t="n">
-        <v>0.055</v>
+        <v>0.046</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.045</v>
+        <v>0.037</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.995</v>
+        <v>8.041</v>
       </c>
       <c r="AA8" t="n">
-        <v>10.525</v>
+        <v>10.603</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.153</v>
+        <v>0.168</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.666</v>
+        <v>0.659</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.044</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="9">
@@ -1372,64 +1368,64 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L9" t="n">
-        <v>4.059</v>
+        <v>3.98</v>
       </c>
       <c r="M9" t="n">
-        <v>3.632</v>
+        <v>3.58</v>
       </c>
       <c r="N9" t="n">
-        <v>0.89</v>
+        <v>0.875</v>
       </c>
       <c r="O9" t="n">
-        <v>1.382</v>
+        <v>1.363</v>
       </c>
       <c r="P9" t="n">
-        <v>0.608</v>
+        <v>0.615</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.332</v>
+        <v>0.314</v>
       </c>
       <c r="R9" t="n">
-        <v>0.594</v>
+        <v>0.58</v>
       </c>
       <c r="S9" t="n">
         <v>0.187</v>
       </c>
       <c r="T9" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="Y9" t="n">
         <v>0.02</v>
       </c>
-      <c r="U9" t="n">
-        <v>0.089</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0.433</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0.427</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0.022</v>
-      </c>
       <c r="Z9" t="n">
-        <v>6.256</v>
+        <v>6.053</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.157</v>
+        <v>7.855</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.61</v>
+        <v>0.604</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.022</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="10">
@@ -1480,64 +1476,64 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>4.156</v>
+        <v>4.685</v>
       </c>
       <c r="M10" t="n">
-        <v>3.653</v>
+        <v>4.134</v>
       </c>
       <c r="N10" t="n">
-        <v>0.848</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>1.601</v>
+        <v>1.847</v>
       </c>
       <c r="P10" t="n">
-        <v>1.078</v>
+        <v>1.226</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.414</v>
+        <v>0.449</v>
       </c>
       <c r="R10" t="n">
-        <v>0.478</v>
+        <v>0.499</v>
       </c>
       <c r="S10" t="n">
-        <v>0.17</v>
+        <v>0.202</v>
       </c>
       <c r="T10" t="n">
-        <v>0.017</v>
+        <v>0.019</v>
       </c>
       <c r="U10" t="n">
-        <v>0.183</v>
+        <v>0.222</v>
       </c>
       <c r="V10" t="n">
-        <v>0.529</v>
+        <v>0.491</v>
       </c>
       <c r="W10" t="n">
-        <v>0.502</v>
+        <v>0.645</v>
       </c>
       <c r="X10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.055</v>
+        <v>0.076</v>
       </c>
       <c r="Z10" t="n">
-        <v>7.419</v>
+        <v>8.428000000000001</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.837999999999999</v>
+        <v>11.129</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.17</v>
+        <v>0.203</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.604</v>
+        <v>0.654</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.055</v>
+        <v>0.074</v>
       </c>
     </row>
     <row r="11">
@@ -1591,61 +1587,61 @@
         <v>3</v>
       </c>
       <c r="L11" t="n">
-        <v>4.27</v>
+        <v>4.228</v>
       </c>
       <c r="M11" t="n">
-        <v>3.664</v>
+        <v>3.631</v>
       </c>
       <c r="N11" t="n">
-        <v>0.997</v>
+        <v>1.021</v>
       </c>
       <c r="O11" t="n">
-        <v>1.581</v>
+        <v>1.611</v>
       </c>
       <c r="P11" t="n">
-        <v>0.612</v>
+        <v>0.58</v>
       </c>
       <c r="Q11" t="n">
         <v>0.503</v>
       </c>
       <c r="R11" t="n">
-        <v>0.68</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>0.181</v>
+        <v>0.197</v>
       </c>
       <c r="T11" t="n">
         <v>0.004</v>
       </c>
       <c r="U11" t="n">
-        <v>0.132</v>
+        <v>0.128</v>
       </c>
       <c r="V11" t="n">
-        <v>0.468</v>
+        <v>0.457</v>
       </c>
       <c r="W11" t="n">
-        <v>0.486</v>
+        <v>0.483</v>
       </c>
       <c r="X11" t="n">
-        <v>0.04</v>
+        <v>0.042</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.031</v>
+        <v>0.033</v>
       </c>
       <c r="Z11" t="n">
-        <v>7.365</v>
+        <v>7.426</v>
       </c>
       <c r="AA11" t="n">
-        <v>9.634</v>
+        <v>9.685</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.126</v>
+        <v>0.123</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.672</v>
+        <v>0.67</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.03</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="12">
@@ -1696,64 +1692,64 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L12" t="n">
-        <v>4.507</v>
+        <v>3.718</v>
       </c>
       <c r="M12" t="n">
-        <v>4.089</v>
+        <v>3.372</v>
       </c>
       <c r="N12" t="n">
-        <v>0.956</v>
+        <v>0.804</v>
       </c>
       <c r="O12" t="n">
-        <v>1.463</v>
+        <v>1.215</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.761</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.317</v>
+        <v>0.258</v>
       </c>
       <c r="R12" t="n">
-        <v>0.657</v>
+        <v>0.555</v>
       </c>
       <c r="S12" t="n">
-        <v>0.183</v>
+        <v>0.159</v>
       </c>
       <c r="T12" t="n">
-        <v>0.023</v>
+        <v>0.017</v>
       </c>
       <c r="U12" t="n">
-        <v>0.093</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>0.362</v>
+        <v>0.379</v>
       </c>
       <c r="W12" t="n">
-        <v>0.52</v>
+        <v>0.365</v>
       </c>
       <c r="X12" t="n">
-        <v>0.192</v>
+        <v>0.174</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.159</v>
+        <v>0.144</v>
       </c>
       <c r="Z12" t="n">
-        <v>7.191</v>
+        <v>6.049</v>
       </c>
       <c r="AA12" t="n">
-        <v>9.226000000000001</v>
+        <v>7.78</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.654</v>
+        <v>0.58</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.147</v>
+        <v>0.135</v>
       </c>
     </row>
     <row r="13">
@@ -1804,64 +1800,64 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L13" t="n">
-        <v>4.353</v>
+        <v>4.221</v>
       </c>
       <c r="M13" t="n">
-        <v>3.863</v>
+        <v>3.757</v>
       </c>
       <c r="N13" t="n">
-        <v>0.821</v>
+        <v>0.795</v>
       </c>
       <c r="O13" t="n">
-        <v>1.658</v>
+        <v>1.601</v>
       </c>
       <c r="P13" t="n">
-        <v>1.491</v>
+        <v>1.435</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.405</v>
+        <v>0.378</v>
       </c>
       <c r="R13" t="n">
-        <v>0.442</v>
+        <v>0.432</v>
       </c>
       <c r="S13" t="n">
-        <v>0.146</v>
+        <v>0.139</v>
       </c>
       <c r="T13" t="n">
         <v>0.007</v>
       </c>
       <c r="U13" t="n">
-        <v>0.225</v>
+        <v>0.218</v>
       </c>
       <c r="V13" t="n">
-        <v>0.612</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>0.539</v>
+        <v>0.499</v>
       </c>
       <c r="X13" t="n">
-        <v>0.053</v>
+        <v>0.049</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.045</v>
+        <v>0.039</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.705</v>
+        <v>7.296</v>
       </c>
       <c r="AA13" t="n">
-        <v>10.324</v>
+        <v>9.737</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.205</v>
+        <v>0.198</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.582</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.044</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="14">
@@ -1915,61 +1911,61 @@
         <v>5</v>
       </c>
       <c r="L14" t="n">
-        <v>4.249</v>
+        <v>4.125</v>
       </c>
       <c r="M14" t="n">
-        <v>3.768</v>
+        <v>3.66</v>
       </c>
       <c r="N14" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.649</v>
       </c>
       <c r="O14" t="n">
-        <v>1.2</v>
+        <v>1.114</v>
       </c>
       <c r="P14" t="n">
-        <v>1.467</v>
+        <v>1.445</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.404</v>
+        <v>0.386</v>
       </c>
       <c r="R14" t="n">
-        <v>0.392</v>
+        <v>0.374</v>
       </c>
       <c r="S14" t="n">
-        <v>0.186</v>
+        <v>0.18</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0.109</v>
+        <v>0.095</v>
       </c>
       <c r="V14" t="n">
-        <v>0.405</v>
+        <v>0.389</v>
       </c>
       <c r="W14" t="n">
-        <v>0.439</v>
+        <v>0.391</v>
       </c>
       <c r="X14" t="n">
-        <v>0.024</v>
+        <v>0.019</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.02</v>
+        <v>0.016</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.791</v>
+        <v>5.385</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.753</v>
+        <v>7.21</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.105</v>
+        <v>0.092</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.515</v>
+        <v>0.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.02</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="15">
@@ -2020,64 +2016,64 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>3.828</v>
+        <v>4.519</v>
       </c>
       <c r="M15" t="n">
-        <v>3.509</v>
+        <v>4.141</v>
       </c>
       <c r="N15" t="n">
-        <v>0.89</v>
+        <v>1.021</v>
       </c>
       <c r="O15" t="n">
-        <v>1.343</v>
+        <v>1.568</v>
       </c>
       <c r="P15" t="n">
-        <v>0.399</v>
+        <v>0.507</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.225</v>
+        <v>0.269</v>
       </c>
       <c r="R15" t="n">
-        <v>0.608</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>0.191</v>
+        <v>0.213</v>
       </c>
       <c r="T15" t="n">
-        <v>0.012</v>
+        <v>0.014</v>
       </c>
       <c r="U15" t="n">
-        <v>0.08</v>
+        <v>0.102</v>
       </c>
       <c r="V15" t="n">
-        <v>0.402</v>
+        <v>0.383</v>
       </c>
       <c r="W15" t="n">
-        <v>0.385</v>
+        <v>0.527</v>
       </c>
       <c r="X15" t="n">
-        <v>0.046</v>
+        <v>0.056</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.038</v>
+        <v>0.044</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.885</v>
+        <v>6.847</v>
       </c>
       <c r="AA15" t="n">
-        <v>7.575</v>
+        <v>8.795999999999999</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.078</v>
+        <v>0.097</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.626</v>
+        <v>0.67</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.037</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="16">
@@ -2095,21 +2091,21 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>676914</v>
+        <v>678218</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Davis Schneider</t>
+          <t>Brandon Valenzuela</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Schneider</t>
+          <t>Valenzuela</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>S</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2128,64 +2124,64 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L16" t="n">
-        <v>3.345</v>
+        <v>3.756</v>
       </c>
       <c r="M16" t="n">
-        <v>2.768</v>
+        <v>3.387</v>
       </c>
       <c r="N16" t="n">
-        <v>0.619</v>
+        <v>0.589</v>
       </c>
       <c r="O16" t="n">
-        <v>1.177</v>
+        <v>1.023</v>
       </c>
       <c r="P16" t="n">
-        <v>0.958</v>
+        <v>1.282</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.505</v>
+        <v>0.296</v>
       </c>
       <c r="R16" t="n">
-        <v>0.344</v>
+        <v>0.354</v>
       </c>
       <c r="S16" t="n">
-        <v>0.132</v>
+        <v>0.136</v>
       </c>
       <c r="T16" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0.139</v>
+        <v>0.099</v>
       </c>
       <c r="V16" t="n">
-        <v>0.396</v>
+        <v>0.358</v>
       </c>
       <c r="W16" t="n">
-        <v>0.42</v>
+        <v>0.343</v>
       </c>
       <c r="X16" t="n">
-        <v>0.037</v>
+        <v>0.029</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.029</v>
+        <v>0.024</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.904</v>
+        <v>4.85</v>
       </c>
       <c r="AA16" t="n">
-        <v>7.95</v>
+        <v>6.453</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.13</v>
+        <v>0.094</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.469</v>
+        <v>0.457</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.028</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="17">
@@ -2203,21 +2199,21 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>680777</v>
+        <v>681546</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ryan Jeffers</t>
+          <t>James Outman</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jeffers</t>
+          <t>Outman</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2236,64 +2232,64 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L17" t="n">
-        <v>4.191</v>
+        <v>3.879</v>
       </c>
       <c r="M17" t="n">
-        <v>3.683</v>
+        <v>3.407</v>
       </c>
       <c r="N17" t="n">
-        <v>0.858</v>
+        <v>0.653</v>
       </c>
       <c r="O17" t="n">
-        <v>1.415</v>
+        <v>1.24</v>
       </c>
       <c r="P17" t="n">
-        <v>0.775</v>
+        <v>1.394</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.414</v>
+        <v>0.392</v>
       </c>
       <c r="R17" t="n">
-        <v>0.532</v>
+        <v>0.369</v>
       </c>
       <c r="S17" t="n">
-        <v>0.208</v>
+        <v>0.128</v>
       </c>
       <c r="T17" t="n">
-        <v>0.003</v>
+        <v>0.012</v>
       </c>
       <c r="U17" t="n">
-        <v>0.114</v>
+        <v>0.145</v>
       </c>
       <c r="V17" t="n">
-        <v>0.406</v>
+        <v>0.405</v>
       </c>
       <c r="W17" t="n">
-        <v>0.479</v>
+        <v>0.424</v>
       </c>
       <c r="X17" t="n">
-        <v>0.04</v>
+        <v>0.105</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.031</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="Z17" t="n">
-        <v>6.557</v>
+        <v>6.15</v>
       </c>
       <c r="AA17" t="n">
-        <v>8.625999999999999</v>
+        <v>8.170999999999999</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.108</v>
+        <v>0.138</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.609</v>
+        <v>0.502</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.03</v>
+        <v>0.082</v>
       </c>
     </row>
     <row r="18">
@@ -2347,61 +2343,61 @@
         <v>8</v>
       </c>
       <c r="L18" t="n">
-        <v>4.045</v>
+        <v>4.035</v>
       </c>
       <c r="M18" t="n">
-        <v>3.693</v>
+        <v>3.719</v>
       </c>
       <c r="N18" t="n">
-        <v>0.949</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>1.481</v>
+        <v>1.496</v>
       </c>
       <c r="P18" t="n">
-        <v>0.731</v>
+        <v>0.722</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.259</v>
+        <v>0.224</v>
       </c>
       <c r="R18" t="n">
-        <v>0.635</v>
+        <v>0.609</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2</v>
+        <v>0.209</v>
       </c>
       <c r="T18" t="n">
         <v>0.008999999999999999</v>
       </c>
       <c r="U18" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.426</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>6.328</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>8.144</v>
+      </c>
+      <c r="AB18" t="n">
         <v>0.105</v>
       </c>
-      <c r="V18" t="n">
-        <v>0.462</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0.438</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0.046</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>6.524</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>8.456</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0.101</v>
-      </c>
       <c r="AC18" t="n">
-        <v>0.642</v>
+        <v>0.638</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.035</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="19">
@@ -2455,61 +2451,61 @@
         <v>3</v>
       </c>
       <c r="L19" t="n">
-        <v>4.536</v>
+        <v>4.511</v>
       </c>
       <c r="M19" t="n">
-        <v>4.055</v>
+        <v>4.02</v>
       </c>
       <c r="N19" t="n">
-        <v>0.971</v>
+        <v>0.965</v>
       </c>
       <c r="O19" t="n">
-        <v>1.621</v>
+        <v>1.582</v>
       </c>
       <c r="P19" t="n">
-        <v>0.664</v>
+        <v>0.654</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.372</v>
+        <v>0.384</v>
       </c>
       <c r="R19" t="n">
-        <v>0.596</v>
+        <v>0.613</v>
       </c>
       <c r="S19" t="n">
-        <v>0.237</v>
+        <v>0.22</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.138</v>
+        <v>0.132</v>
       </c>
       <c r="V19" t="n">
-        <v>0.499</v>
+        <v>0.467</v>
       </c>
       <c r="W19" t="n">
-        <v>0.518</v>
+        <v>0.51</v>
       </c>
       <c r="X19" t="n">
-        <v>0.249</v>
+        <v>0.25</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.205</v>
+        <v>0.207</v>
       </c>
       <c r="Z19" t="n">
-        <v>8.151999999999999</v>
+        <v>8.015000000000001</v>
       </c>
       <c r="AA19" t="n">
-        <v>10.612</v>
+        <v>10.402</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.13</v>
+        <v>0.124</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.647</v>
+        <v>0.633</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.19</v>
+        <v>0.189</v>
       </c>
     </row>
     <row r="20">
@@ -14227,61 +14223,61 @@
         <v>3</v>
       </c>
       <c r="L128" t="n">
-        <v>4.371</v>
+        <v>4.378</v>
       </c>
       <c r="M128" t="n">
-        <v>3.729</v>
+        <v>3.722</v>
       </c>
       <c r="N128" t="n">
-        <v>0.972</v>
+        <v>0.929</v>
       </c>
       <c r="O128" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="P128" t="n">
-        <v>0.828</v>
+        <v>0.832</v>
       </c>
       <c r="Q128" t="n">
-        <v>0.546</v>
+        <v>0.551</v>
       </c>
       <c r="R128" t="n">
-        <v>0.61</v>
+        <v>0.588</v>
       </c>
       <c r="S128" t="n">
-        <v>0.203</v>
+        <v>0.194</v>
       </c>
       <c r="T128" t="n">
-        <v>0.021</v>
+        <v>0.016</v>
       </c>
       <c r="U128" t="n">
-        <v>0.138</v>
+        <v>0.132</v>
       </c>
       <c r="V128" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.556</v>
       </c>
       <c r="W128" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.552</v>
       </c>
       <c r="X128" t="n">
-        <v>0.158</v>
+        <v>0.165</v>
       </c>
       <c r="Y128" t="n">
-        <v>0.123</v>
+        <v>0.136</v>
       </c>
       <c r="Z128" t="n">
-        <v>8.347</v>
+        <v>8.173999999999999</v>
       </c>
       <c r="AA128" t="n">
-        <v>11.032</v>
+        <v>10.83</v>
       </c>
       <c r="AB128" t="n">
-        <v>0.13</v>
+        <v>0.124</v>
       </c>
       <c r="AC128" t="n">
-        <v>0.648</v>
+        <v>0.645</v>
       </c>
       <c r="AD128" t="n">
-        <v>0.117</v>
+        <v>0.129</v>
       </c>
     </row>
     <row r="129">
@@ -14332,64 +14328,64 @@
         </is>
       </c>
       <c r="K129" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L129" t="n">
-        <v>4.153</v>
+        <v>4.042</v>
       </c>
       <c r="M129" t="n">
-        <v>3.392</v>
+        <v>3.341</v>
       </c>
       <c r="N129" t="n">
-        <v>0.776</v>
+        <v>0.761</v>
       </c>
       <c r="O129" t="n">
-        <v>1.469</v>
+        <v>1.465</v>
       </c>
       <c r="P129" t="n">
-        <v>0.885</v>
+        <v>0.886</v>
       </c>
       <c r="Q129" t="n">
-        <v>0.67</v>
+        <v>0.617</v>
       </c>
       <c r="R129" t="n">
-        <v>0.443</v>
+        <v>0.431</v>
       </c>
       <c r="S129" t="n">
-        <v>0.148</v>
+        <v>0.138</v>
       </c>
       <c r="T129" t="n">
-        <v>0.01</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="U129" t="n">
-        <v>0.175</v>
+        <v>0.182</v>
       </c>
       <c r="V129" t="n">
-        <v>0.61</v>
+        <v>0.587</v>
       </c>
       <c r="W129" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.541</v>
       </c>
       <c r="X129" t="n">
-        <v>0.126</v>
+        <v>0.139</v>
       </c>
       <c r="Y129" t="n">
-        <v>0.108</v>
+        <v>0.112</v>
       </c>
       <c r="Z129" t="n">
-        <v>8.114000000000001</v>
+        <v>7.932</v>
       </c>
       <c r="AA129" t="n">
-        <v>10.984</v>
+        <v>10.703</v>
       </c>
       <c r="AB129" t="n">
-        <v>0.167</v>
+        <v>0.172</v>
       </c>
       <c r="AC129" t="n">
-        <v>0.569</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="AD129" t="n">
-        <v>0.104</v>
+        <v>0.106</v>
       </c>
     </row>
     <row r="130">
@@ -14407,97 +14403,97 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>660688</v>
+        <v>661388</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Keibert Ruiz</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Ruiz</t>
+          <t>Contreras</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>R</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
           <t>WAS</t>
         </is>
       </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="K130" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L130" t="n">
-        <v>3.706</v>
+        <v>4.571</v>
       </c>
       <c r="M130" t="n">
-        <v>3.414</v>
+        <v>3.883</v>
       </c>
       <c r="N130" t="n">
-        <v>0.761</v>
+        <v>1.037</v>
       </c>
       <c r="O130" t="n">
-        <v>1.066</v>
+        <v>1.8</v>
       </c>
       <c r="P130" t="n">
-        <v>0.457</v>
+        <v>0.7</v>
       </c>
       <c r="Q130" t="n">
-        <v>0.189</v>
+        <v>0.585</v>
       </c>
       <c r="R130" t="n">
-        <v>0.573</v>
+        <v>0.626</v>
       </c>
       <c r="S130" t="n">
-        <v>0.13</v>
+        <v>0.23</v>
       </c>
       <c r="T130" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="U130" t="n">
-        <v>0.058</v>
+        <v>0.171</v>
       </c>
       <c r="V130" t="n">
-        <v>0.296</v>
+        <v>0.594</v>
       </c>
       <c r="W130" t="n">
-        <v>0.309</v>
+        <v>0.639</v>
       </c>
       <c r="X130" t="n">
-        <v>0.034</v>
+        <v>0.053</v>
       </c>
       <c r="Y130" t="n">
-        <v>0.029</v>
+        <v>0.044</v>
       </c>
       <c r="Z130" t="n">
-        <v>4.684</v>
+        <v>8.676</v>
       </c>
       <c r="AA130" t="n">
-        <v>5.963</v>
+        <v>11.545</v>
       </c>
       <c r="AB130" t="n">
-        <v>0.056</v>
+        <v>0.16</v>
       </c>
       <c r="AC130" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.674</v>
       </c>
       <c r="AD130" t="n">
-        <v>0.029</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="131">
@@ -14515,16 +14511,16 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>661388</v>
+        <v>663604</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Brandon Lockridge</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Contreras</t>
+          <t>Lockridge</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -14548,64 +14544,64 @@
         </is>
       </c>
       <c r="K131" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L131" t="n">
-        <v>4.592</v>
+        <v>3.909</v>
       </c>
       <c r="M131" t="n">
-        <v>3.889</v>
+        <v>3.457</v>
       </c>
       <c r="N131" t="n">
-        <v>1.04</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="O131" t="n">
-        <v>1.798</v>
+        <v>1.191</v>
       </c>
       <c r="P131" t="n">
-        <v>0.656</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="Q131" t="n">
-        <v>0.596</v>
+        <v>0.36</v>
       </c>
       <c r="R131" t="n">
-        <v>0.631</v>
+        <v>0.579</v>
       </c>
       <c r="S131" t="n">
-        <v>0.231</v>
+        <v>0.157</v>
       </c>
       <c r="T131" t="n">
-        <v>0.008</v>
+        <v>0.014</v>
       </c>
       <c r="U131" t="n">
-        <v>0.17</v>
+        <v>0.064</v>
       </c>
       <c r="V131" t="n">
+        <v>0.403</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.243</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>6.588</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>8.534000000000001</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="AC131" t="n">
         <v>0.587</v>
       </c>
-      <c r="W131" t="n">
-        <v>0.674</v>
-      </c>
-      <c r="X131" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="Y131" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="Z131" t="n">
-        <v>8.691000000000001</v>
-      </c>
-      <c r="AA131" t="n">
-        <v>11.587</v>
-      </c>
-      <c r="AB131" t="n">
-        <v>0.161</v>
-      </c>
-      <c r="AC131" t="n">
-        <v>0.6820000000000001</v>
-      </c>
       <c r="AD131" t="n">
-        <v>0.032</v>
+        <v>0.177</v>
       </c>
     </row>
     <row r="132">
@@ -14623,21 +14619,21 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>663368</v>
+        <v>666152</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Blake Perkins</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Perkins</t>
+          <t>Hamilton</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -14659,61 +14655,61 @@
         <v>8</v>
       </c>
       <c r="L132" t="n">
-        <v>3.824</v>
+        <v>3.594</v>
       </c>
       <c r="M132" t="n">
-        <v>3.292</v>
+        <v>3.155</v>
       </c>
       <c r="N132" t="n">
-        <v>0.699</v>
+        <v>0.675</v>
       </c>
       <c r="O132" t="n">
-        <v>1.104</v>
+        <v>1.169</v>
       </c>
       <c r="P132" t="n">
-        <v>0.835</v>
+        <v>0.651</v>
       </c>
       <c r="Q132" t="n">
-        <v>0.451</v>
+        <v>0.362</v>
       </c>
       <c r="R132" t="n">
-        <v>0.466</v>
+        <v>0.41</v>
       </c>
       <c r="S132" t="n">
-        <v>0.144</v>
+        <v>0.145</v>
       </c>
       <c r="T132" t="n">
-        <v>0.007</v>
+        <v>0.012</v>
       </c>
       <c r="U132" t="n">
-        <v>0.082</v>
+        <v>0.108</v>
       </c>
       <c r="V132" t="n">
-        <v>0.398</v>
+        <v>0.436</v>
       </c>
       <c r="W132" t="n">
-        <v>0.427</v>
+        <v>0.433</v>
       </c>
       <c r="X132" t="n">
-        <v>0.18</v>
+        <v>0.388</v>
       </c>
       <c r="Y132" t="n">
-        <v>0.146</v>
+        <v>0.32</v>
       </c>
       <c r="Z132" t="n">
-        <v>6.277</v>
+        <v>7.194</v>
       </c>
       <c r="AA132" t="n">
-        <v>8.298</v>
+        <v>9.423</v>
       </c>
       <c r="AB132" t="n">
-        <v>0.081</v>
+        <v>0.102</v>
       </c>
       <c r="AC132" t="n">
-        <v>0.527</v>
+        <v>0.506</v>
       </c>
       <c r="AD132" t="n">
-        <v>0.138</v>
+        <v>0.276</v>
       </c>
     </row>
     <row r="133">
@@ -14731,16 +14727,16 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>666152</v>
+        <v>668930</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Hamilton</t>
+          <t>Turang</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -14764,64 +14760,64 @@
         </is>
       </c>
       <c r="K133" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L133" t="n">
-        <v>3.695</v>
+        <v>4.59</v>
       </c>
       <c r="M133" t="n">
-        <v>3.241</v>
+        <v>3.821</v>
       </c>
       <c r="N133" t="n">
-        <v>0.673</v>
+        <v>0.854</v>
       </c>
       <c r="O133" t="n">
-        <v>1.181</v>
+        <v>1.469</v>
       </c>
       <c r="P133" t="n">
-        <v>0.675</v>
+        <v>0.97</v>
       </c>
       <c r="Q133" t="n">
-        <v>0.368</v>
+        <v>0.67</v>
       </c>
       <c r="R133" t="n">
-        <v>0.404</v>
+        <v>0.523</v>
       </c>
       <c r="S133" t="n">
-        <v>0.146</v>
+        <v>0.18</v>
       </c>
       <c r="T133" t="n">
-        <v>0.007</v>
+        <v>0.018</v>
       </c>
       <c r="U133" t="n">
-        <v>0.116</v>
+        <v>0.133</v>
       </c>
       <c r="V133" t="n">
-        <v>0.432</v>
+        <v>0.45</v>
       </c>
       <c r="W133" t="n">
-        <v>0.411</v>
+        <v>0.642</v>
       </c>
       <c r="X133" t="n">
-        <v>0.39</v>
+        <v>0.299</v>
       </c>
       <c r="Y133" t="n">
-        <v>0.319</v>
+        <v>0.252</v>
       </c>
       <c r="Z133" t="n">
-        <v>7.175</v>
+        <v>8.728</v>
       </c>
       <c r="AA133" t="n">
-        <v>9.388</v>
+        <v>11.558</v>
       </c>
       <c r="AB133" t="n">
-        <v>0.112</v>
+        <v>0.124</v>
       </c>
       <c r="AC133" t="n">
-        <v>0.517</v>
+        <v>0.595</v>
       </c>
       <c r="AD133" t="n">
-        <v>0.282</v>
+        <v>0.224</v>
       </c>
     </row>
     <row r="134">
@@ -14839,16 +14835,16 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>668930</v>
+        <v>669003</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Turang</t>
+          <t>Mitchell</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -14872,64 +14868,64 @@
         </is>
       </c>
       <c r="K134" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L134" t="n">
-        <v>4.571</v>
+        <v>4.155</v>
       </c>
       <c r="M134" t="n">
-        <v>3.819</v>
+        <v>3.513</v>
       </c>
       <c r="N134" t="n">
-        <v>0.854</v>
+        <v>0.697</v>
       </c>
       <c r="O134" t="n">
-        <v>1.474</v>
+        <v>1.246</v>
       </c>
       <c r="P134" t="n">
-        <v>0.976</v>
+        <v>1.361</v>
       </c>
       <c r="Q134" t="n">
-        <v>0.642</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="R134" t="n">
-        <v>0.522</v>
+        <v>0.41</v>
       </c>
       <c r="S134" t="n">
-        <v>0.177</v>
+        <v>0.151</v>
       </c>
       <c r="T134" t="n">
-        <v>0.021</v>
+        <v>0.011</v>
       </c>
       <c r="U134" t="n">
-        <v>0.134</v>
+        <v>0.126</v>
       </c>
       <c r="V134" t="n">
-        <v>0.449</v>
+        <v>0.489</v>
       </c>
       <c r="W134" t="n">
-        <v>0.656</v>
+        <v>0.49</v>
       </c>
       <c r="X134" t="n">
-        <v>0.295</v>
+        <v>0.265</v>
       </c>
       <c r="Y134" t="n">
-        <v>0.245</v>
+        <v>0.214</v>
       </c>
       <c r="Z134" t="n">
-        <v>8.678000000000001</v>
+        <v>7.479</v>
       </c>
       <c r="AA134" t="n">
-        <v>11.492</v>
+        <v>9.99</v>
       </c>
       <c r="AB134" t="n">
-        <v>0.127</v>
+        <v>0.12</v>
       </c>
       <c r="AC134" t="n">
-        <v>0.601</v>
+        <v>0.528</v>
       </c>
       <c r="AD134" t="n">
-        <v>0.223</v>
+        <v>0.195</v>
       </c>
     </row>
     <row r="135">
@@ -14947,16 +14943,16 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>669003</v>
+        <v>671277</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Luis Garcia</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mitchell</t>
+          <t>Garcia</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -14966,78 +14962,78 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
+          <t>WAS</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>WAS</t>
-        </is>
-      </c>
       <c r="K135" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L135" t="n">
-        <v>4.047</v>
+        <v>4.555</v>
       </c>
       <c r="M135" t="n">
-        <v>3.428</v>
+        <v>4.253</v>
       </c>
       <c r="N135" t="n">
-        <v>0.699</v>
+        <v>1.01</v>
       </c>
       <c r="O135" t="n">
-        <v>1.228</v>
+        <v>1.778</v>
       </c>
       <c r="P135" t="n">
-        <v>1.332</v>
+        <v>0.928</v>
       </c>
       <c r="Q135" t="n">
-        <v>0.537</v>
+        <v>0.205</v>
       </c>
       <c r="R135" t="n">
-        <v>0.421</v>
+        <v>0.637</v>
       </c>
       <c r="S135" t="n">
-        <v>0.147</v>
+        <v>0.167</v>
       </c>
       <c r="T135" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.015</v>
       </c>
       <c r="U135" t="n">
-        <v>0.122</v>
+        <v>0.191</v>
       </c>
       <c r="V135" t="n">
-        <v>0.495</v>
+        <v>0.52</v>
       </c>
       <c r="W135" t="n">
-        <v>0.456</v>
+        <v>0.491</v>
       </c>
       <c r="X135" t="n">
-        <v>0.259</v>
+        <v>0.118</v>
       </c>
       <c r="Y135" t="n">
-        <v>0.207</v>
+        <v>0.094</v>
       </c>
       <c r="Z135" t="n">
-        <v>7.297</v>
+        <v>7.674</v>
       </c>
       <c r="AA135" t="n">
-        <v>9.73</v>
+        <v>9.904999999999999</v>
       </c>
       <c r="AB135" t="n">
-        <v>0.118</v>
+        <v>0.178</v>
       </c>
       <c r="AC135" t="n">
-        <v>0.529</v>
+        <v>0.654</v>
       </c>
       <c r="AD135" t="n">
-        <v>0.192</v>
+        <v>0.092</v>
       </c>
     </row>
     <row r="136">
@@ -15055,16 +15051,16 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>671277</v>
+        <v>678391</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Luis Garcia</t>
+          <t>Jorbit Vivas</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garcia</t>
+          <t>Vivas</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -15088,64 +15084,64 @@
         </is>
       </c>
       <c r="K136" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L136" t="n">
-        <v>4.517</v>
+        <v>3.914</v>
       </c>
       <c r="M136" t="n">
-        <v>4.206</v>
+        <v>3.57</v>
       </c>
       <c r="N136" t="n">
-        <v>1.018</v>
+        <v>0.719</v>
       </c>
       <c r="O136" t="n">
-        <v>1.812</v>
+        <v>1.139</v>
       </c>
       <c r="P136" t="n">
-        <v>0.905</v>
+        <v>0.959</v>
       </c>
       <c r="Q136" t="n">
-        <v>0.203</v>
+        <v>0.256</v>
       </c>
       <c r="R136" t="n">
-        <v>0.624</v>
+        <v>0.489</v>
       </c>
       <c r="S136" t="n">
-        <v>0.185</v>
+        <v>0.135</v>
       </c>
       <c r="T136" t="n">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="U136" t="n">
-        <v>0.191</v>
+        <v>0.095</v>
       </c>
       <c r="V136" t="n">
-        <v>0.534</v>
+        <v>0.371</v>
       </c>
       <c r="W136" t="n">
-        <v>0.511</v>
+        <v>0.32</v>
       </c>
       <c r="X136" t="n">
-        <v>0.118</v>
+        <v>0.025</v>
       </c>
       <c r="Y136" t="n">
-        <v>0.097</v>
+        <v>0.018</v>
       </c>
       <c r="Z136" t="n">
-        <v>7.832</v>
+        <v>5.08</v>
       </c>
       <c r="AA136" t="n">
-        <v>10.131</v>
+        <v>6.621</v>
       </c>
       <c r="AB136" t="n">
-        <v>0.176</v>
+        <v>0.091</v>
       </c>
       <c r="AC136" t="n">
-        <v>0.676</v>
+        <v>0.541</v>
       </c>
       <c r="AD136" t="n">
-        <v>0.093</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="137">
@@ -15163,16 +15159,16 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>677588</v>
+        <v>682928</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Jose Tena</t>
+          <t>C.J. Abrams</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tena</t>
+          <t>Abrams</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -15196,64 +15192,64 @@
         </is>
       </c>
       <c r="K137" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L137" t="n">
-        <v>3.833</v>
+        <v>4.176</v>
       </c>
       <c r="M137" t="n">
-        <v>3.427</v>
+        <v>3.755</v>
       </c>
       <c r="N137" t="n">
-        <v>0.676</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="O137" t="n">
-        <v>1.064</v>
+        <v>1.383</v>
       </c>
       <c r="P137" t="n">
-        <v>1.182</v>
+        <v>0.982</v>
       </c>
       <c r="Q137" t="n">
-        <v>0.336</v>
+        <v>0.325</v>
       </c>
       <c r="R137" t="n">
-        <v>0.464</v>
+        <v>0.527</v>
       </c>
       <c r="S137" t="n">
-        <v>0.116</v>
+        <v>0.134</v>
       </c>
       <c r="T137" t="n">
-        <v>0.015</v>
+        <v>0.023</v>
       </c>
       <c r="U137" t="n">
-        <v>0.081</v>
+        <v>0.13</v>
       </c>
       <c r="V137" t="n">
-        <v>0.325</v>
+        <v>0.412</v>
       </c>
       <c r="W137" t="n">
-        <v>0.318</v>
+        <v>0.426</v>
       </c>
       <c r="X137" t="n">
-        <v>0.132</v>
+        <v>0.243</v>
       </c>
       <c r="Y137" t="n">
-        <v>0.107</v>
+        <v>0.201</v>
       </c>
       <c r="Z137" t="n">
-        <v>5.392</v>
+        <v>7.063</v>
       </c>
       <c r="AA137" t="n">
-        <v>6.996</v>
+        <v>9.134</v>
       </c>
       <c r="AB137" t="n">
-        <v>0.077</v>
+        <v>0.124</v>
       </c>
       <c r="AC137" t="n">
-        <v>0.509</v>
+        <v>0.59</v>
       </c>
       <c r="AD137" t="n">
-        <v>0.102</v>
+        <v>0.182</v>
       </c>
     </row>
     <row r="138">
@@ -15271,21 +15267,21 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>682928</v>
+        <v>683083</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>C.J. Abrams</t>
+          <t>Nasim Nunez</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Abrams</t>
+          <t>Nunez</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -15304,64 +15300,64 @@
         </is>
       </c>
       <c r="K138" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L138" t="n">
-        <v>4.18</v>
+        <v>3.538</v>
       </c>
       <c r="M138" t="n">
-        <v>3.754</v>
+        <v>3.147</v>
       </c>
       <c r="N138" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.546</v>
       </c>
       <c r="O138" t="n">
-        <v>1.426</v>
+        <v>0.863</v>
       </c>
       <c r="P138" t="n">
-        <v>1.009</v>
+        <v>0.974</v>
       </c>
       <c r="Q138" t="n">
-        <v>0.327</v>
+        <v>0.319</v>
       </c>
       <c r="R138" t="n">
-        <v>0.506</v>
+        <v>0.363</v>
       </c>
       <c r="S138" t="n">
-        <v>0.147</v>
+        <v>0.117</v>
       </c>
       <c r="T138" t="n">
-        <v>0.027</v>
+        <v>0</v>
       </c>
       <c r="U138" t="n">
-        <v>0.137</v>
+        <v>0.067</v>
       </c>
       <c r="V138" t="n">
-        <v>0.443</v>
+        <v>0.261</v>
       </c>
       <c r="W138" t="n">
-        <v>0.417</v>
+        <v>0.314</v>
       </c>
       <c r="X138" t="n">
-        <v>0.243</v>
+        <v>0.292</v>
       </c>
       <c r="Y138" t="n">
-        <v>0.197</v>
+        <v>0.238</v>
       </c>
       <c r="Z138" t="n">
-        <v>7.187</v>
+        <v>5.316</v>
       </c>
       <c r="AA138" t="n">
-        <v>9.321999999999999</v>
+        <v>6.891</v>
       </c>
       <c r="AB138" t="n">
-        <v>0.13</v>
+        <v>0.065</v>
       </c>
       <c r="AC138" t="n">
-        <v>0.588</v>
+        <v>0.433</v>
       </c>
       <c r="AD138" t="n">
-        <v>0.182</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="139">
@@ -15379,97 +15375,97 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>683083</v>
+        <v>686217</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Nasim Nunez</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Nunez</t>
+          <t>Frelick</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
           <t>WAS</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>MIL</t>
         </is>
       </c>
       <c r="K139" t="n">
         <v>6</v>
       </c>
       <c r="L139" t="n">
-        <v>4.005</v>
+        <v>4.099</v>
       </c>
       <c r="M139" t="n">
         <v>3.571</v>
       </c>
       <c r="N139" t="n">
-        <v>0.65</v>
+        <v>0.883</v>
       </c>
       <c r="O139" t="n">
-        <v>1.058</v>
+        <v>1.383</v>
       </c>
       <c r="P139" t="n">
-        <v>1.052</v>
+        <v>0.528</v>
       </c>
       <c r="Q139" t="n">
-        <v>0.356</v>
+        <v>0.435</v>
       </c>
       <c r="R139" t="n">
-        <v>0.418</v>
+        <v>0.581</v>
       </c>
       <c r="S139" t="n">
-        <v>0.145</v>
+        <v>0.193</v>
       </c>
       <c r="T139" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="U139" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="V139" t="n">
-        <v>0.322</v>
+        <v>0.472</v>
       </c>
       <c r="W139" t="n">
-        <v>0.359</v>
+        <v>0.451</v>
       </c>
       <c r="X139" t="n">
-        <v>0.314</v>
+        <v>0.123</v>
       </c>
       <c r="Y139" t="n">
-        <v>0.257</v>
+        <v>0.099</v>
       </c>
       <c r="Z139" t="n">
-        <v>6.215</v>
+        <v>6.969</v>
       </c>
       <c r="AA139" t="n">
-        <v>8.061999999999999</v>
+        <v>9.144</v>
       </c>
       <c r="AB139" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AC139" t="n">
-        <v>0.498</v>
+        <v>0.617</v>
       </c>
       <c r="AD139" t="n">
-        <v>0.232</v>
+        <v>0.096</v>
       </c>
     </row>
     <row r="140">
@@ -15487,97 +15483,97 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>686217</v>
+        <v>686452</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Sal Frelick</t>
+          <t>Drew Millas</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Frelick</t>
+          <t>Millas</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
+          <t>WAS</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>WAS</t>
-        </is>
-      </c>
       <c r="K140" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L140" t="n">
-        <v>4.068</v>
+        <v>3.728</v>
       </c>
       <c r="M140" t="n">
-        <v>3.548</v>
+        <v>3.315</v>
       </c>
       <c r="N140" t="n">
-        <v>0.871</v>
+        <v>0.711</v>
       </c>
       <c r="O140" t="n">
-        <v>1.358</v>
+        <v>1.01</v>
       </c>
       <c r="P140" t="n">
-        <v>0.539</v>
+        <v>0.795</v>
       </c>
       <c r="Q140" t="n">
-        <v>0.428</v>
+        <v>0.334</v>
       </c>
       <c r="R140" t="n">
-        <v>0.575</v>
+        <v>0.517</v>
       </c>
       <c r="S140" t="n">
-        <v>0.193</v>
+        <v>0.141</v>
       </c>
       <c r="T140" t="n">
-        <v>0.017</v>
+        <v>0.003</v>
       </c>
       <c r="U140" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.05</v>
       </c>
       <c r="V140" t="n">
-        <v>0.488</v>
+        <v>0.278</v>
       </c>
       <c r="W140" t="n">
-        <v>0.441</v>
+        <v>0.313</v>
       </c>
       <c r="X140" t="n">
-        <v>0.131</v>
+        <v>0.176</v>
       </c>
       <c r="Y140" t="n">
-        <v>0.108</v>
+        <v>0.142</v>
       </c>
       <c r="Z140" t="n">
-        <v>6.946</v>
+        <v>5.347</v>
       </c>
       <c r="AA140" t="n">
-        <v>9.127000000000001</v>
+        <v>6.861</v>
       </c>
       <c r="AB140" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.049</v>
       </c>
       <c r="AC140" t="n">
-        <v>0.616</v>
+        <v>0.524</v>
       </c>
       <c r="AD140" t="n">
-        <v>0.101</v>
+        <v>0.133</v>
       </c>
     </row>
     <row r="141">
@@ -15631,61 +15627,61 @@
         <v>9</v>
       </c>
       <c r="L141" t="n">
-        <v>3.523</v>
+        <v>3.511</v>
       </c>
       <c r="M141" t="n">
-        <v>3.185</v>
+        <v>3.19</v>
       </c>
       <c r="N141" t="n">
-        <v>0.793</v>
+        <v>0.788</v>
       </c>
       <c r="O141" t="n">
-        <v>1.108</v>
+        <v>1.107</v>
       </c>
       <c r="P141" t="n">
-        <v>0.432</v>
+        <v>0.448</v>
       </c>
       <c r="Q141" t="n">
-        <v>0.241</v>
+        <v>0.24</v>
       </c>
       <c r="R141" t="n">
-        <v>0.578</v>
+        <v>0.572</v>
       </c>
       <c r="S141" t="n">
-        <v>0.157</v>
+        <v>0.156</v>
       </c>
       <c r="T141" t="n">
-        <v>0.016</v>
+        <v>0.018</v>
       </c>
       <c r="U141" t="n">
         <v>0.042</v>
       </c>
       <c r="V141" t="n">
-        <v>0.352</v>
+        <v>0.358</v>
       </c>
       <c r="W141" t="n">
-        <v>0.384</v>
+        <v>0.395</v>
       </c>
       <c r="X141" t="n">
-        <v>0.119</v>
+        <v>0.113</v>
       </c>
       <c r="Y141" t="n">
-        <v>0.095</v>
+        <v>0.09</v>
       </c>
       <c r="Z141" t="n">
-        <v>5.493</v>
+        <v>5.497</v>
       </c>
       <c r="AA141" t="n">
-        <v>7.074</v>
+        <v>7.096</v>
       </c>
       <c r="AB141" t="n">
         <v>0.041</v>
       </c>
       <c r="AC141" t="n">
-        <v>0.573</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="AD141" t="n">
-        <v>0.092</v>
+        <v>0.08699999999999999</v>
       </c>
     </row>
     <row r="142">
@@ -15739,61 +15735,61 @@
         <v>3</v>
       </c>
       <c r="L142" t="n">
-        <v>4.306</v>
+        <v>4.317</v>
       </c>
       <c r="M142" t="n">
-        <v>3.964</v>
+        <v>3.939</v>
       </c>
       <c r="N142" t="n">
-        <v>0.788</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="O142" t="n">
-        <v>1.263</v>
+        <v>1.332</v>
       </c>
       <c r="P142" t="n">
-        <v>1.316</v>
+        <v>1.274</v>
       </c>
       <c r="Q142" t="n">
-        <v>0.254</v>
+        <v>0.282</v>
       </c>
       <c r="R142" t="n">
-        <v>0.532</v>
+        <v>0.542</v>
       </c>
       <c r="S142" t="n">
-        <v>0.147</v>
+        <v>0.15</v>
       </c>
       <c r="T142" t="n">
         <v>0</v>
       </c>
       <c r="U142" t="n">
-        <v>0.109</v>
+        <v>0.123</v>
       </c>
       <c r="V142" t="n">
-        <v>0.376</v>
+        <v>0.408</v>
       </c>
       <c r="W142" t="n">
-        <v>0.388</v>
+        <v>0.39</v>
       </c>
       <c r="X142" t="n">
-        <v>0.091</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="Y142" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="Z142" t="n">
-        <v>5.819</v>
+        <v>6.108</v>
       </c>
       <c r="AA142" t="n">
-        <v>7.54</v>
+        <v>7.934</v>
       </c>
       <c r="AB142" t="n">
-        <v>0.104</v>
+        <v>0.117</v>
       </c>
       <c r="AC142" t="n">
-        <v>0.571</v>
+        <v>0.578</v>
       </c>
       <c r="AD142" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.067</v>
       </c>
     </row>
     <row r="143">
@@ -15847,61 +15843,61 @@
         <v>1</v>
       </c>
       <c r="L143" t="n">
-        <v>4.552</v>
+        <v>4.568</v>
       </c>
       <c r="M143" t="n">
-        <v>3.858</v>
+        <v>3.866</v>
       </c>
       <c r="N143" t="n">
-        <v>0.791</v>
+        <v>0.822</v>
       </c>
       <c r="O143" t="n">
-        <v>1.436</v>
+        <v>1.516</v>
       </c>
       <c r="P143" t="n">
-        <v>1.476</v>
+        <v>1.422</v>
       </c>
       <c r="Q143" t="n">
-        <v>0.606</v>
+        <v>0.612</v>
       </c>
       <c r="R143" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="S143" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.164</v>
+      </c>
+      <c r="Y143" t="n">
         <v>0.14</v>
       </c>
-      <c r="T143" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="U143" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="V143" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="W143" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="X143" t="n">
-        <v>0.159</v>
-      </c>
-      <c r="Y143" t="n">
-        <v>0.132</v>
-      </c>
       <c r="Z143" t="n">
-        <v>7.584</v>
+        <v>7.992</v>
       </c>
       <c r="AA143" t="n">
-        <v>10.045</v>
+        <v>10.6</v>
       </c>
       <c r="AB143" t="n">
-        <v>0.155</v>
+        <v>0.166</v>
       </c>
       <c r="AC143" t="n">
-        <v>0.577</v>
+        <v>0.578</v>
       </c>
       <c r="AD143" t="n">
-        <v>0.128</v>
+        <v>0.133</v>
       </c>
     </row>
     <row r="144">
@@ -15955,61 +15951,61 @@
         <v>4</v>
       </c>
       <c r="L144" t="n">
-        <v>4.25</v>
+        <v>4.295</v>
       </c>
       <c r="M144" t="n">
-        <v>3.884</v>
+        <v>3.923</v>
       </c>
       <c r="N144" t="n">
-        <v>0.917</v>
+        <v>0.911</v>
       </c>
       <c r="O144" t="n">
-        <v>1.495</v>
+        <v>1.487</v>
       </c>
       <c r="P144" t="n">
-        <v>0.828</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="Q144" t="n">
-        <v>0.267</v>
+        <v>0.26</v>
       </c>
       <c r="R144" t="n">
-        <v>0.616</v>
+        <v>0.606</v>
       </c>
       <c r="S144" t="n">
-        <v>0.145</v>
+        <v>0.151</v>
       </c>
       <c r="T144" t="n">
-        <v>0.036</v>
+        <v>0.038</v>
       </c>
       <c r="U144" t="n">
-        <v>0.12</v>
+        <v>0.117</v>
       </c>
       <c r="V144" t="n">
-        <v>0.444</v>
+        <v>0.426</v>
       </c>
       <c r="W144" t="n">
-        <v>0.419</v>
+        <v>0.42</v>
       </c>
       <c r="X144" t="n">
-        <v>0.104</v>
+        <v>0.112</v>
       </c>
       <c r="Y144" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="Z144" t="n">
-        <v>6.767</v>
+        <v>6.705</v>
       </c>
       <c r="AA144" t="n">
-        <v>8.712999999999999</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="AB144" t="n">
-        <v>0.115</v>
+        <v>0.111</v>
       </c>
       <c r="AC144" t="n">
         <v>0.626</v>
       </c>
       <c r="AD144" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08599999999999999</v>
       </c>
     </row>
     <row r="145">
@@ -16060,64 +16056,64 @@
         </is>
       </c>
       <c r="K145" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L145" t="n">
-        <v>3.417</v>
+        <v>3.782</v>
       </c>
       <c r="M145" t="n">
-        <v>3.121</v>
+        <v>3.449</v>
       </c>
       <c r="N145" t="n">
-        <v>0.717</v>
+        <v>0.758</v>
       </c>
       <c r="O145" t="n">
-        <v>1.027</v>
+        <v>1.102</v>
       </c>
       <c r="P145" t="n">
-        <v>0.694</v>
+        <v>0.792</v>
       </c>
       <c r="Q145" t="n">
-        <v>0.221</v>
+        <v>0.252</v>
       </c>
       <c r="R145" t="n">
-        <v>0.503</v>
+        <v>0.534</v>
       </c>
       <c r="S145" t="n">
-        <v>0.161</v>
+        <v>0.159</v>
       </c>
       <c r="T145" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
       <c r="U145" t="n">
-        <v>0.045</v>
+        <v>0.055</v>
       </c>
       <c r="V145" t="n">
-        <v>0.267</v>
+        <v>0.299</v>
       </c>
       <c r="W145" t="n">
-        <v>0.317</v>
+        <v>0.325</v>
       </c>
       <c r="X145" t="n">
-        <v>0.229</v>
+        <v>0.274</v>
       </c>
       <c r="Y145" t="n">
-        <v>0.188</v>
+        <v>0.23</v>
       </c>
       <c r="Z145" t="n">
-        <v>5.373</v>
+        <v>5.927</v>
       </c>
       <c r="AA145" t="n">
-        <v>6.82</v>
+        <v>7.525</v>
       </c>
       <c r="AB145" t="n">
-        <v>0.044</v>
+        <v>0.054</v>
       </c>
       <c r="AC145" t="n">
-        <v>0.533</v>
+        <v>0.556</v>
       </c>
       <c r="AD145" t="n">
-        <v>0.172</v>
+        <v>0.208</v>
       </c>
     </row>
     <row r="146">
@@ -25891,61 +25887,61 @@
         <v>2</v>
       </c>
       <c r="L236" t="n">
-        <v>4.439</v>
+        <v>4.482</v>
       </c>
       <c r="M236" t="n">
-        <v>3.586</v>
+        <v>3.608</v>
       </c>
       <c r="N236" t="n">
-        <v>0.819</v>
+        <v>0.848</v>
       </c>
       <c r="O236" t="n">
-        <v>1.185</v>
+        <v>1.263</v>
       </c>
       <c r="P236" t="n">
-        <v>0.752</v>
+        <v>0.745</v>
       </c>
       <c r="Q236" t="n">
-        <v>0.753</v>
+        <v>0.772</v>
       </c>
       <c r="R236" t="n">
-        <v>0.579</v>
+        <v>0.589</v>
       </c>
       <c r="S236" t="n">
-        <v>0.172</v>
+        <v>0.176</v>
       </c>
       <c r="T236" t="n">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
       <c r="U236" t="n">
-        <v>0.057</v>
+        <v>0.073</v>
       </c>
       <c r="V236" t="n">
-        <v>0.398</v>
+        <v>0.394</v>
       </c>
       <c r="W236" t="n">
-        <v>0.531</v>
+        <v>0.555</v>
       </c>
       <c r="X236" t="n">
-        <v>0.059</v>
+        <v>0.053</v>
       </c>
       <c r="Y236" t="n">
-        <v>0.046</v>
+        <v>0.042</v>
       </c>
       <c r="Z236" t="n">
-        <v>6.853</v>
+        <v>7.11</v>
       </c>
       <c r="AA236" t="n">
-        <v>9.183999999999999</v>
+        <v>9.513</v>
       </c>
       <c r="AB236" t="n">
-        <v>0.057</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AC236" t="n">
-        <v>0.581</v>
+        <v>0.598</v>
       </c>
       <c r="AD236" t="n">
-        <v>0.045</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="237">
@@ -25999,61 +25995,61 @@
         <v>3</v>
       </c>
       <c r="L237" t="n">
-        <v>4.424</v>
+        <v>4.41</v>
       </c>
       <c r="M237" t="n">
-        <v>3.831</v>
+        <v>3.822</v>
       </c>
       <c r="N237" t="n">
-        <v>1.032</v>
+        <v>1.064</v>
       </c>
       <c r="O237" t="n">
-        <v>1.579</v>
+        <v>1.62</v>
       </c>
       <c r="P237" t="n">
-        <v>0.857</v>
+        <v>0.828</v>
       </c>
       <c r="Q237" t="n">
-        <v>0.496</v>
+        <v>0.495</v>
       </c>
       <c r="R237" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.714</v>
       </c>
       <c r="S237" t="n">
-        <v>0.248</v>
+        <v>0.244</v>
       </c>
       <c r="T237" t="n">
-        <v>0.008</v>
+        <v>0.004</v>
       </c>
       <c r="U237" t="n">
-        <v>0.095</v>
+        <v>0.101</v>
       </c>
       <c r="V237" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.554</v>
       </c>
       <c r="W237" t="n">
-        <v>0.488</v>
+        <v>0.494</v>
       </c>
       <c r="X237" t="n">
-        <v>0.048</v>
+        <v>0.051</v>
       </c>
       <c r="Y237" t="n">
         <v>0.039</v>
       </c>
       <c r="Z237" t="n">
-        <v>7.573</v>
+        <v>7.693</v>
       </c>
       <c r="AA237" t="n">
-        <v>9.977</v>
+        <v>10.102</v>
       </c>
       <c r="AB237" t="n">
-        <v>0.091</v>
+        <v>0.099</v>
       </c>
       <c r="AC237" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="AD237" t="n">
-        <v>0.039</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="238">
@@ -26071,16 +26067,16 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>641933</v>
+        <v>642715</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Tyler O'Neill</t>
+          <t>Willy Adames</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>O'Neill</t>
+          <t>Adames</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -26090,78 +26086,78 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
+          <t xml:space="preserve">SF </t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
           <t>BAL</t>
         </is>
       </c>
-      <c r="J238" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SF </t>
-        </is>
-      </c>
       <c r="K238" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L238" t="n">
-        <v>4.17</v>
+        <v>4.877</v>
       </c>
       <c r="M238" t="n">
-        <v>3.537</v>
+        <v>4.039</v>
       </c>
       <c r="N238" t="n">
-        <v>0.871</v>
+        <v>0.879</v>
       </c>
       <c r="O238" t="n">
-        <v>1.355</v>
+        <v>1.44</v>
       </c>
       <c r="P238" t="n">
-        <v>0.885</v>
+        <v>1.126</v>
       </c>
       <c r="Q238" t="n">
-        <v>0.544</v>
+        <v>0.738</v>
       </c>
       <c r="R238" t="n">
-        <v>0.588</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="S238" t="n">
-        <v>0.18</v>
+        <v>0.189</v>
       </c>
       <c r="T238" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="U238" t="n">
-        <v>0.098</v>
+        <v>0.121</v>
       </c>
       <c r="V238" t="n">
-        <v>0.481</v>
+        <v>0.392</v>
       </c>
       <c r="W238" t="n">
-        <v>0.483</v>
+        <v>0.649</v>
       </c>
       <c r="X238" t="n">
-        <v>0.11</v>
+        <v>0.101</v>
       </c>
       <c r="Y238" t="n">
-        <v>0.091</v>
+        <v>0.08</v>
       </c>
       <c r="Z238" t="n">
-        <v>7.155</v>
+        <v>7.842</v>
       </c>
       <c r="AA238" t="n">
-        <v>9.472</v>
+        <v>10.463</v>
       </c>
       <c r="AB238" t="n">
-        <v>0.094</v>
+        <v>0.116</v>
       </c>
       <c r="AC238" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="AD238" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.075</v>
       </c>
     </row>
     <row r="239">
@@ -26179,21 +26175,21 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>642715</v>
+        <v>646240</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Willy Adames</t>
+          <t>Rafael Devers</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Adames</t>
+          <t>Devers</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -26212,64 +26208,64 @@
         </is>
       </c>
       <c r="K239" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L239" t="n">
-        <v>4.847</v>
+        <v>4.7</v>
       </c>
       <c r="M239" t="n">
-        <v>4.001</v>
+        <v>3.992</v>
       </c>
       <c r="N239" t="n">
-        <v>0.84</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="O239" t="n">
-        <v>1.348</v>
+        <v>1.657</v>
       </c>
       <c r="P239" t="n">
-        <v>1.102</v>
+        <v>1.14</v>
       </c>
       <c r="Q239" t="n">
-        <v>0.75</v>
+        <v>0.614</v>
       </c>
       <c r="R239" t="n">
-        <v>0.551</v>
+        <v>0.597</v>
       </c>
       <c r="S239" t="n">
-        <v>0.177</v>
+        <v>0.16</v>
       </c>
       <c r="T239" t="n">
-        <v>0.004</v>
+        <v>0.007</v>
       </c>
       <c r="U239" t="n">
-        <v>0.107</v>
+        <v>0.18</v>
       </c>
       <c r="V239" t="n">
-        <v>0.393</v>
+        <v>0.521</v>
       </c>
       <c r="W239" t="n">
-        <v>0.609</v>
+        <v>0.618</v>
       </c>
       <c r="X239" t="n">
-        <v>0.101</v>
+        <v>0.049</v>
       </c>
       <c r="Y239" t="n">
-        <v>0.079</v>
+        <v>0.039</v>
       </c>
       <c r="Z239" t="n">
-        <v>7.546</v>
+        <v>8.144</v>
       </c>
       <c r="AA239" t="n">
-        <v>10.091</v>
+        <v>10.846</v>
       </c>
       <c r="AB239" t="n">
-        <v>0.103</v>
+        <v>0.162</v>
       </c>
       <c r="AC239" t="n">
-        <v>0.592</v>
+        <v>0.638</v>
       </c>
       <c r="AD239" t="n">
-        <v>0.075</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="240">
@@ -26287,21 +26283,21 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>646240</v>
+        <v>656305</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Rafael Devers</t>
+          <t>Matt Chapman</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Devers</t>
+          <t>Chapman</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -26320,64 +26316,64 @@
         </is>
       </c>
       <c r="K240" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L240" t="n">
-        <v>4.385</v>
+        <v>4.614</v>
       </c>
       <c r="M240" t="n">
-        <v>3.711</v>
+        <v>3.842</v>
       </c>
       <c r="N240" t="n">
-        <v>0.881</v>
+        <v>1.003</v>
       </c>
       <c r="O240" t="n">
-        <v>1.539</v>
+        <v>1.413</v>
       </c>
       <c r="P240" t="n">
-        <v>1.035</v>
+        <v>0.856</v>
       </c>
       <c r="Q240" t="n">
-        <v>0.584</v>
+        <v>0.675</v>
       </c>
       <c r="R240" t="n">
-        <v>0.555</v>
+        <v>0.742</v>
       </c>
       <c r="S240" t="n">
-        <v>0.157</v>
+        <v>0.18</v>
       </c>
       <c r="T240" t="n">
-        <v>0.007</v>
+        <v>0.014</v>
       </c>
       <c r="U240" t="n">
-        <v>0.162</v>
+        <v>0.067</v>
       </c>
       <c r="V240" t="n">
-        <v>0.581</v>
+        <v>0.454</v>
       </c>
       <c r="W240" t="n">
-        <v>0.543</v>
+        <v>0.499</v>
       </c>
       <c r="X240" t="n">
-        <v>0.047</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="Y240" t="n">
-        <v>0.038</v>
+        <v>0.051</v>
       </c>
       <c r="Z240" t="n">
-        <v>7.733</v>
+        <v>7.42</v>
       </c>
       <c r="AA240" t="n">
-        <v>10.366</v>
+        <v>9.754</v>
       </c>
       <c r="AB240" t="n">
-        <v>0.153</v>
+        <v>0.065</v>
       </c>
       <c r="AC240" t="n">
-        <v>0.614</v>
+        <v>0.665</v>
       </c>
       <c r="AD240" t="n">
-        <v>0.037</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="241">
@@ -26395,97 +26391,97 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>650333</v>
+        <v>665750</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Luis Arraez</t>
+          <t>Leody Taveras</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Arraez</t>
+          <t>Taveras</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
           <t xml:space="preserve">SF </t>
         </is>
       </c>
-      <c r="J241" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
       <c r="K241" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L241" t="n">
-        <v>4.587</v>
+        <v>4.164</v>
       </c>
       <c r="M241" t="n">
-        <v>4.188</v>
+        <v>3.678</v>
       </c>
       <c r="N241" t="n">
-        <v>1.141</v>
+        <v>0.89</v>
       </c>
       <c r="O241" t="n">
-        <v>1.515</v>
+        <v>1.306</v>
       </c>
       <c r="P241" t="n">
-        <v>0.324</v>
+        <v>0.839</v>
       </c>
       <c r="Q241" t="n">
-        <v>0.284</v>
+        <v>0.39</v>
       </c>
       <c r="R241" t="n">
-        <v>0.879</v>
+        <v>0.632</v>
       </c>
       <c r="S241" t="n">
-        <v>0.195</v>
+        <v>0.168</v>
       </c>
       <c r="T241" t="n">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
       <c r="U241" t="n">
-        <v>0.044</v>
+        <v>0.068</v>
       </c>
       <c r="V241" t="n">
-        <v>0.49</v>
+        <v>0.431</v>
       </c>
       <c r="W241" t="n">
-        <v>0.446</v>
+        <v>0.442</v>
       </c>
       <c r="X241" t="n">
-        <v>0.06</v>
+        <v>0.231</v>
       </c>
       <c r="Y241" t="n">
-        <v>0.05</v>
+        <v>0.19</v>
       </c>
       <c r="Z241" t="n">
-        <v>6.93</v>
+        <v>7.068</v>
       </c>
       <c r="AA241" t="n">
-        <v>8.84</v>
+        <v>9.151</v>
       </c>
       <c r="AB241" t="n">
-        <v>0.043</v>
+        <v>0.066</v>
       </c>
       <c r="AC241" t="n">
-        <v>0.714</v>
+        <v>0.623</v>
       </c>
       <c r="AD241" t="n">
-        <v>0.05</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="242">
@@ -26503,16 +26499,16 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>656305</v>
+        <v>666464</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Matt Chapman</t>
+          <t>Jerar Encarnacion</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Chapman</t>
+          <t>Encarnacion</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -26536,64 +26532,64 @@
         </is>
       </c>
       <c r="K242" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L242" t="n">
-        <v>4.704</v>
+        <v>3.951</v>
       </c>
       <c r="M242" t="n">
-        <v>3.908</v>
+        <v>3.582</v>
       </c>
       <c r="N242" t="n">
-        <v>1.014</v>
+        <v>0.895</v>
       </c>
       <c r="O242" t="n">
-        <v>1.411</v>
+        <v>1.34</v>
       </c>
       <c r="P242" t="n">
-        <v>0.873</v>
+        <v>0.951</v>
       </c>
       <c r="Q242" t="n">
-        <v>0.697</v>
+        <v>0.284</v>
       </c>
       <c r="R242" t="n">
-        <v>0.754</v>
+        <v>0.625</v>
       </c>
       <c r="S242" t="n">
-        <v>0.184</v>
+        <v>0.183</v>
       </c>
       <c r="T242" t="n">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="U242" t="n">
-        <v>0.063</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="V242" t="n">
-        <v>0.402</v>
+        <v>0.418</v>
       </c>
       <c r="W242" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.39</v>
       </c>
       <c r="X242" t="n">
-        <v>0.074</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="Y242" t="n">
-        <v>0.054</v>
+        <v>0.068</v>
       </c>
       <c r="Z242" t="n">
-        <v>7.502</v>
+        <v>6.183</v>
       </c>
       <c r="AA242" t="n">
-        <v>9.851000000000001</v>
+        <v>7.986</v>
       </c>
       <c r="AB242" t="n">
-        <v>0.061</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AC242" t="n">
-        <v>0.658</v>
+        <v>0.62</v>
       </c>
       <c r="AD242" t="n">
-        <v>0.053</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="243">
@@ -26611,16 +26607,16 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>664056</v>
+        <v>669236</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Harrison Bader</t>
+          <t>Jeremiah Jackson</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Bader</t>
+          <t>Jackson</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
@@ -26630,78 +26626,78 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
           <t xml:space="preserve">SF </t>
         </is>
       </c>
-      <c r="J243" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
       <c r="K243" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L243" t="n">
-        <v>4.083</v>
+        <v>3.675</v>
       </c>
       <c r="M243" t="n">
-        <v>3.684</v>
+        <v>3.332</v>
       </c>
       <c r="N243" t="n">
-        <v>0.741</v>
+        <v>0.763</v>
       </c>
       <c r="O243" t="n">
-        <v>1.109</v>
+        <v>1.099</v>
       </c>
       <c r="P243" t="n">
-        <v>1.13</v>
+        <v>0.792</v>
       </c>
       <c r="Q243" t="n">
-        <v>0.313</v>
+        <v>0.254</v>
       </c>
       <c r="R243" t="n">
-        <v>0.512</v>
+        <v>0.542</v>
       </c>
       <c r="S243" t="n">
-        <v>0.153</v>
+        <v>0.16</v>
       </c>
       <c r="T243" t="n">
-        <v>0.016</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="U243" t="n">
-        <v>0.061</v>
+        <v>0.052</v>
       </c>
       <c r="V243" t="n">
-        <v>0.377</v>
+        <v>0.372</v>
       </c>
       <c r="W243" t="n">
-        <v>0.382</v>
+        <v>0.37</v>
       </c>
       <c r="X243" t="n">
-        <v>0.199</v>
+        <v>0.031</v>
       </c>
       <c r="Y243" t="n">
-        <v>0.157</v>
+        <v>0.025</v>
       </c>
       <c r="Z243" t="n">
-        <v>5.964</v>
+        <v>5.139</v>
       </c>
       <c r="AA243" t="n">
-        <v>7.748</v>
+        <v>6.694</v>
       </c>
       <c r="AB243" t="n">
-        <v>0.06</v>
+        <v>0.052</v>
       </c>
       <c r="AC243" t="n">
-        <v>0.551</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="AD243" t="n">
-        <v>0.145</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="244">
@@ -26719,16 +26715,16 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>666464</v>
+        <v>669477</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Jerar Encarnacion</t>
+          <t>Casey Schmitt</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Encarnacion</t>
+          <t>Schmitt</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -26752,64 +26748,64 @@
         </is>
       </c>
       <c r="K244" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L244" t="n">
-        <v>4.26</v>
+        <v>4.476</v>
       </c>
       <c r="M244" t="n">
-        <v>3.883</v>
+        <v>4.092</v>
       </c>
       <c r="N244" t="n">
-        <v>0.929</v>
+        <v>0.894</v>
       </c>
       <c r="O244" t="n">
-        <v>1.381</v>
+        <v>1.364</v>
       </c>
       <c r="P244" t="n">
-        <v>1.01</v>
+        <v>1.232</v>
       </c>
       <c r="Q244" t="n">
-        <v>0.284</v>
+        <v>0.297</v>
       </c>
       <c r="R244" t="n">
-        <v>0.647</v>
+        <v>0.583</v>
       </c>
       <c r="S244" t="n">
-        <v>0.197</v>
+        <v>0.228</v>
       </c>
       <c r="T244" t="n">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="U244" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.074</v>
       </c>
       <c r="V244" t="n">
-        <v>0.467</v>
+        <v>0.488</v>
       </c>
       <c r="W244" t="n">
-        <v>0.422</v>
+        <v>0.404</v>
       </c>
       <c r="X244" t="n">
-        <v>0.091</v>
+        <v>0.024</v>
       </c>
       <c r="Y244" t="n">
-        <v>0.067</v>
+        <v>0.018</v>
       </c>
       <c r="Z244" t="n">
-        <v>6.461</v>
+        <v>6.175</v>
       </c>
       <c r="AA244" t="n">
-        <v>8.387</v>
+        <v>8.093</v>
       </c>
       <c r="AB244" t="n">
-        <v>0.08</v>
+        <v>0.073</v>
       </c>
       <c r="AC244" t="n">
-        <v>0.632</v>
+        <v>0.62</v>
       </c>
       <c r="AD244" t="n">
-        <v>0.066</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="245">
@@ -26827,16 +26823,16 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>669236</v>
+        <v>671218</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Jeremiah Jackson</t>
+          <t>Heliot Ramos</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Jackson</t>
+          <t>Ramos</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -26846,78 +26842,78 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
+          <t xml:space="preserve">SF </t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
           <t>BAL</t>
         </is>
       </c>
-      <c r="J245" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SF </t>
-        </is>
-      </c>
       <c r="K245" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L245" t="n">
-        <v>3.977</v>
+        <v>4.237</v>
       </c>
       <c r="M245" t="n">
-        <v>3.63</v>
+        <v>3.802</v>
       </c>
       <c r="N245" t="n">
-        <v>0.841</v>
+        <v>0.869</v>
       </c>
       <c r="O245" t="n">
-        <v>1.215</v>
+        <v>1.338</v>
       </c>
       <c r="P245" t="n">
-        <v>0.856</v>
+        <v>1.02</v>
       </c>
       <c r="Q245" t="n">
-        <v>0.257</v>
+        <v>0.348</v>
       </c>
       <c r="R245" t="n">
-        <v>0.6</v>
+        <v>0.589</v>
       </c>
       <c r="S245" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="T245" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.013</v>
       </c>
       <c r="U245" t="n">
-        <v>0.062</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="V245" t="n">
-        <v>0.41</v>
+        <v>0.452</v>
       </c>
       <c r="W245" t="n">
-        <v>0.391</v>
+        <v>0.409</v>
       </c>
       <c r="X245" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Y245" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="Z245" t="n">
+        <v>6.232</v>
+      </c>
+      <c r="AA245" t="n">
+        <v>8.151</v>
+      </c>
+      <c r="AB245" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="AC245" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="AD245" t="n">
         <v>0.033</v>
-      </c>
-      <c r="Y245" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="Z245" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AA245" t="n">
-        <v>7.273</v>
-      </c>
-      <c r="AB245" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="AC245" t="n">
-        <v>0.598</v>
-      </c>
-      <c r="AD245" t="n">
-        <v>0.028</v>
       </c>
     </row>
     <row r="246">
@@ -26935,97 +26931,97 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>671218</v>
+        <v>681297</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Heliot Ramos</t>
+          <t>Colton Cowser</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Ramos</t>
+          <t>Cowser</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
           <t xml:space="preserve">SF </t>
         </is>
       </c>
-      <c r="J246" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
       <c r="K246" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L246" t="n">
-        <v>4.454</v>
+        <v>3.993</v>
       </c>
       <c r="M246" t="n">
-        <v>3.99</v>
+        <v>3.411</v>
       </c>
       <c r="N246" t="n">
-        <v>0.892</v>
+        <v>0.734</v>
       </c>
       <c r="O246" t="n">
-        <v>1.349</v>
+        <v>1.144</v>
       </c>
       <c r="P246" t="n">
-        <v>1.055</v>
+        <v>1.03</v>
       </c>
       <c r="Q246" t="n">
-        <v>0.361</v>
+        <v>0.499</v>
       </c>
       <c r="R246" t="n">
-        <v>0.613</v>
+        <v>0.492</v>
       </c>
       <c r="S246" t="n">
-        <v>0.184</v>
+        <v>0.157</v>
       </c>
       <c r="T246" t="n">
-        <v>0.013</v>
+        <v>0.001</v>
       </c>
       <c r="U246" t="n">
-        <v>0.082</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="V246" t="n">
-        <v>0.516</v>
+        <v>0.44</v>
       </c>
       <c r="W246" t="n">
-        <v>0.45</v>
+        <v>0.429</v>
       </c>
       <c r="X246" t="n">
-        <v>0.043</v>
+        <v>0.125</v>
       </c>
       <c r="Y246" t="n">
-        <v>0.036</v>
+        <v>0.104</v>
       </c>
       <c r="Z246" t="n">
-        <v>6.517</v>
+        <v>6.359</v>
       </c>
       <c r="AA246" t="n">
-        <v>8.589</v>
+        <v>8.462</v>
       </c>
       <c r="AB246" t="n">
-        <v>0.078</v>
+        <v>0.081</v>
       </c>
       <c r="AC246" t="n">
-        <v>0.62</v>
+        <v>0.55</v>
       </c>
       <c r="AD246" t="n">
-        <v>0.035</v>
+        <v>0.101</v>
       </c>
     </row>
     <row r="247">
@@ -27043,97 +27039,97 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>672275</v>
+        <v>683002</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Gunnar Henderson</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Bailey</t>
+          <t>Henderson</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
           <t xml:space="preserve">SF </t>
         </is>
       </c>
-      <c r="J247" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
       <c r="K247" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L247" t="n">
-        <v>3.774</v>
+        <v>4.614</v>
       </c>
       <c r="M247" t="n">
-        <v>3.371</v>
+        <v>3.921</v>
       </c>
       <c r="N247" t="n">
-        <v>0.758</v>
+        <v>0.976</v>
       </c>
       <c r="O247" t="n">
-        <v>1.058</v>
+        <v>1.526</v>
       </c>
       <c r="P247" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.694</v>
       </c>
       <c r="Q247" t="n">
-        <v>0.311</v>
+        <v>0.595</v>
       </c>
       <c r="R247" t="n">
-        <v>0.575</v>
+        <v>0.65</v>
       </c>
       <c r="S247" t="n">
-        <v>0.118</v>
+        <v>0.193</v>
       </c>
       <c r="T247" t="n">
-        <v>0.014</v>
+        <v>0.041</v>
       </c>
       <c r="U247" t="n">
-        <v>0.051</v>
+        <v>0.092</v>
       </c>
       <c r="V247" t="n">
-        <v>0.338</v>
+        <v>0.413</v>
       </c>
       <c r="W247" t="n">
-        <v>0.373</v>
+        <v>0.622</v>
       </c>
       <c r="X247" t="n">
-        <v>0.03</v>
+        <v>0.191</v>
       </c>
       <c r="Y247" t="n">
-        <v>0.026</v>
+        <v>0.163</v>
       </c>
       <c r="Z247" t="n">
-        <v>5.111</v>
+        <v>8.236000000000001</v>
       </c>
       <c r="AA247" t="n">
-        <v>6.636</v>
+        <v>10.778</v>
       </c>
       <c r="AB247" t="n">
-        <v>0.051</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AC247" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.654</v>
       </c>
       <c r="AD247" t="n">
-        <v>0.026</v>
+        <v>0.152</v>
       </c>
     </row>
     <row r="248">
@@ -27151,97 +27147,97 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>681297</v>
+        <v>683766</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Colton Cowser</t>
+          <t>Christian Koss</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Cowser</t>
+          <t>Koss</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
+          <t xml:space="preserve">SF </t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
           <t>BAL</t>
         </is>
       </c>
-      <c r="J248" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SF </t>
-        </is>
-      </c>
       <c r="K248" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L248" t="n">
-        <v>3.869</v>
+        <v>3.706</v>
       </c>
       <c r="M248" t="n">
-        <v>3.317</v>
+        <v>3.41</v>
       </c>
       <c r="N248" t="n">
-        <v>0.711</v>
+        <v>0.765</v>
       </c>
       <c r="O248" t="n">
-        <v>1.1</v>
+        <v>1.094</v>
       </c>
       <c r="P248" t="n">
-        <v>1.015</v>
+        <v>0.827</v>
       </c>
       <c r="Q248" t="n">
-        <v>0.47</v>
+        <v>0.205</v>
       </c>
       <c r="R248" t="n">
-        <v>0.486</v>
+        <v>0.55</v>
       </c>
       <c r="S248" t="n">
-        <v>0.141</v>
+        <v>0.157</v>
       </c>
       <c r="T248" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="U248" t="n">
-        <v>0.081</v>
+        <v>0.057</v>
       </c>
       <c r="V248" t="n">
-        <v>0.394</v>
+        <v>0.339</v>
       </c>
       <c r="W248" t="n">
-        <v>0.423</v>
+        <v>0.349</v>
       </c>
       <c r="X248" t="n">
-        <v>0.112</v>
+        <v>0.093</v>
       </c>
       <c r="Y248" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.073</v>
       </c>
       <c r="Z248" t="n">
-        <v>5.998</v>
+        <v>5.164</v>
       </c>
       <c r="AA248" t="n">
-        <v>7.959</v>
+        <v>6.642</v>
       </c>
       <c r="AB248" t="n">
-        <v>0.077</v>
+        <v>0.056</v>
       </c>
       <c r="AC248" t="n">
-        <v>0.534</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AD248" t="n">
-        <v>0.083</v>
+        <v>0.07199999999999999</v>
       </c>
     </row>
     <row r="249">
@@ -27259,16 +27255,16 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>683002</v>
+        <v>687637</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Gunnar Henderson</t>
+          <t>Dylan Beavers</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Henderson</t>
+          <t>Beavers</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -27292,64 +27288,64 @@
         </is>
       </c>
       <c r="K249" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L249" t="n">
-        <v>4.609</v>
+        <v>4.088</v>
       </c>
       <c r="M249" t="n">
-        <v>3.896</v>
+        <v>3.39</v>
       </c>
       <c r="N249" t="n">
-        <v>0.998</v>
+        <v>0.721</v>
       </c>
       <c r="O249" t="n">
-        <v>1.524</v>
+        <v>1.091</v>
       </c>
       <c r="P249" t="n">
-        <v>0.712</v>
+        <v>0.852</v>
       </c>
       <c r="Q249" t="n">
-        <v>0.605</v>
+        <v>0.61</v>
       </c>
       <c r="R249" t="n">
-        <v>0.676</v>
+        <v>0.511</v>
       </c>
       <c r="S249" t="n">
-        <v>0.199</v>
+        <v>0.128</v>
       </c>
       <c r="T249" t="n">
-        <v>0.042</v>
+        <v>0.003</v>
       </c>
       <c r="U249" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="V249" t="n">
+        <v>0.422</v>
+      </c>
+      <c r="W249" t="n">
+        <v>0.443</v>
+      </c>
+      <c r="X249" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="Y249" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="Z249" t="n">
+        <v>6.354</v>
+      </c>
+      <c r="AA249" t="n">
+        <v>8.502000000000001</v>
+      </c>
+      <c r="AB249" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="AC249" t="n">
+        <v>0.542</v>
+      </c>
+      <c r="AD249" t="n">
         <v>0.081</v>
-      </c>
-      <c r="V249" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="W249" t="n">
-        <v>0.632</v>
-      </c>
-      <c r="X249" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Y249" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="Z249" t="n">
-        <v>8.353</v>
-      </c>
-      <c r="AA249" t="n">
-        <v>10.934</v>
-      </c>
-      <c r="AB249" t="n">
-        <v>0.078</v>
-      </c>
-      <c r="AC249" t="n">
-        <v>0.664</v>
-      </c>
-      <c r="AD249" t="n">
-        <v>0.158</v>
       </c>
     </row>
     <row r="250">
@@ -27367,21 +27363,21 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>687637</v>
+        <v>691723</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Dylan Beavers</t>
+          <t>Coby Mayo</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Beavers</t>
+          <t>Mayo</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -27400,64 +27396,64 @@
         </is>
       </c>
       <c r="K250" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L250" t="n">
-        <v>4.014</v>
+        <v>3.873</v>
       </c>
       <c r="M250" t="n">
-        <v>3.339</v>
+        <v>3.36</v>
       </c>
       <c r="N250" t="n">
-        <v>0.712</v>
+        <v>0.749</v>
       </c>
       <c r="O250" t="n">
-        <v>1.075</v>
+        <v>1.076</v>
       </c>
       <c r="P250" t="n">
-        <v>0.854</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="Q250" t="n">
-        <v>0.591</v>
+        <v>0.434</v>
       </c>
       <c r="R250" t="n">
-        <v>0.501</v>
+        <v>0.517</v>
       </c>
       <c r="S250" t="n">
-        <v>0.133</v>
+        <v>0.185</v>
       </c>
       <c r="T250" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="U250" t="n">
-        <v>0.074</v>
+        <v>0.047</v>
       </c>
       <c r="V250" t="n">
-        <v>0.381</v>
+        <v>0.393</v>
       </c>
       <c r="W250" t="n">
-        <v>0.417</v>
+        <v>0.401</v>
       </c>
       <c r="X250" t="n">
-        <v>0.102</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="Y250" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.068</v>
       </c>
       <c r="Z250" t="n">
-        <v>6.135</v>
+        <v>5.742</v>
       </c>
       <c r="AA250" t="n">
-        <v>8.166</v>
+        <v>7.594</v>
       </c>
       <c r="AB250" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.046</v>
       </c>
       <c r="AC250" t="n">
-        <v>0.527</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="AD250" t="n">
-        <v>0.08</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="251">
@@ -27475,16 +27471,16 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>691723</v>
+        <v>691740</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Coby Mayo</t>
+          <t>Daniel Susac</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Mayo</t>
+          <t>Susac</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -27494,78 +27490,78 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
+          <t xml:space="preserve">SF </t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
           <t>BAL</t>
         </is>
       </c>
-      <c r="J251" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SF </t>
-        </is>
-      </c>
       <c r="K251" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L251" t="n">
-        <v>3.717</v>
+        <v>4.131</v>
       </c>
       <c r="M251" t="n">
-        <v>3.205</v>
+        <v>3.729</v>
       </c>
       <c r="N251" t="n">
-        <v>0.695</v>
+        <v>0.783</v>
       </c>
       <c r="O251" t="n">
-        <v>0.995</v>
+        <v>1.192</v>
       </c>
       <c r="P251" t="n">
-        <v>0.863</v>
+        <v>1.133</v>
       </c>
       <c r="Q251" t="n">
-        <v>0.426</v>
+        <v>0.312</v>
       </c>
       <c r="R251" t="n">
-        <v>0.484</v>
+        <v>0.546</v>
       </c>
       <c r="S251" t="n">
-        <v>0.167</v>
+        <v>0.146</v>
       </c>
       <c r="T251" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="U251" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="V251" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="W251" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="X251" t="n">
         <v>0.044</v>
       </c>
-      <c r="V251" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="W251" t="n">
-        <v>0.396</v>
-      </c>
-      <c r="X251" t="n">
-        <v>0.08400000000000001</v>
-      </c>
       <c r="Y251" t="n">
-        <v>0.067</v>
+        <v>0.032</v>
       </c>
       <c r="Z251" t="n">
-        <v>5.396</v>
+        <v>5.555</v>
       </c>
       <c r="AA251" t="n">
-        <v>7.137</v>
+        <v>7.236</v>
       </c>
       <c r="AB251" t="n">
-        <v>0.043</v>
+        <v>0.079</v>
       </c>
       <c r="AC251" t="n">
-        <v>0.522</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="AD251" t="n">
-        <v>0.066</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="252">
@@ -27619,61 +27615,61 @@
         <v>4</v>
       </c>
       <c r="L252" t="n">
-        <v>4.333</v>
+        <v>4.364</v>
       </c>
       <c r="M252" t="n">
-        <v>3.962</v>
+        <v>3.959</v>
       </c>
       <c r="N252" t="n">
-        <v>0.865</v>
+        <v>0.888</v>
       </c>
       <c r="O252" t="n">
-        <v>1.297</v>
+        <v>1.306</v>
       </c>
       <c r="P252" t="n">
-        <v>0.971</v>
+        <v>0.987</v>
       </c>
       <c r="Q252" t="n">
-        <v>0.289</v>
+        <v>0.316</v>
       </c>
       <c r="R252" t="n">
-        <v>0.601</v>
+        <v>0.624</v>
       </c>
       <c r="S252" t="n">
-        <v>0.179</v>
+        <v>0.187</v>
       </c>
       <c r="T252" t="n">
         <v>0</v>
       </c>
       <c r="U252" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.077</v>
       </c>
       <c r="V252" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.533</v>
       </c>
       <c r="W252" t="n">
         <v>0.415</v>
       </c>
       <c r="X252" t="n">
-        <v>0.029</v>
+        <v>0.027</v>
       </c>
       <c r="Y252" t="n">
-        <v>0.024</v>
+        <v>0.022</v>
       </c>
       <c r="Z252" t="n">
-        <v>6.201</v>
+        <v>6.213</v>
       </c>
       <c r="AA252" t="n">
-        <v>8.208</v>
+        <v>8.189</v>
       </c>
       <c r="AB252" t="n">
-        <v>0.082</v>
+        <v>0.074</v>
       </c>
       <c r="AC252" t="n">
-        <v>0.604</v>
+        <v>0.613</v>
       </c>
       <c r="AD252" t="n">
-        <v>0.024</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="253">
@@ -27724,43 +27720,43 @@
         </is>
       </c>
       <c r="K253" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L253" t="n">
-        <v>4.118</v>
+        <v>4.373</v>
       </c>
       <c r="M253" t="n">
-        <v>3.664</v>
+        <v>3.881</v>
       </c>
       <c r="N253" t="n">
-        <v>1.009</v>
+        <v>1.044</v>
       </c>
       <c r="O253" t="n">
-        <v>1.378</v>
+        <v>1.45</v>
       </c>
       <c r="P253" t="n">
-        <v>0.476</v>
+        <v>0.503</v>
       </c>
       <c r="Q253" t="n">
-        <v>0.355</v>
+        <v>0.388</v>
       </c>
       <c r="R253" t="n">
-        <v>0.765</v>
+        <v>0.794</v>
       </c>
       <c r="S253" t="n">
-        <v>0.162</v>
+        <v>0.157</v>
       </c>
       <c r="T253" t="n">
-        <v>0.037</v>
+        <v>0.032</v>
       </c>
       <c r="U253" t="n">
-        <v>0.044</v>
+        <v>0.062</v>
       </c>
       <c r="V253" t="n">
-        <v>0.418</v>
+        <v>0.504</v>
       </c>
       <c r="W253" t="n">
-        <v>0.409</v>
+        <v>0.453</v>
       </c>
       <c r="X253" t="n">
         <v>0.078</v>
@@ -27769,19 +27765,19 @@
         <v>0.059</v>
       </c>
       <c r="Z253" t="n">
-        <v>6.508</v>
+        <v>7.021</v>
       </c>
       <c r="AA253" t="n">
-        <v>8.329000000000001</v>
+        <v>9.077999999999999</v>
       </c>
       <c r="AB253" t="n">
-        <v>0.043</v>
+        <v>0.06</v>
       </c>
       <c r="AC253" t="n">
-        <v>0.661</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="AD253" t="n">
-        <v>0.058</v>
+        <v>0.057</v>
       </c>
     </row>
     <row r="254">

--- a/data/live/BallparkPal_Batters_2026-04-12.xlsx
+++ b/data/live/BallparkPal_Batters_2026-04-12.xlsx
@@ -8355,16 +8355,16 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>592518</v>
+        <v>592206</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Manny Machado</t>
+          <t>Nick Castellanos</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Machado</t>
+          <t>Castellanos</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -8388,64 +8388,64 @@
         </is>
       </c>
       <c r="K74" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L74" t="n">
-        <v>4.25</v>
+        <v>3.903</v>
       </c>
       <c r="M74" t="n">
-        <v>3.743</v>
+        <v>3.617</v>
       </c>
       <c r="N74" t="n">
-        <v>1.02</v>
+        <v>0.843</v>
       </c>
       <c r="O74" t="n">
-        <v>1.71</v>
+        <v>1.371</v>
       </c>
       <c r="P74" t="n">
-        <v>0.862</v>
+        <v>0.905</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.412</v>
+        <v>0.195</v>
       </c>
       <c r="R74" t="n">
-        <v>0.673</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="S74" t="n">
-        <v>0.172</v>
+        <v>0.149</v>
       </c>
       <c r="T74" t="n">
-        <v>0.007</v>
+        <v>0.015</v>
       </c>
       <c r="U74" t="n">
-        <v>0.168</v>
+        <v>0.116</v>
       </c>
       <c r="V74" t="n">
-        <v>0.61</v>
+        <v>0.462</v>
       </c>
       <c r="W74" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.403</v>
       </c>
       <c r="X74" t="n">
-        <v>0.083</v>
+        <v>0.041</v>
       </c>
       <c r="Y74" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.034</v>
       </c>
       <c r="Z74" t="n">
-        <v>8.140000000000001</v>
+        <v>6.006</v>
       </c>
       <c r="AA74" t="n">
-        <v>10.734</v>
+        <v>7.809</v>
       </c>
       <c r="AB74" t="n">
-        <v>0.157</v>
+        <v>0.11</v>
       </c>
       <c r="AC74" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.596</v>
       </c>
       <c r="AD74" t="n">
-        <v>0.067</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="75">
@@ -8463,16 +8463,16 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>593428</v>
+        <v>592518</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Xander Bogaerts</t>
+          <t>Manny Machado</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bogaerts</t>
+          <t>Machado</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -8496,64 +8496,64 @@
         </is>
       </c>
       <c r="K75" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L75" t="n">
-        <v>3.966</v>
+        <v>4.25</v>
       </c>
       <c r="M75" t="n">
-        <v>3.55</v>
+        <v>3.733</v>
       </c>
       <c r="N75" t="n">
-        <v>0.902</v>
+        <v>0.994</v>
       </c>
       <c r="O75" t="n">
-        <v>1.34</v>
+        <v>1.676</v>
       </c>
       <c r="P75" t="n">
-        <v>0.547</v>
+        <v>0.874</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.328</v>
+        <v>0.424</v>
       </c>
       <c r="R75" t="n">
-        <v>0.658</v>
+        <v>0.655</v>
       </c>
       <c r="S75" t="n">
-        <v>0.143</v>
+        <v>0.164</v>
       </c>
       <c r="T75" t="n">
         <v>0.008</v>
       </c>
       <c r="U75" t="n">
-        <v>0.093</v>
+        <v>0.167</v>
       </c>
       <c r="V75" t="n">
-        <v>0.449</v>
+        <v>0.591</v>
       </c>
       <c r="W75" t="n">
-        <v>0.442</v>
+        <v>0.536</v>
       </c>
       <c r="X75" t="n">
-        <v>0.117</v>
+        <v>0.079</v>
       </c>
       <c r="Y75" t="n">
-        <v>0.095</v>
+        <v>0.064</v>
       </c>
       <c r="Z75" t="n">
-        <v>6.597</v>
+        <v>7.947</v>
       </c>
       <c r="AA75" t="n">
-        <v>8.561</v>
+        <v>10.472</v>
       </c>
       <c r="AB75" t="n">
-        <v>0.089</v>
+        <v>0.156</v>
       </c>
       <c r="AC75" t="n">
-        <v>0.622</v>
+        <v>0.669</v>
       </c>
       <c r="AD75" t="n">
-        <v>0.092</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="76">
@@ -8571,16 +8571,16 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>609280</v>
+        <v>593428</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Miguel Andujar</t>
+          <t>Xander Bogaerts</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Andujar</t>
+          <t>Bogaerts</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -8607,61 +8607,61 @@
         <v>5</v>
       </c>
       <c r="L76" t="n">
-        <v>4.055</v>
+        <v>4.042</v>
       </c>
       <c r="M76" t="n">
-        <v>3.717</v>
+        <v>3.615</v>
       </c>
       <c r="N76" t="n">
-        <v>1.029</v>
+        <v>0.883</v>
       </c>
       <c r="O76" t="n">
-        <v>1.436</v>
+        <v>1.335</v>
       </c>
       <c r="P76" t="n">
-        <v>0.589</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.233</v>
+        <v>0.335</v>
       </c>
       <c r="R76" t="n">
-        <v>0.783</v>
+        <v>0.635</v>
       </c>
       <c r="S76" t="n">
-        <v>0.16</v>
+        <v>0.144</v>
       </c>
       <c r="T76" t="n">
-        <v>0.011</v>
+        <v>0.004</v>
       </c>
       <c r="U76" t="n">
-        <v>0.075</v>
+        <v>0.1</v>
       </c>
       <c r="V76" t="n">
-        <v>0.447</v>
+        <v>0.454</v>
       </c>
       <c r="W76" t="n">
-        <v>0.457</v>
+        <v>0.451</v>
       </c>
       <c r="X76" t="n">
-        <v>0.044</v>
+        <v>0.1</v>
       </c>
       <c r="Y76" t="n">
-        <v>0.034</v>
+        <v>0.081</v>
       </c>
       <c r="Z76" t="n">
-        <v>6.431</v>
+        <v>6.543</v>
       </c>
       <c r="AA76" t="n">
-        <v>8.237</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="AB76" t="n">
-        <v>0.074</v>
+        <v>0.095</v>
       </c>
       <c r="AC76" t="n">
-        <v>0.681</v>
+        <v>0.619</v>
       </c>
       <c r="AD76" t="n">
-        <v>0.032</v>
+        <v>0.076</v>
       </c>
     </row>
     <row r="77">
@@ -8679,21 +8679,21 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>630105</v>
+        <v>657656</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Jake Cronenworth</t>
+          <t>Ramon Laureano</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Cronenworth</t>
+          <t>Laureano</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -8712,64 +8712,64 @@
         </is>
       </c>
       <c r="K77" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L77" t="n">
-        <v>3.687</v>
+        <v>4.51</v>
       </c>
       <c r="M77" t="n">
-        <v>3.171</v>
+        <v>4.024</v>
       </c>
       <c r="N77" t="n">
-        <v>0.792</v>
+        <v>1.035</v>
       </c>
       <c r="O77" t="n">
-        <v>1.191</v>
+        <v>1.747</v>
       </c>
       <c r="P77" t="n">
-        <v>0.731</v>
+        <v>0.944</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.429</v>
+        <v>0.376</v>
       </c>
       <c r="R77" t="n">
-        <v>0.571</v>
+        <v>0.676</v>
       </c>
       <c r="S77" t="n">
-        <v>0.12</v>
+        <v>0.177</v>
       </c>
       <c r="T77" t="n">
-        <v>0.021</v>
+        <v>0.012</v>
       </c>
       <c r="U77" t="n">
-        <v>0.079</v>
+        <v>0.17</v>
       </c>
       <c r="V77" t="n">
-        <v>0.393</v>
+        <v>0.488</v>
       </c>
       <c r="W77" t="n">
-        <v>0.432</v>
+        <v>0.631</v>
       </c>
       <c r="X77" t="n">
-        <v>0.033</v>
+        <v>0.18</v>
       </c>
       <c r="Y77" t="n">
-        <v>0.025</v>
+        <v>0.147</v>
       </c>
       <c r="Z77" t="n">
-        <v>5.908</v>
+        <v>8.438000000000001</v>
       </c>
       <c r="AA77" t="n">
-        <v>7.769</v>
+        <v>10.98</v>
       </c>
       <c r="AB77" t="n">
-        <v>0.077</v>
+        <v>0.159</v>
       </c>
       <c r="AC77" t="n">
-        <v>0.581</v>
+        <v>0.668</v>
       </c>
       <c r="AD77" t="n">
-        <v>0.025</v>
+        <v>0.137</v>
       </c>
     </row>
     <row r="78">
@@ -8787,97 +8787,97 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>650489</v>
+        <v>664034</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Willi Castro</t>
+          <t>Ty France</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Castro</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>R</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
+          <t xml:space="preserve">SD </t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
           <t>COL</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SD </t>
         </is>
       </c>
       <c r="K78" t="n">
         <v>7</v>
       </c>
       <c r="L78" t="n">
-        <v>3.809</v>
+        <v>3.885</v>
       </c>
       <c r="M78" t="n">
-        <v>3.409</v>
+        <v>3.518</v>
       </c>
       <c r="N78" t="n">
-        <v>0.601</v>
+        <v>0.92</v>
       </c>
       <c r="O78" t="n">
-        <v>0.977</v>
+        <v>1.372</v>
       </c>
       <c r="P78" t="n">
-        <v>1.32</v>
+        <v>0.649</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.322</v>
+        <v>0.268</v>
       </c>
       <c r="R78" t="n">
-        <v>0.413</v>
+        <v>0.671</v>
       </c>
       <c r="S78" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.145</v>
       </c>
       <c r="T78" t="n">
-        <v>0.016</v>
+        <v>0.007</v>
       </c>
       <c r="U78" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.098</v>
       </c>
       <c r="V78" t="n">
-        <v>0.266</v>
+        <v>0.431</v>
       </c>
       <c r="W78" t="n">
-        <v>0.285</v>
+        <v>0.415</v>
       </c>
       <c r="X78" t="n">
-        <v>0.113</v>
+        <v>0.023</v>
       </c>
       <c r="Y78" t="n">
-        <v>0.094</v>
+        <v>0.018</v>
       </c>
       <c r="Z78" t="n">
-        <v>4.875</v>
+        <v>6.087</v>
       </c>
       <c r="AA78" t="n">
-        <v>6.306</v>
+        <v>7.866</v>
       </c>
       <c r="AB78" t="n">
-        <v>0.079</v>
+        <v>0.096</v>
       </c>
       <c r="AC78" t="n">
-        <v>0.458</v>
+        <v>0.639</v>
       </c>
       <c r="AD78" t="n">
-        <v>0.089</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="79">
@@ -8895,97 +8895,97 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>657656</v>
+        <v>664954</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ramon Laureano</t>
+          <t>Brett Sullivan</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Laureano</t>
+          <t>Sullivan</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
           <t xml:space="preserve">SD </t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
       <c r="K79" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L79" t="n">
-        <v>4.51</v>
+        <v>3.614</v>
       </c>
       <c r="M79" t="n">
-        <v>4.045</v>
+        <v>3.348</v>
       </c>
       <c r="N79" t="n">
-        <v>1.021</v>
+        <v>0.611</v>
       </c>
       <c r="O79" t="n">
-        <v>1.705</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="P79" t="n">
-        <v>0.988</v>
+        <v>0.979</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.373</v>
+        <v>0.191</v>
       </c>
       <c r="R79" t="n">
-        <v>0.676</v>
+        <v>0.434</v>
       </c>
       <c r="S79" t="n">
-        <v>0.172</v>
+        <v>0.104</v>
       </c>
       <c r="T79" t="n">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="U79" t="n">
-        <v>0.166</v>
+        <v>0.073</v>
       </c>
       <c r="V79" t="n">
-        <v>0.496</v>
+        <v>0.254</v>
       </c>
       <c r="W79" t="n">
-        <v>0.62</v>
+        <v>0.256</v>
       </c>
       <c r="X79" t="n">
-        <v>0.179</v>
+        <v>0.018</v>
       </c>
       <c r="Y79" t="n">
-        <v>0.149</v>
+        <v>0.015</v>
       </c>
       <c r="Z79" t="n">
-        <v>8.326000000000001</v>
+        <v>4.029</v>
       </c>
       <c r="AA79" t="n">
-        <v>10.847</v>
+        <v>5.173</v>
       </c>
       <c r="AB79" t="n">
-        <v>0.154</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AC79" t="n">
-        <v>0.677</v>
+        <v>0.475</v>
       </c>
       <c r="AD79" t="n">
-        <v>0.141</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="80">
@@ -9003,16 +9003,16 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>664034</v>
+        <v>665487</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ty France</t>
+          <t>Fernando Tatis Jr.</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Tatis Jr.</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -9036,64 +9036,64 @@
         </is>
       </c>
       <c r="K80" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L80" t="n">
-        <v>3.914</v>
+        <v>4.314</v>
       </c>
       <c r="M80" t="n">
-        <v>3.534</v>
+        <v>3.764</v>
       </c>
       <c r="N80" t="n">
-        <v>0.953</v>
+        <v>0.917</v>
       </c>
       <c r="O80" t="n">
-        <v>1.423</v>
+        <v>1.53</v>
       </c>
       <c r="P80" t="n">
-        <v>0.621</v>
+        <v>1.004</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="R80" t="n">
-        <v>0.695</v>
+        <v>0.615</v>
       </c>
       <c r="S80" t="n">
-        <v>0.149</v>
+        <v>0.142</v>
       </c>
       <c r="T80" t="n">
-        <v>0.006</v>
+        <v>0.011</v>
       </c>
       <c r="U80" t="n">
-        <v>0.103</v>
+        <v>0.15</v>
       </c>
       <c r="V80" t="n">
-        <v>0.473</v>
+        <v>0.455</v>
       </c>
       <c r="W80" t="n">
-        <v>0.459</v>
+        <v>0.572</v>
       </c>
       <c r="X80" t="n">
-        <v>0.024</v>
+        <v>0.282</v>
       </c>
       <c r="Y80" t="n">
-        <v>0.018</v>
+        <v>0.22</v>
       </c>
       <c r="Z80" t="n">
-        <v>6.465</v>
+        <v>8.191000000000001</v>
       </c>
       <c r="AA80" t="n">
-        <v>8.406000000000001</v>
+        <v>10.682</v>
       </c>
       <c r="AB80" t="n">
-        <v>0.099</v>
+        <v>0.139</v>
       </c>
       <c r="AC80" t="n">
-        <v>0.652</v>
+        <v>0.631</v>
       </c>
       <c r="AD80" t="n">
-        <v>0.018</v>
+        <v>0.202</v>
       </c>
     </row>
     <row r="81">
@@ -9111,16 +9111,16 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>665487</v>
+        <v>666023</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Fernando Tatis Jr.</t>
+          <t>Freddy Fermin</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tatis Jr.</t>
+          <t>Fermin</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -9144,64 +9144,64 @@
         </is>
       </c>
       <c r="K81" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L81" t="n">
-        <v>4.355</v>
+        <v>3.363</v>
       </c>
       <c r="M81" t="n">
-        <v>3.788</v>
+        <v>3.035</v>
       </c>
       <c r="N81" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.716</v>
       </c>
       <c r="O81" t="n">
-        <v>1.578</v>
+        <v>1.051</v>
       </c>
       <c r="P81" t="n">
-        <v>0.958</v>
+        <v>0.616</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.476</v>
+        <v>0.247</v>
       </c>
       <c r="R81" t="n">
-        <v>0.623</v>
+        <v>0.518</v>
       </c>
       <c r="S81" t="n">
-        <v>0.155</v>
+        <v>0.129</v>
       </c>
       <c r="T81" t="n">
-        <v>0.008999999999999999</v>
+        <v>0</v>
       </c>
       <c r="U81" t="n">
-        <v>0.154</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="V81" t="n">
-        <v>0.494</v>
+        <v>0.312</v>
       </c>
       <c r="W81" t="n">
-        <v>0.606</v>
+        <v>0.368</v>
       </c>
       <c r="X81" t="n">
-        <v>0.293</v>
+        <v>0.021</v>
       </c>
       <c r="Y81" t="n">
-        <v>0.222</v>
+        <v>0.016</v>
       </c>
       <c r="Z81" t="n">
-        <v>8.525</v>
+        <v>4.822</v>
       </c>
       <c r="AA81" t="n">
-        <v>11.164</v>
+        <v>6.262</v>
       </c>
       <c r="AB81" t="n">
-        <v>0.143</v>
+        <v>0.066</v>
       </c>
       <c r="AC81" t="n">
-        <v>0.654</v>
+        <v>0.534</v>
       </c>
       <c r="AD81" t="n">
-        <v>0.201</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="82">
@@ -9252,61 +9252,61 @@
         </is>
       </c>
       <c r="K82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L82" t="n">
-        <v>4.261</v>
+        <v>4.198</v>
       </c>
       <c r="M82" t="n">
-        <v>3.962</v>
+        <v>3.926</v>
       </c>
       <c r="N82" t="n">
-        <v>0.729</v>
+        <v>0.751</v>
       </c>
       <c r="O82" t="n">
-        <v>1.33</v>
+        <v>1.343</v>
       </c>
       <c r="P82" t="n">
-        <v>1.303</v>
+        <v>1.262</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.202</v>
+        <v>0.188</v>
       </c>
       <c r="R82" t="n">
-        <v>0.456</v>
+        <v>0.469</v>
       </c>
       <c r="S82" t="n">
-        <v>0.098</v>
+        <v>0.111</v>
       </c>
       <c r="T82" t="n">
-        <v>0.023</v>
+        <v>0.03</v>
       </c>
       <c r="U82" t="n">
-        <v>0.152</v>
+        <v>0.14</v>
       </c>
       <c r="V82" t="n">
-        <v>0.391</v>
+        <v>0.418</v>
       </c>
       <c r="W82" t="n">
-        <v>0.365</v>
+        <v>0.345</v>
       </c>
       <c r="X82" t="n">
-        <v>0.096</v>
+        <v>0.103</v>
       </c>
       <c r="Y82" t="n">
         <v>0.083</v>
       </c>
       <c r="Z82" t="n">
-        <v>5.892</v>
+        <v>5.922</v>
       </c>
       <c r="AA82" t="n">
-        <v>7.625</v>
+        <v>7.655</v>
       </c>
       <c r="AB82" t="n">
-        <v>0.142</v>
+        <v>0.133</v>
       </c>
       <c r="AC82" t="n">
-        <v>0.521</v>
+        <v>0.55</v>
       </c>
       <c r="AD82" t="n">
         <v>0.08</v>
@@ -9363,61 +9363,61 @@
         <v>1</v>
       </c>
       <c r="L83" t="n">
-        <v>4.222</v>
+        <v>4.258</v>
       </c>
       <c r="M83" t="n">
-        <v>3.62</v>
+        <v>3.637</v>
       </c>
       <c r="N83" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="O83" t="n">
-        <v>1.145</v>
+        <v>1.127</v>
       </c>
       <c r="P83" t="n">
-        <v>1.453</v>
+        <v>1.462</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.513</v>
+        <v>0.541</v>
       </c>
       <c r="R83" t="n">
-        <v>0.47</v>
+        <v>0.466</v>
       </c>
       <c r="S83" t="n">
-        <v>0.102</v>
+        <v>0.098</v>
       </c>
       <c r="T83" t="n">
         <v>0.006</v>
       </c>
       <c r="U83" t="n">
-        <v>0.114</v>
+        <v>0.112</v>
       </c>
       <c r="V83" t="n">
-        <v>0.288</v>
+        <v>0.267</v>
       </c>
       <c r="W83" t="n">
-        <v>0.384</v>
+        <v>0.405</v>
       </c>
       <c r="X83" t="n">
-        <v>0.061</v>
+        <v>0.062</v>
       </c>
       <c r="Y83" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>5.728</v>
+      </c>
+      <c r="AA83" t="n">
+        <v>7.533</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="AC83" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AD83" t="n">
         <v>0.049</v>
-      </c>
-      <c r="Z83" t="n">
-        <v>5.718</v>
-      </c>
-      <c r="AA83" t="n">
-        <v>7.508</v>
-      </c>
-      <c r="AB83" t="n">
-        <v>0.109</v>
-      </c>
-      <c r="AC83" t="n">
-        <v>0.509</v>
-      </c>
-      <c r="AD83" t="n">
-        <v>0.048</v>
       </c>
     </row>
     <row r="84">
@@ -9435,21 +9435,21 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>669134</v>
+        <v>669369</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Luis Campusano</t>
+          <t>Bryce Johnson</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Campusano</t>
+          <t>Johnson</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>S</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -9468,64 +9468,64 @@
         </is>
       </c>
       <c r="K84" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L84" t="n">
-        <v>3.422</v>
+        <v>3.652</v>
       </c>
       <c r="M84" t="n">
-        <v>3.098</v>
+        <v>3.353</v>
       </c>
       <c r="N84" t="n">
-        <v>0.724</v>
+        <v>0.805</v>
       </c>
       <c r="O84" t="n">
-        <v>1.095</v>
+        <v>1.225</v>
       </c>
       <c r="P84" t="n">
-        <v>0.643</v>
+        <v>0.76</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.238</v>
+        <v>0.215</v>
       </c>
       <c r="R84" t="n">
-        <v>0.519</v>
+        <v>0.575</v>
       </c>
       <c r="S84" t="n">
-        <v>0.123</v>
+        <v>0.136</v>
       </c>
       <c r="T84" t="n">
         <v>0</v>
       </c>
       <c r="U84" t="n">
-        <v>0.082</v>
+        <v>0.095</v>
       </c>
       <c r="V84" t="n">
-        <v>0.385</v>
+        <v>0.388</v>
       </c>
       <c r="W84" t="n">
-        <v>0.37</v>
+        <v>0.412</v>
       </c>
       <c r="X84" t="n">
-        <v>0.006</v>
+        <v>0.179</v>
       </c>
       <c r="Y84" t="n">
-        <v>0.004</v>
+        <v>0.142</v>
       </c>
       <c r="Z84" t="n">
-        <v>5.003</v>
+        <v>6.087</v>
       </c>
       <c r="AA84" t="n">
-        <v>6.555</v>
+        <v>7.845</v>
       </c>
       <c r="AB84" t="n">
-        <v>0.079</v>
+        <v>0.09</v>
       </c>
       <c r="AC84" t="n">
-        <v>0.543</v>
+        <v>0.576</v>
       </c>
       <c r="AD84" t="n">
-        <v>0.004</v>
+        <v>0.135</v>
       </c>
     </row>
     <row r="85">
@@ -9543,16 +9543,16 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>678662</v>
+        <v>671289</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Ezequiel Tovar</t>
+          <t>Tyler Freeman</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tovar</t>
+          <t>Freeman</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -9576,64 +9576,64 @@
         </is>
       </c>
       <c r="K85" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L85" t="n">
-        <v>4.165</v>
+        <v>4.445</v>
       </c>
       <c r="M85" t="n">
-        <v>3.845</v>
+        <v>4.004</v>
       </c>
       <c r="N85" t="n">
-        <v>0.751</v>
+        <v>0.923</v>
       </c>
       <c r="O85" t="n">
-        <v>1.314</v>
+        <v>1.332</v>
       </c>
       <c r="P85" t="n">
-        <v>1.303</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.228</v>
+        <v>0.337</v>
       </c>
       <c r="R85" t="n">
-        <v>0.477</v>
+        <v>0.678</v>
       </c>
       <c r="S85" t="n">
-        <v>0.121</v>
+        <v>0.16</v>
       </c>
       <c r="T85" t="n">
-        <v>0.014</v>
+        <v>0.006</v>
       </c>
       <c r="U85" t="n">
-        <v>0.138</v>
+        <v>0.079</v>
       </c>
       <c r="V85" t="n">
-        <v>0.372</v>
+        <v>0.326</v>
       </c>
       <c r="W85" t="n">
-        <v>0.336</v>
+        <v>0.39</v>
       </c>
       <c r="X85" t="n">
-        <v>0.061</v>
+        <v>0.188</v>
       </c>
       <c r="Y85" t="n">
-        <v>0.052</v>
+        <v>0.155</v>
       </c>
       <c r="Z85" t="n">
-        <v>5.664</v>
+        <v>6.552</v>
       </c>
       <c r="AA85" t="n">
-        <v>7.317</v>
+        <v>8.324</v>
       </c>
       <c r="AB85" t="n">
-        <v>0.132</v>
+        <v>0.076</v>
       </c>
       <c r="AC85" t="n">
-        <v>0.551</v>
+        <v>0.627</v>
       </c>
       <c r="AD85" t="n">
-        <v>0.051</v>
+        <v>0.145</v>
       </c>
     </row>
     <row r="86">
@@ -9651,21 +9651,21 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>681198</v>
+        <v>678662</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>TJ Rumfield</t>
+          <t>Ezequiel Tovar</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rumfield</t>
+          <t>Tovar</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -9684,64 +9684,64 @@
         </is>
       </c>
       <c r="K86" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L86" t="n">
-        <v>4.101</v>
+        <v>4.023</v>
       </c>
       <c r="M86" t="n">
-        <v>3.678</v>
+        <v>3.73</v>
       </c>
       <c r="N86" t="n">
-        <v>0.612</v>
+        <v>0.725</v>
       </c>
       <c r="O86" t="n">
-        <v>0.958</v>
+        <v>1.301</v>
       </c>
       <c r="P86" t="n">
-        <v>1.214</v>
+        <v>1.286</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.337</v>
+        <v>0.211</v>
       </c>
       <c r="R86" t="n">
-        <v>0.416</v>
+        <v>0.447</v>
       </c>
       <c r="S86" t="n">
-        <v>0.119</v>
+        <v>0.123</v>
       </c>
       <c r="T86" t="n">
-        <v>0.006</v>
+        <v>0.011</v>
       </c>
       <c r="U86" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.144</v>
       </c>
       <c r="V86" t="n">
-        <v>0.267</v>
+        <v>0.385</v>
       </c>
       <c r="W86" t="n">
-        <v>0.279</v>
+        <v>0.344</v>
       </c>
       <c r="X86" t="n">
-        <v>0.041</v>
+        <v>0.05</v>
       </c>
       <c r="Y86" t="n">
-        <v>0.031</v>
+        <v>0.043</v>
       </c>
       <c r="Z86" t="n">
-        <v>4.527</v>
+        <v>5.578</v>
       </c>
       <c r="AA86" t="n">
-        <v>5.898</v>
+        <v>7.243</v>
       </c>
       <c r="AB86" t="n">
-        <v>0.068</v>
+        <v>0.14</v>
       </c>
       <c r="AC86" t="n">
-        <v>0.471</v>
+        <v>0.545</v>
       </c>
       <c r="AD86" t="n">
-        <v>0.03</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="87">
@@ -9759,21 +9759,21 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>686668</v>
+        <v>681198</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Brenton Doyle</t>
+          <t>TJ Rumfield</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Doyle</t>
+          <t>Rumfield</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -9792,64 +9792,64 @@
         </is>
       </c>
       <c r="K87" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L87" t="n">
-        <v>3.704</v>
+        <v>3.993</v>
       </c>
       <c r="M87" t="n">
-        <v>3.371</v>
+        <v>3.584</v>
       </c>
       <c r="N87" t="n">
-        <v>0.61</v>
+        <v>0.599</v>
       </c>
       <c r="O87" t="n">
-        <v>0.964</v>
+        <v>0.919</v>
       </c>
       <c r="P87" t="n">
-        <v>1.231</v>
+        <v>1.162</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.25</v>
+        <v>0.321</v>
       </c>
       <c r="R87" t="n">
         <v>0.422</v>
       </c>
       <c r="S87" t="n">
-        <v>0.1</v>
+        <v>0.103</v>
       </c>
       <c r="T87" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="U87" t="n">
-        <v>0.079</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="V87" t="n">
-        <v>0.262</v>
+        <v>0.255</v>
       </c>
       <c r="W87" t="n">
-        <v>0.277</v>
+        <v>0.281</v>
       </c>
       <c r="X87" t="n">
-        <v>0.164</v>
+        <v>0.04</v>
       </c>
       <c r="Y87" t="n">
-        <v>0.138</v>
+        <v>0.033</v>
       </c>
       <c r="Z87" t="n">
-        <v>4.896</v>
+        <v>4.386</v>
       </c>
       <c r="AA87" t="n">
-        <v>6.277</v>
+        <v>5.705</v>
       </c>
       <c r="AB87" t="n">
-        <v>0.077</v>
+        <v>0.067</v>
       </c>
       <c r="AC87" t="n">
-        <v>0.466</v>
+        <v>0.464</v>
       </c>
       <c r="AD87" t="n">
-        <v>0.13</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="88">
@@ -9867,21 +9867,21 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>687859</v>
+        <v>686668</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Troy Johnston</t>
+          <t>Brenton Doyle</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Johnston</t>
+          <t>Doyle</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -9900,64 +9900,64 @@
         </is>
       </c>
       <c r="K88" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L88" t="n">
-        <v>3.689</v>
+        <v>3.856</v>
       </c>
       <c r="M88" t="n">
-        <v>3.359</v>
+        <v>3.517</v>
       </c>
       <c r="N88" t="n">
-        <v>0.575</v>
+        <v>0.634</v>
       </c>
       <c r="O88" t="n">
-        <v>0.931</v>
+        <v>0.994</v>
       </c>
       <c r="P88" t="n">
-        <v>1.101</v>
+        <v>1.252</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.249</v>
+        <v>0.255</v>
       </c>
       <c r="R88" t="n">
-        <v>0.391</v>
+        <v>0.448</v>
       </c>
       <c r="S88" t="n">
-        <v>0.096</v>
+        <v>0.091</v>
       </c>
       <c r="T88" t="n">
-        <v>0.006</v>
+        <v>0.013</v>
       </c>
       <c r="U88" t="n">
-        <v>0.083</v>
+        <v>0.081</v>
       </c>
       <c r="V88" t="n">
-        <v>0.247</v>
+        <v>0.269</v>
       </c>
       <c r="W88" t="n">
-        <v>0.258</v>
+        <v>0.276</v>
       </c>
       <c r="X88" t="n">
-        <v>0.079</v>
+        <v>0.183</v>
       </c>
       <c r="Y88" t="n">
-        <v>0.06</v>
+        <v>0.146</v>
       </c>
       <c r="Z88" t="n">
-        <v>4.332</v>
+        <v>5.044</v>
       </c>
       <c r="AA88" t="n">
-        <v>5.588</v>
+        <v>6.445</v>
       </c>
       <c r="AB88" t="n">
-        <v>0.08</v>
+        <v>0.077</v>
       </c>
       <c r="AC88" t="n">
-        <v>0.459</v>
+        <v>0.48</v>
       </c>
       <c r="AD88" t="n">
-        <v>0.058</v>
+        <v>0.138</v>
       </c>
     </row>
     <row r="89">
@@ -10011,61 +10011,61 @@
         <v>9</v>
       </c>
       <c r="L89" t="n">
-        <v>3.614</v>
+        <v>3.627</v>
       </c>
       <c r="M89" t="n">
-        <v>3.181</v>
+        <v>3.18</v>
       </c>
       <c r="N89" t="n">
-        <v>0.575</v>
+        <v>0.592</v>
       </c>
       <c r="O89" t="n">
-        <v>0.866</v>
+        <v>0.89</v>
       </c>
       <c r="P89" t="n">
-        <v>1.213</v>
+        <v>1.223</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.367</v>
+        <v>0.378</v>
       </c>
       <c r="R89" t="n">
-        <v>0.414</v>
+        <v>0.431</v>
       </c>
       <c r="S89" t="n">
-        <v>0.097</v>
+        <v>0.093</v>
       </c>
       <c r="T89" t="n">
         <v>0</v>
       </c>
       <c r="U89" t="n">
-        <v>0.064</v>
+        <v>0.068</v>
       </c>
       <c r="V89" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="W89" t="n">
-        <v>0.28</v>
+        <v>0.292</v>
       </c>
       <c r="X89" t="n">
-        <v>0.045</v>
+        <v>0.043</v>
       </c>
       <c r="Y89" t="n">
-        <v>0.034</v>
+        <v>0.037</v>
       </c>
       <c r="Z89" t="n">
-        <v>4.318</v>
+        <v>4.426</v>
       </c>
       <c r="AA89" t="n">
-        <v>5.642</v>
+        <v>5.766</v>
       </c>
       <c r="AB89" t="n">
-        <v>0.063</v>
+        <v>0.067</v>
       </c>
       <c r="AC89" t="n">
-        <v>0.458</v>
+        <v>0.463</v>
       </c>
       <c r="AD89" t="n">
-        <v>0.033</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="90">
@@ -10116,64 +10116,64 @@
         </is>
       </c>
       <c r="K90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L90" t="n">
-        <v>4.24</v>
+        <v>4.191</v>
       </c>
       <c r="M90" t="n">
-        <v>3.784</v>
+        <v>3.756</v>
       </c>
       <c r="N90" t="n">
-        <v>0.675</v>
+        <v>0.659</v>
       </c>
       <c r="O90" t="n">
-        <v>1.275</v>
+        <v>1.24</v>
       </c>
       <c r="P90" t="n">
-        <v>1.414</v>
+        <v>1.4</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.355</v>
+        <v>0.348</v>
       </c>
       <c r="R90" t="n">
-        <v>0.396</v>
+        <v>0.39</v>
       </c>
       <c r="S90" t="n">
-        <v>0.111</v>
+        <v>0.102</v>
       </c>
       <c r="T90" t="n">
-        <v>0.015</v>
+        <v>0.019</v>
       </c>
       <c r="U90" t="n">
-        <v>0.153</v>
+        <v>0.147</v>
       </c>
       <c r="V90" t="n">
-        <v>0.367</v>
+        <v>0.406</v>
       </c>
       <c r="W90" t="n">
-        <v>0.352</v>
+        <v>0.35</v>
       </c>
       <c r="X90" t="n">
-        <v>0.047</v>
+        <v>0.044</v>
       </c>
       <c r="Y90" t="n">
-        <v>0.036</v>
+        <v>0.035</v>
       </c>
       <c r="Z90" t="n">
-        <v>5.72</v>
+        <v>5.687</v>
       </c>
       <c r="AA90" t="n">
-        <v>7.516</v>
+        <v>7.515</v>
       </c>
       <c r="AB90" t="n">
-        <v>0.141</v>
+        <v>0.138</v>
       </c>
       <c r="AC90" t="n">
-        <v>0.51</v>
+        <v>0.501</v>
       </c>
       <c r="AD90" t="n">
-        <v>0.035</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="91">
@@ -10227,61 +10227,61 @@
         <v>3</v>
       </c>
       <c r="L91" t="n">
-        <v>4.345</v>
+        <v>4.346</v>
       </c>
       <c r="M91" t="n">
-        <v>3.901</v>
+        <v>3.892</v>
       </c>
       <c r="N91" t="n">
-        <v>1.01</v>
+        <v>1.003</v>
       </c>
       <c r="O91" t="n">
-        <v>1.7</v>
+        <v>1.638</v>
       </c>
       <c r="P91" t="n">
-        <v>0.845</v>
+        <v>0.831</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="R91" t="n">
-        <v>0.661</v>
+        <v>0.674</v>
       </c>
       <c r="S91" t="n">
         <v>0.161</v>
       </c>
       <c r="T91" t="n">
-        <v>0.037</v>
+        <v>0.03</v>
       </c>
       <c r="U91" t="n">
-        <v>0.152</v>
+        <v>0.138</v>
       </c>
       <c r="V91" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="W91" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.524</v>
       </c>
       <c r="X91" t="n">
-        <v>0.123</v>
+        <v>0.118</v>
       </c>
       <c r="Y91" t="n">
-        <v>0.095</v>
+        <v>0.098</v>
       </c>
       <c r="Z91" t="n">
-        <v>7.995</v>
+        <v>7.746</v>
       </c>
       <c r="AA91" t="n">
-        <v>10.444</v>
+        <v>10.086</v>
       </c>
       <c r="AB91" t="n">
-        <v>0.143</v>
+        <v>0.13</v>
       </c>
       <c r="AC91" t="n">
-        <v>0.666</v>
+        <v>0.674</v>
       </c>
       <c r="AD91" t="n">
-        <v>0.091</v>
+        <v>0.094</v>
       </c>
     </row>
     <row r="92">
@@ -16167,61 +16167,61 @@
         <v>4</v>
       </c>
       <c r="L146" t="n">
-        <v>4.058</v>
+        <v>4.059</v>
       </c>
       <c r="M146" t="n">
-        <v>3.611</v>
+        <v>3.597</v>
       </c>
       <c r="N146" t="n">
-        <v>0.784</v>
+        <v>0.768</v>
       </c>
       <c r="O146" t="n">
-        <v>1.399</v>
+        <v>1.342</v>
       </c>
       <c r="P146" t="n">
-        <v>0.93</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="Q146" t="n">
-        <v>0.361</v>
+        <v>0.375</v>
       </c>
       <c r="R146" t="n">
-        <v>0.467</v>
+        <v>0.47</v>
       </c>
       <c r="S146" t="n">
-        <v>0.163</v>
+        <v>0.157</v>
       </c>
       <c r="T146" t="n">
         <v>0.008</v>
       </c>
       <c r="U146" t="n">
-        <v>0.145</v>
+        <v>0.134</v>
       </c>
       <c r="V146" t="n">
-        <v>0.466</v>
+        <v>0.413</v>
       </c>
       <c r="W146" t="n">
-        <v>0.434</v>
+        <v>0.401</v>
       </c>
       <c r="X146" t="n">
-        <v>0.052</v>
+        <v>0.055</v>
       </c>
       <c r="Y146" t="n">
-        <v>0.041</v>
+        <v>0.045</v>
       </c>
       <c r="Z146" t="n">
-        <v>6.465</v>
+        <v>6.196</v>
       </c>
       <c r="AA146" t="n">
-        <v>8.550000000000001</v>
+        <v>8.148</v>
       </c>
       <c r="AB146" t="n">
-        <v>0.136</v>
+        <v>0.129</v>
       </c>
       <c r="AC146" t="n">
-        <v>0.571</v>
+        <v>0.572</v>
       </c>
       <c r="AD146" t="n">
-        <v>0.04</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="147">
@@ -16275,61 +16275,61 @@
         <v>5</v>
       </c>
       <c r="L147" t="n">
-        <v>4.062</v>
+        <v>4.023</v>
       </c>
       <c r="M147" t="n">
-        <v>3.525</v>
+        <v>3.49</v>
       </c>
       <c r="N147" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="O147" t="n">
-        <v>1.279</v>
+        <v>1.323</v>
       </c>
       <c r="P147" t="n">
-        <v>1.197</v>
+        <v>1.185</v>
       </c>
       <c r="Q147" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="R147" t="n">
-        <v>0.397</v>
+        <v>0.404</v>
       </c>
       <c r="S147" t="n">
-        <v>0.126</v>
+        <v>0.129</v>
       </c>
       <c r="T147" t="n">
         <v>0.006</v>
       </c>
       <c r="U147" t="n">
-        <v>0.153</v>
+        <v>0.16</v>
       </c>
       <c r="V147" t="n">
-        <v>0.443</v>
+        <v>0.43</v>
       </c>
       <c r="W147" t="n">
-        <v>0.416</v>
+        <v>0.391</v>
       </c>
       <c r="X147" t="n">
-        <v>0.037</v>
+        <v>0.034</v>
       </c>
       <c r="Y147" t="n">
-        <v>0.029</v>
+        <v>0.025</v>
       </c>
       <c r="Z147" t="n">
-        <v>6.171</v>
+        <v>6.187</v>
       </c>
       <c r="AA147" t="n">
-        <v>8.257</v>
+        <v>8.236000000000001</v>
       </c>
       <c r="AB147" t="n">
-        <v>0.143</v>
+        <v>0.15</v>
       </c>
       <c r="AC147" t="n">
-        <v>0.511</v>
+        <v>0.528</v>
       </c>
       <c r="AD147" t="n">
-        <v>0.029</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="148">
@@ -16383,61 +16383,61 @@
         <v>5</v>
       </c>
       <c r="L148" t="n">
-        <v>4.243</v>
+        <v>4.237</v>
       </c>
       <c r="M148" t="n">
-        <v>3.584</v>
+        <v>3.605</v>
       </c>
       <c r="N148" t="n">
-        <v>0.753</v>
+        <v>0.758</v>
       </c>
       <c r="O148" t="n">
-        <v>1.314</v>
+        <v>1.328</v>
       </c>
       <c r="P148" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.967</v>
       </c>
       <c r="Q148" t="n">
-        <v>0.57</v>
+        <v>0.545</v>
       </c>
       <c r="R148" t="n">
-        <v>0.46</v>
+        <v>0.461</v>
       </c>
       <c r="S148" t="n">
-        <v>0.154</v>
+        <v>0.155</v>
       </c>
       <c r="T148" t="n">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="U148" t="n">
-        <v>0.128</v>
+        <v>0.131</v>
       </c>
       <c r="V148" t="n">
-        <v>0.472</v>
+        <v>0.489</v>
       </c>
       <c r="W148" t="n">
-        <v>0.467</v>
+        <v>0.475</v>
       </c>
       <c r="X148" t="n">
-        <v>0.046</v>
+        <v>0.052</v>
       </c>
       <c r="Y148" t="n">
-        <v>0.034</v>
+        <v>0.041</v>
       </c>
       <c r="Z148" t="n">
-        <v>6.708</v>
+        <v>6.78</v>
       </c>
       <c r="AA148" t="n">
-        <v>9</v>
+        <v>9.097</v>
       </c>
       <c r="AB148" t="n">
-        <v>0.121</v>
+        <v>0.123</v>
       </c>
       <c r="AC148" t="n">
         <v>0.55</v>
       </c>
       <c r="AD148" t="n">
-        <v>0.033</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="149">
@@ -16455,97 +16455,97 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>606192</v>
+        <v>607043</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Teoscar Hernandez</t>
+          <t>Brandon Nimmo</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Hernandez</t>
+          <t>Nimmo</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>TEX</t>
-        </is>
-      </c>
       <c r="K149" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L149" t="n">
-        <v>3.881</v>
+        <v>4.854</v>
       </c>
       <c r="M149" t="n">
-        <v>3.523</v>
+        <v>4.145</v>
       </c>
       <c r="N149" t="n">
-        <v>0.771</v>
+        <v>0.966</v>
       </c>
       <c r="O149" t="n">
-        <v>1.303</v>
+        <v>1.659</v>
       </c>
       <c r="P149" t="n">
-        <v>1.103</v>
+        <v>0.991</v>
       </c>
       <c r="Q149" t="n">
-        <v>0.272</v>
+        <v>0.599</v>
       </c>
       <c r="R149" t="n">
-        <v>0.487</v>
+        <v>0.611</v>
       </c>
       <c r="S149" t="n">
-        <v>0.155</v>
+        <v>0.174</v>
       </c>
       <c r="T149" t="n">
-        <v>0.01</v>
+        <v>0.023</v>
       </c>
       <c r="U149" t="n">
-        <v>0.119</v>
+        <v>0.158</v>
       </c>
       <c r="V149" t="n">
-        <v>0.409</v>
+        <v>0.481</v>
       </c>
       <c r="W149" t="n">
-        <v>0.343</v>
+        <v>0.638</v>
       </c>
       <c r="X149" t="n">
-        <v>0.099</v>
+        <v>0.102</v>
       </c>
       <c r="Y149" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="Z149" t="n">
+        <v>8.324999999999999</v>
+      </c>
+      <c r="AA149" t="n">
+        <v>11.008</v>
+      </c>
+      <c r="AB149" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="AC149" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="AD149" t="n">
         <v>0.082</v>
-      </c>
-      <c r="Z149" t="n">
-        <v>5.965</v>
-      </c>
-      <c r="AA149" t="n">
-        <v>7.747</v>
-      </c>
-      <c r="AB149" t="n">
-        <v>0.113</v>
-      </c>
-      <c r="AC149" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="AD149" t="n">
-        <v>0.08</v>
       </c>
     </row>
     <row r="150">
@@ -16563,16 +16563,16 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>607043</v>
+        <v>608369</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Brandon Nimmo</t>
+          <t>Corey Seager</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Nimmo</t>
+          <t>Seager</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -16596,64 +16596,64 @@
         </is>
       </c>
       <c r="K150" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L150" t="n">
-        <v>4.862</v>
+        <v>4.644</v>
       </c>
       <c r="M150" t="n">
-        <v>4.174</v>
+        <v>3.864</v>
       </c>
       <c r="N150" t="n">
-        <v>0.952</v>
+        <v>0.979</v>
       </c>
       <c r="O150" t="n">
-        <v>1.641</v>
+        <v>1.784</v>
       </c>
       <c r="P150" t="n">
-        <v>0.973</v>
+        <v>0.948</v>
       </c>
       <c r="Q150" t="n">
-        <v>0.581</v>
+        <v>0.678</v>
       </c>
       <c r="R150" t="n">
-        <v>0.591</v>
+        <v>0.572</v>
       </c>
       <c r="S150" t="n">
-        <v>0.181</v>
+        <v>0.204</v>
       </c>
       <c r="T150" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="U150" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="V150" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="W150" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="X150" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Z150" t="n">
+        <v>8.728999999999999</v>
+      </c>
+      <c r="AA150" t="n">
+        <v>11.718</v>
+      </c>
+      <c r="AB150" t="n">
+        <v>0.178</v>
+      </c>
+      <c r="AC150" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="AD150" t="n">
         <v>0.029</v>
-      </c>
-      <c r="U150" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="V150" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="W150" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="X150" t="n">
-        <v>0.101</v>
-      </c>
-      <c r="Y150" t="n">
-        <v>0.082</v>
-      </c>
-      <c r="Z150" t="n">
-        <v>8.244999999999999</v>
-      </c>
-      <c r="AA150" t="n">
-        <v>10.919</v>
-      </c>
-      <c r="AB150" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AC150" t="n">
-        <v>0.638</v>
-      </c>
-      <c r="AD150" t="n">
-        <v>0.081</v>
       </c>
     </row>
     <row r="151">
@@ -16671,21 +16671,21 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>608369</v>
+        <v>643376</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Corey Seager</t>
+          <t>Danny Jansen</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Seager</t>
+          <t>Jansen</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -16704,64 +16704,64 @@
         </is>
       </c>
       <c r="K151" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L151" t="n">
-        <v>4.656</v>
+        <v>4.309</v>
       </c>
       <c r="M151" t="n">
-        <v>3.896</v>
+        <v>3.635</v>
       </c>
       <c r="N151" t="n">
-        <v>0.981</v>
+        <v>0.728</v>
       </c>
       <c r="O151" t="n">
-        <v>1.777</v>
+        <v>1.281</v>
       </c>
       <c r="P151" t="n">
-        <v>0.959</v>
+        <v>1.142</v>
       </c>
       <c r="Q151" t="n">
-        <v>0.669</v>
+        <v>0.583</v>
       </c>
       <c r="R151" t="n">
-        <v>0.576</v>
+        <v>0.439</v>
       </c>
       <c r="S151" t="n">
-        <v>0.204</v>
+        <v>0.156</v>
       </c>
       <c r="T151" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.002</v>
       </c>
       <c r="U151" t="n">
-        <v>0.191</v>
+        <v>0.131</v>
       </c>
       <c r="V151" t="n">
-        <v>0.648</v>
+        <v>0.435</v>
       </c>
       <c r="W151" t="n">
-        <v>0.577</v>
+        <v>0.458</v>
       </c>
       <c r="X151" t="n">
-        <v>0.039</v>
+        <v>0.021</v>
       </c>
       <c r="Y151" t="n">
-        <v>0.03</v>
+        <v>0.017</v>
       </c>
       <c r="Z151" t="n">
-        <v>8.673</v>
+        <v>6.461</v>
       </c>
       <c r="AA151" t="n">
-        <v>11.633</v>
+        <v>8.683999999999999</v>
       </c>
       <c r="AB151" t="n">
-        <v>0.177</v>
+        <v>0.122</v>
       </c>
       <c r="AC151" t="n">
-        <v>0.658</v>
+        <v>0.54</v>
       </c>
       <c r="AD151" t="n">
-        <v>0.029</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="152">
@@ -16779,97 +16779,97 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>643376</v>
+        <v>660271</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Danny Jansen</t>
+          <t>Shohei Ohtani</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Jansen</t>
+          <t>Ohtani</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
           <t>TEX</t>
         </is>
       </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="K152" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L152" t="n">
-        <v>4.235</v>
+        <v>4.487</v>
       </c>
       <c r="M152" t="n">
-        <v>3.574</v>
+        <v>3.91</v>
       </c>
       <c r="N152" t="n">
-        <v>0.74</v>
+        <v>0.803</v>
       </c>
       <c r="O152" t="n">
-        <v>1.277</v>
+        <v>1.742</v>
       </c>
       <c r="P152" t="n">
-        <v>1.112</v>
+        <v>1.514</v>
       </c>
       <c r="Q152" t="n">
-        <v>0.576</v>
+        <v>0.484</v>
       </c>
       <c r="R152" t="n">
-        <v>0.453</v>
+        <v>0.403</v>
       </c>
       <c r="S152" t="n">
-        <v>0.16</v>
+        <v>0.113</v>
       </c>
       <c r="T152" t="n">
-        <v>0.002</v>
+        <v>0.034</v>
       </c>
       <c r="U152" t="n">
-        <v>0.125</v>
+        <v>0.253</v>
       </c>
       <c r="V152" t="n">
-        <v>0.463</v>
+        <v>0.511</v>
       </c>
       <c r="W152" t="n">
-        <v>0.475</v>
+        <v>0.593</v>
       </c>
       <c r="X152" t="n">
-        <v>0.02</v>
+        <v>0.226</v>
       </c>
       <c r="Y152" t="n">
-        <v>0.016</v>
+        <v>0.19</v>
       </c>
       <c r="Z152" t="n">
-        <v>6.528</v>
+        <v>8.702999999999999</v>
       </c>
       <c r="AA152" t="n">
-        <v>8.795</v>
+        <v>11.508</v>
       </c>
       <c r="AB152" t="n">
-        <v>0.118</v>
+        <v>0.23</v>
       </c>
       <c r="AC152" t="n">
-        <v>0.549</v>
+        <v>0.578</v>
       </c>
       <c r="AD152" t="n">
-        <v>0.016</v>
+        <v>0.177</v>
       </c>
     </row>
     <row r="153">
@@ -16887,16 +16887,16 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>660271</v>
+        <v>663656</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Shohei Ohtani</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Ohtani</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -16920,64 +16920,64 @@
         </is>
       </c>
       <c r="K153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L153" t="n">
-        <v>4.476</v>
+        <v>4.274</v>
       </c>
       <c r="M153" t="n">
-        <v>3.918</v>
+        <v>3.724</v>
       </c>
       <c r="N153" t="n">
-        <v>0.799</v>
+        <v>0.794</v>
       </c>
       <c r="O153" t="n">
-        <v>1.756</v>
+        <v>1.335</v>
       </c>
       <c r="P153" t="n">
-        <v>1.514</v>
+        <v>0.991</v>
       </c>
       <c r="Q153" t="n">
-        <v>0.48</v>
+        <v>0.459</v>
       </c>
       <c r="R153" t="n">
-        <v>0.391</v>
+        <v>0.531</v>
       </c>
       <c r="S153" t="n">
-        <v>0.118</v>
+        <v>0.115</v>
       </c>
       <c r="T153" t="n">
-        <v>0.029</v>
+        <v>0.018</v>
       </c>
       <c r="U153" t="n">
-        <v>0.26</v>
+        <v>0.13</v>
       </c>
       <c r="V153" t="n">
-        <v>0.497</v>
+        <v>0.371</v>
       </c>
       <c r="W153" t="n">
-        <v>0.594</v>
+        <v>0.45</v>
       </c>
       <c r="X153" t="n">
-        <v>0.207</v>
+        <v>0.232</v>
       </c>
       <c r="Y153" t="n">
-        <v>0.172</v>
+        <v>0.191</v>
       </c>
       <c r="Z153" t="n">
-        <v>8.605</v>
+        <v>7.124</v>
       </c>
       <c r="AA153" t="n">
-        <v>11.383</v>
+        <v>9.262</v>
       </c>
       <c r="AB153" t="n">
-        <v>0.233</v>
+        <v>0.123</v>
       </c>
       <c r="AC153" t="n">
-        <v>0.581</v>
+        <v>0.576</v>
       </c>
       <c r="AD153" t="n">
-        <v>0.16</v>
+        <v>0.174</v>
       </c>
     </row>
     <row r="154">
@@ -16995,97 +16995,97 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>663656</v>
+        <v>669394</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Jake Burger</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Tucker</t>
+          <t>Burger</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>TEX</t>
-        </is>
-      </c>
       <c r="K154" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L154" t="n">
-        <v>4.277</v>
+        <v>4.459</v>
       </c>
       <c r="M154" t="n">
-        <v>3.731</v>
+        <v>4.098</v>
       </c>
       <c r="N154" t="n">
-        <v>0.805</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="O154" t="n">
-        <v>1.391</v>
+        <v>1.634</v>
       </c>
       <c r="P154" t="n">
-        <v>1.013</v>
+        <v>1.187</v>
       </c>
       <c r="Q154" t="n">
-        <v>0.452</v>
+        <v>0.264</v>
       </c>
       <c r="R154" t="n">
-        <v>0.513</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="S154" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="T154" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="U154" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="V154" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="W154" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="X154" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="Y154" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="Z154" t="n">
+        <v>7.198</v>
+      </c>
+      <c r="AA154" t="n">
+        <v>9.493</v>
+      </c>
+      <c r="AB154" t="n">
         <v>0.139</v>
       </c>
-      <c r="T154" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="U154" t="n">
-        <v>0.139</v>
-      </c>
-      <c r="V154" t="n">
-        <v>0.374</v>
-      </c>
-      <c r="W154" t="n">
-        <v>0.486</v>
-      </c>
-      <c r="X154" t="n">
-        <v>0.214</v>
-      </c>
-      <c r="Y154" t="n">
-        <v>0.176</v>
-      </c>
-      <c r="Z154" t="n">
-        <v>7.245</v>
-      </c>
-      <c r="AA154" t="n">
-        <v>9.449999999999999</v>
-      </c>
-      <c r="AB154" t="n">
-        <v>0.131</v>
-      </c>
       <c r="AC154" t="n">
-        <v>0.58</v>
+        <v>0.633</v>
       </c>
       <c r="AD154" t="n">
-        <v>0.164</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="155">
@@ -17103,11 +17103,11 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>669257</v>
+        <v>669701</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Will Smith</t>
+          <t>Josh Smith</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -17117,83 +17117,83 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>TEX</t>
-        </is>
-      </c>
       <c r="K155" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L155" t="n">
-        <v>4.231</v>
+        <v>4.177</v>
       </c>
       <c r="M155" t="n">
-        <v>3.581</v>
+        <v>3.56</v>
       </c>
       <c r="N155" t="n">
-        <v>0.77</v>
+        <v>0.831</v>
       </c>
       <c r="O155" t="n">
-        <v>1.356</v>
+        <v>1.336</v>
       </c>
       <c r="P155" t="n">
-        <v>1.112</v>
+        <v>0.737</v>
       </c>
       <c r="Q155" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.532</v>
       </c>
       <c r="R155" t="n">
-        <v>0.481</v>
+        <v>0.528</v>
       </c>
       <c r="S155" t="n">
-        <v>0.134</v>
+        <v>0.195</v>
       </c>
       <c r="T155" t="n">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
       <c r="U155" t="n">
-        <v>0.143</v>
+        <v>0.094</v>
       </c>
       <c r="V155" t="n">
-        <v>0.43</v>
+        <v>0.425</v>
       </c>
       <c r="W155" t="n">
-        <v>0.451</v>
+        <v>0.45</v>
       </c>
       <c r="X155" t="n">
-        <v>0.04</v>
+        <v>0.113</v>
       </c>
       <c r="Y155" t="n">
-        <v>0.029</v>
+        <v>0.092</v>
       </c>
       <c r="Z155" t="n">
-        <v>6.664</v>
+        <v>6.884</v>
       </c>
       <c r="AA155" t="n">
-        <v>8.869999999999999</v>
+        <v>9.082000000000001</v>
       </c>
       <c r="AB155" t="n">
-        <v>0.136</v>
+        <v>0.091</v>
       </c>
       <c r="AC155" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.597</v>
       </c>
       <c r="AD155" t="n">
-        <v>0.029</v>
+        <v>0.089</v>
       </c>
     </row>
     <row r="156">
@@ -17211,16 +17211,16 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>669394</v>
+        <v>669743</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Jake Burger</t>
+          <t>Alex Call</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Burger</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -17230,78 +17230,78 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
           <t>TEX</t>
         </is>
       </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="K156" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L156" t="n">
-        <v>4.479</v>
+        <v>3.551</v>
       </c>
       <c r="M156" t="n">
-        <v>4.126</v>
+        <v>3.064</v>
       </c>
       <c r="N156" t="n">
-        <v>0.913</v>
+        <v>0.632</v>
       </c>
       <c r="O156" t="n">
-        <v>1.576</v>
+        <v>0.975</v>
       </c>
       <c r="P156" t="n">
-        <v>1.168</v>
+        <v>0.741</v>
       </c>
       <c r="Q156" t="n">
-        <v>0.248</v>
+        <v>0.405</v>
       </c>
       <c r="R156" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.437</v>
       </c>
       <c r="S156" t="n">
-        <v>0.192</v>
+        <v>0.117</v>
       </c>
       <c r="T156" t="n">
-        <v>0.011</v>
+        <v>0.006</v>
       </c>
       <c r="U156" t="n">
-        <v>0.15</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="V156" t="n">
-        <v>0.586</v>
+        <v>0.274</v>
       </c>
       <c r="W156" t="n">
-        <v>0.458</v>
+        <v>0.302</v>
       </c>
       <c r="X156" t="n">
-        <v>0.037</v>
+        <v>0.09</v>
       </c>
       <c r="Y156" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Z156" t="n">
-        <v>6.96</v>
+        <v>4.971</v>
       </c>
       <c r="AA156" t="n">
-        <v>9.17</v>
+        <v>6.484</v>
       </c>
       <c r="AB156" t="n">
-        <v>0.138</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AC156" t="n">
-        <v>0.619</v>
+        <v>0.483</v>
       </c>
       <c r="AD156" t="n">
-        <v>0.03</v>
+        <v>0.06900000000000001</v>
       </c>
     </row>
     <row r="157">
@@ -17319,21 +17319,21 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>669701</v>
+        <v>673962</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Josh Smith</t>
+          <t>Josh Jung</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>Jung</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -17355,61 +17355,61 @@
         <v>8</v>
       </c>
       <c r="L157" t="n">
-        <v>4.086</v>
+        <v>4.03</v>
       </c>
       <c r="M157" t="n">
-        <v>3.463</v>
+        <v>3.635</v>
       </c>
       <c r="N157" t="n">
-        <v>0.803</v>
+        <v>0.856</v>
       </c>
       <c r="O157" t="n">
-        <v>1.269</v>
+        <v>1.351</v>
       </c>
       <c r="P157" t="n">
-        <v>0.694</v>
+        <v>0.946</v>
       </c>
       <c r="Q157" t="n">
-        <v>0.522</v>
+        <v>0.307</v>
       </c>
       <c r="R157" t="n">
-        <v>0.522</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="S157" t="n">
-        <v>0.183</v>
+        <v>0.191</v>
       </c>
       <c r="T157" t="n">
-        <v>0.011</v>
+        <v>0.015</v>
       </c>
       <c r="U157" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.091</v>
       </c>
       <c r="V157" t="n">
-        <v>0.442</v>
+        <v>0.446</v>
       </c>
       <c r="W157" t="n">
-        <v>0.472</v>
+        <v>0.42</v>
       </c>
       <c r="X157" t="n">
-        <v>0.102</v>
+        <v>0.043</v>
       </c>
       <c r="Y157" t="n">
-        <v>0.082</v>
+        <v>0.033</v>
       </c>
       <c r="Z157" t="n">
-        <v>6.717</v>
+        <v>6.173</v>
       </c>
       <c r="AA157" t="n">
-        <v>8.917</v>
+        <v>8.074</v>
       </c>
       <c r="AB157" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AC157" t="n">
-        <v>0.571</v>
+        <v>0.604</v>
       </c>
       <c r="AD157" t="n">
-        <v>0.079</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="158">
@@ -17427,16 +17427,16 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>673962</v>
+        <v>677649</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Josh Jung</t>
+          <t>Ezequiel Duran</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Jung</t>
+          <t>Duran</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -17463,61 +17463,61 @@
         <v>9</v>
       </c>
       <c r="L158" t="n">
-        <v>3.957</v>
+        <v>3.843</v>
       </c>
       <c r="M158" t="n">
-        <v>3.565</v>
+        <v>3.465</v>
       </c>
       <c r="N158" t="n">
-        <v>0.829</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="O158" t="n">
-        <v>1.297</v>
+        <v>1.265</v>
       </c>
       <c r="P158" t="n">
-        <v>0.886</v>
+        <v>0.867</v>
       </c>
       <c r="Q158" t="n">
-        <v>0.3</v>
+        <v>0.296</v>
       </c>
       <c r="R158" t="n">
-        <v>0.544</v>
+        <v>0.545</v>
       </c>
       <c r="S158" t="n">
-        <v>0.187</v>
+        <v>0.17</v>
       </c>
       <c r="T158" t="n">
-        <v>0.011</v>
+        <v>0.005</v>
       </c>
       <c r="U158" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.091</v>
       </c>
       <c r="V158" t="n">
-        <v>0.452</v>
+        <v>0.405</v>
       </c>
       <c r="W158" t="n">
-        <v>0.434</v>
+        <v>0.403</v>
       </c>
       <c r="X158" t="n">
-        <v>0.044</v>
+        <v>0.096</v>
       </c>
       <c r="Y158" t="n">
-        <v>0.037</v>
+        <v>0.077</v>
       </c>
       <c r="Z158" t="n">
-        <v>6.075</v>
+        <v>6.031</v>
       </c>
       <c r="AA158" t="n">
-        <v>7.981</v>
+        <v>7.852</v>
       </c>
       <c r="AB158" t="n">
-        <v>0.083</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AC158" t="n">
-        <v>0.588</v>
+        <v>0.575</v>
       </c>
       <c r="AD158" t="n">
-        <v>0.036</v>
+        <v>0.074</v>
       </c>
     </row>
     <row r="159">
@@ -17568,64 +17568,64 @@
         </is>
       </c>
       <c r="K159" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L159" t="n">
-        <v>3.796</v>
+        <v>4.169</v>
       </c>
       <c r="M159" t="n">
-        <v>3.463</v>
+        <v>3.819</v>
       </c>
       <c r="N159" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.733</v>
       </c>
       <c r="O159" t="n">
-        <v>1.156</v>
+        <v>1.271</v>
       </c>
       <c r="P159" t="n">
-        <v>1.001</v>
+        <v>1.12</v>
       </c>
       <c r="Q159" t="n">
-        <v>0.249</v>
+        <v>0.271</v>
       </c>
       <c r="R159" t="n">
-        <v>0.433</v>
+        <v>0.443</v>
       </c>
       <c r="S159" t="n">
-        <v>0.151</v>
+        <v>0.162</v>
       </c>
       <c r="T159" t="n">
-        <v>0.003</v>
+        <v>0.008</v>
       </c>
       <c r="U159" t="n">
-        <v>0.103</v>
+        <v>0.12</v>
       </c>
       <c r="V159" t="n">
-        <v>0.363</v>
+        <v>0.399</v>
       </c>
       <c r="W159" t="n">
-        <v>0.306</v>
+        <v>0.349</v>
       </c>
       <c r="X159" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.098</v>
       </c>
       <c r="Y159" t="n">
-        <v>0.055</v>
+        <v>0.081</v>
       </c>
       <c r="Z159" t="n">
-        <v>5.215</v>
+        <v>5.846</v>
       </c>
       <c r="AA159" t="n">
-        <v>6.79</v>
+        <v>7.625</v>
       </c>
       <c r="AB159" t="n">
-        <v>0.098</v>
+        <v>0.113</v>
       </c>
       <c r="AC159" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="AD159" t="n">
-        <v>0.054</v>
+        <v>0.077</v>
       </c>
     </row>
     <row r="160">
@@ -17643,21 +17643,21 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>690976</v>
+        <v>687221</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Alex Freeland</t>
+          <t>Dalton Rushing</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Freeland</t>
+          <t>Rushing</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -17676,64 +17676,64 @@
         </is>
       </c>
       <c r="K160" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L160" t="n">
-        <v>3.444</v>
+        <v>3.688</v>
       </c>
       <c r="M160" t="n">
-        <v>3.074</v>
+        <v>3.376</v>
       </c>
       <c r="N160" t="n">
-        <v>0.511</v>
+        <v>0.572</v>
       </c>
       <c r="O160" t="n">
-        <v>0.828</v>
+        <v>1.034</v>
       </c>
       <c r="P160" t="n">
-        <v>1.282</v>
+        <v>1.262</v>
       </c>
       <c r="Q160" t="n">
-        <v>0.303</v>
+        <v>0.235</v>
       </c>
       <c r="R160" t="n">
-        <v>0.334</v>
+        <v>0.341</v>
       </c>
       <c r="S160" t="n">
-        <v>0.102</v>
+        <v>0.116</v>
       </c>
       <c r="T160" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="U160" t="n">
-        <v>0.065</v>
+        <v>0.115</v>
       </c>
       <c r="V160" t="n">
-        <v>0.24</v>
+        <v>0.33</v>
       </c>
       <c r="W160" t="n">
-        <v>0.306</v>
+        <v>0.296</v>
       </c>
       <c r="X160" t="n">
-        <v>0.033</v>
+        <v>0.019</v>
       </c>
       <c r="Y160" t="n">
-        <v>0.026</v>
+        <v>0.013</v>
       </c>
       <c r="Z160" t="n">
-        <v>4.068</v>
+        <v>4.542</v>
       </c>
       <c r="AA160" t="n">
-        <v>5.365</v>
+        <v>5.986</v>
       </c>
       <c r="AB160" t="n">
-        <v>0.064</v>
+        <v>0.112</v>
       </c>
       <c r="AC160" t="n">
-        <v>0.412</v>
+        <v>0.463</v>
       </c>
       <c r="AD160" t="n">
-        <v>0.025</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="161">
@@ -17751,97 +17751,97 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>694497</v>
+        <v>690976</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Evan Carter</t>
+          <t>Alex Freeland</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Carter</t>
+          <t>Freeland</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
           <t>TEX</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>LAD</t>
         </is>
       </c>
       <c r="K161" t="n">
         <v>6</v>
       </c>
       <c r="L161" t="n">
-        <v>4.229</v>
+        <v>3.886</v>
       </c>
       <c r="M161" t="n">
-        <v>3.524</v>
+        <v>3.465</v>
       </c>
       <c r="N161" t="n">
-        <v>0.712</v>
+        <v>0.549</v>
       </c>
       <c r="O161" t="n">
-        <v>1.165</v>
+        <v>0.893</v>
       </c>
       <c r="P161" t="n">
-        <v>0.97</v>
+        <v>1.458</v>
       </c>
       <c r="Q161" t="n">
-        <v>0.622</v>
+        <v>0.339</v>
       </c>
       <c r="R161" t="n">
-        <v>0.45</v>
+        <v>0.364</v>
       </c>
       <c r="S161" t="n">
-        <v>0.161</v>
+        <v>0.102</v>
       </c>
       <c r="T161" t="n">
-        <v>0.011</v>
+        <v>0.006</v>
       </c>
       <c r="U161" t="n">
-        <v>0.09</v>
+        <v>0.077</v>
       </c>
       <c r="V161" t="n">
-        <v>0.386</v>
+        <v>0.277</v>
       </c>
       <c r="W161" t="n">
-        <v>0.475</v>
+        <v>0.286</v>
       </c>
       <c r="X161" t="n">
-        <v>0.249</v>
+        <v>0.034</v>
       </c>
       <c r="Y161" t="n">
-        <v>0.208</v>
+        <v>0.028</v>
       </c>
       <c r="Z161" t="n">
-        <v>7.146</v>
+        <v>4.36</v>
       </c>
       <c r="AA161" t="n">
-        <v>9.476000000000001</v>
+        <v>5.747</v>
       </c>
       <c r="AB161" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.075</v>
       </c>
       <c r="AC161" t="n">
-        <v>0.525</v>
+        <v>0.439</v>
       </c>
       <c r="AD161" t="n">
-        <v>0.19</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="162">
@@ -17859,21 +17859,21 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>694671</v>
+        <v>694497</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Wyatt Langford</t>
+          <t>Evan Carter</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Langford</t>
+          <t>Carter</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -17895,61 +17895,61 @@
         <v>2</v>
       </c>
       <c r="L162" t="n">
-        <v>4.795</v>
+        <v>4.729</v>
       </c>
       <c r="M162" t="n">
-        <v>3.922</v>
+        <v>3.892</v>
       </c>
       <c r="N162" t="n">
-        <v>0.921</v>
+        <v>0.773</v>
       </c>
       <c r="O162" t="n">
-        <v>1.648</v>
+        <v>1.254</v>
       </c>
       <c r="P162" t="n">
-        <v>1.164</v>
+        <v>1.064</v>
       </c>
       <c r="Q162" t="n">
-        <v>0.779</v>
+        <v>0.737</v>
       </c>
       <c r="R162" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.496</v>
       </c>
       <c r="S162" t="n">
-        <v>0.162</v>
+        <v>0.167</v>
       </c>
       <c r="T162" t="n">
-        <v>0.013</v>
+        <v>0.016</v>
       </c>
       <c r="U162" t="n">
-        <v>0.18</v>
+        <v>0.094</v>
       </c>
       <c r="V162" t="n">
-        <v>0.542</v>
+        <v>0.387</v>
       </c>
       <c r="W162" t="n">
-        <v>0.67</v>
+        <v>0.569</v>
       </c>
       <c r="X162" t="n">
-        <v>0.275</v>
+        <v>0.286</v>
       </c>
       <c r="Y162" t="n">
-        <v>0.224</v>
+        <v>0.232</v>
       </c>
       <c r="Z162" t="n">
-        <v>9.513</v>
+        <v>7.937</v>
       </c>
       <c r="AA162" t="n">
-        <v>12.668</v>
+        <v>10.54</v>
       </c>
       <c r="AB162" t="n">
-        <v>0.165</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AC162" t="n">
-        <v>0.626</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="AD162" t="n">
-        <v>0.206</v>
+        <v>0.204</v>
       </c>
     </row>
     <row r="163">
@@ -18000,64 +18000,64 @@
         </is>
       </c>
       <c r="K163" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L163" t="n">
-        <v>3.472</v>
+        <v>3.324</v>
       </c>
       <c r="M163" t="n">
-        <v>3.188</v>
+        <v>3.04</v>
       </c>
       <c r="N163" t="n">
-        <v>0.514</v>
+        <v>0.49</v>
       </c>
       <c r="O163" t="n">
-        <v>0.843</v>
+        <v>0.775</v>
       </c>
       <c r="P163" t="n">
-        <v>1.262</v>
+        <v>1.19</v>
       </c>
       <c r="Q163" t="n">
-        <v>0.223</v>
+        <v>0.22</v>
       </c>
       <c r="R163" t="n">
-        <v>0.33</v>
+        <v>0.327</v>
       </c>
       <c r="S163" t="n">
-        <v>0.108</v>
+        <v>0.099</v>
       </c>
       <c r="T163" t="n">
-        <v>0.008</v>
+        <v>0.005</v>
       </c>
       <c r="U163" t="n">
-        <v>0.068</v>
+        <v>0.059</v>
       </c>
       <c r="V163" t="n">
-        <v>0.242</v>
+        <v>0.211</v>
       </c>
       <c r="W163" t="n">
-        <v>0.266</v>
+        <v>0.279</v>
       </c>
       <c r="X163" t="n">
-        <v>0.155</v>
+        <v>0.158</v>
       </c>
       <c r="Y163" t="n">
-        <v>0.128</v>
+        <v>0.133</v>
       </c>
       <c r="Z163" t="n">
-        <v>4.378</v>
+        <v>4.187</v>
       </c>
       <c r="AA163" t="n">
-        <v>5.663</v>
+        <v>5.412</v>
       </c>
       <c r="AB163" t="n">
-        <v>0.066</v>
+        <v>0.058</v>
       </c>
       <c r="AC163" t="n">
-        <v>0.412</v>
+        <v>0.401</v>
       </c>
       <c r="AD163" t="n">
-        <v>0.12</v>
+        <v>0.127</v>
       </c>
     </row>
     <row r="164">
